--- a/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="89520" uniqueCount="905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="93148" uniqueCount="1307">
   <si>
     <t>Year</t>
   </si>
@@ -2729,6 +2729,1212 @@
   </si>
   <si>
     <t>MaxForce</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10418\compression\COMPRESSION_20240401_160942_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10418\tension\TENSION_20240401_163910_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10418\tension\TENSION_20240401_163910_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10418\fracture\Fracture_20240401_164955_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10418\fracture\Fracture_20240401_164955_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10418\fracture\Fracture_20240401_164955_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10418\fracture\Fracture_20240401_164955_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10418\fracture\Fracture_20240401_164955_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10418\fracture\Fracture_20240401_164955_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10418\fracture\Fracture_20240401_164955_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10428\compression\COMPRESSION_20240401_185443_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10428\compression\COMPRESSION_20240401_185443_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10428\tension\TENSION_20240401_191732_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10428\tension\TENSION_20240401_191732_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10428\fracture\Fracture_20240401_193229_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10428\fracture\Fracture_20240401_193229_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10428\fracture\Fracture_20240401_193229_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10428\fracture\Fracture_20240401_193229_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10428\fracture\Fracture_20240401_193229_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10428\fracture\Fracture_20240401_193229_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10428\fracture\Fracture_20240401_193229_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10428\fracture\Fracture_20240401_193229_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10432\compression\COMPRESSION_20240401_82330_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10432\compression\COMPRESSION_20240401_82330_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10432\fracture\Fracture_20240401_92159_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10432\fracture\Fracture_20240401_90926_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10432\fracture\Fracture_20240401_90926_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10432\fracture\Fracture_20240401_92159_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10432\fracture\Fracture_20240401_92159_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10432\fracture\Fracture_20240401_90926_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10432\fracture\Fracture_20240401_92159_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10432\fracture\Fracture_20240401_90926_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10415\compression\COMPRESSION_20240402_91710_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10415\tension\TENSION_20240402_82137_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10415\tension\TENSION_20240402_84137_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10415\fracture\Fracture_20240402_90350_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10415\fracture\Fracture_20240402_90554_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10415\fracture\Fracture_20240402_84959_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10415\fracture\Fracture_20240402_90731_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10415\fracture\Fracture_20240402_85726_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10415\fracture\Fracture_20240402_85930_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10415\fracture\Fracture_20240402_90913_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10415\fracture\Fracture_20240402_90053_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10417\compression\COMPRESSION_20240402_111706_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10417\compression\COMPRESSION_20240402_111706_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10417\tension\TENSION_20240404_121403_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10417\tension\TENSION_20240404_121403_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10417\fracture\Fracture_20240402_122031_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10417\fracture\Fracture_20240402_122031_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10417\fracture\Fracture_20240402_122031_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10417\fracture\Fracture_20240402_122031_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10417\fracture\Fracture_20240402_122031_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10417\fracture\Fracture_20240402_122031_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10417\fracture\Fracture_20240402_122031_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10417\fracture\Fracture_20240402_122031_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10422\compression\COMPRESSION_20240402_180620_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10422\compression\COMPRESSION_20240402_180620_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10422\tension\TENSION_20240402_181443_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10422\tension\TENSION_20240402_181443_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10422\fracture\Fracture_20240402_173811_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10422\fracture\Fracture_20240402_173811_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10422\fracture\Fracture_20240402_173811_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10422\fracture\Fracture_20240402_173811_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10422\fracture\Fracture_20240402_173811_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10422\fracture\Fracture_20240402_173811_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10422\fracture\Fracture_20240402_173811_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10422\fracture\Fracture_20240402_173811_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10431\compression\COMPRESSION_20240402_143204_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10431\compression\COMPRESSION_20240402_143204_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10431\tension\TENSION_20240402_144717_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10431\tension\TENSION_20240402_144717_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10431\fracture\Fracture_20240402_150850_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10431\fracture\Fracture_20240402_150850_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10431\fracture\Fracture_20240402_150850_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10431\fracture\Fracture_20240402_150850_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10431\fracture\Fracture_20240402_150850_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10431\fracture\Fracture_20240402_150850_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10431\fracture\Fracture_20240402_150850_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10431\fracture\Fracture_20240402_150850_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10416\compression\COMPRESSION_20240403_84523_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10416\compression\COMPRESSION_20240403_84523_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10416\tension\TENSION_20240403_81840_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10416\tension\TENSION_20240403_81840_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10416\fracture\Fracture_20240403_91159_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10416\fracture\Fracture_20240404_114124_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10416\fracture\Fracture_20240403_91159_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10416\fracture\Fracture_20240403_91159_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10416\fracture\Fracture_20240403_91159_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10416\fracture\Fracture_20240403_91159_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10416\fracture\Fracture_20240403_91159_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10416\fracture\Fracture_20240403_91159_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10424\compression\COMPRESSION_20240403_164647_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10424\compression\COMPRESSION_20240403_164647_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10424\tension\TENSION_20240403_172802_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10424\tension\TENSION_20240403_172802_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10424\fracture\Fracture_20240403_170753_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10424\fracture\Fracture_20240403_170753_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10424\fracture\Fracture_20240403_170753_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10424\fracture\Fracture_20240403_170753_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10424\fracture\Fracture_20240403_170753_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10424\fracture\Fracture_20240403_170753_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10424\fracture\Fracture_20240403_170753_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10424\fracture\Fracture_20240403_170753_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10425\compression\COMPRESSION_20240403_135735_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10425\compression\COMPRESSION_20240403_135735_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10425\fracture\Fracture_20240403_144224_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10425\fracture\Fracture_20240403_144224_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10425\fracture\Fracture_20240403_144224_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10425\fracture\Fracture_20240403_144224_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10425\fracture\Fracture_20240403_144224_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10425\fracture\Fracture_20240403_144224_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10425\fracture\Fracture_20240403_144224_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10425\fracture\Fracture_20240403_144224_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10419\fracture\Fracture_20240404_91154_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10419\fracture\Fracture_20240404_91414_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10419\fracture\Fracture_20240404_91027_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10419\fracture\Fracture_20240404_90541_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10419\fracture\Fracture_20240404_85908_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10419\fracture\Fracture_20240404_90628_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10419\fracture\Fracture_20240404_90813_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10419\fracture\Fracture_20240404_91609_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10421\compression\COMPRESSION_20240404_112804_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10421\compression\COMPRESSION_20240404_112804_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10421\tension\TENSION_20240404_121403_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10421\tension\TENSION_20240404_121403_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10421\fracture\Fracture_20240404_114124_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10421\fracture\Fracture_20240404_114124_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10421\fracture\Fracture_20240404_114124_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10421\fracture\Fracture_20240404_114124_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10421\fracture\Fracture_20240404_114124_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10421\fracture\Fracture_20240404_114124_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10421\fracture\Fracture_20240404_114124_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10421\fracture\Fracture_20240404_114124_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\COMPRESSION_20240404_175301.is_comp_Exports\COMPRESSION_20240404_175301_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\COMPRESSION_20240404_175301.is_comp_Exports\COMPRESSION_20240404_175301_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\COMPRESSION_20240404_175301.is_comp_Exports\COMPRESSION_20240404_175301_1_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\COMPRESSION_20240404_175301.is_comp_Exports\COMPRESSION_20240404_175301_2_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\TENSION_20240404_174421.is_tens_Exports\TENSION_20240404_174421_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\TENSION_20240404_174421.is_tens_Exports\TENSION_20240404_174421_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\Fracture_20240404_180435.is_tens_Exports\Fracture_20240404_180435_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\Fracture_20240404_180435.is_tens_Exports\Fracture_20240404_180435_6_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\Fracture_20240404_180435.is_tens_Exports\Fracture_20240404_180435_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\Fracture_20240404_180435.is_tens_Exports\Fracture_20240404_180435_1_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\Fracture_20240404_180435.is_tens_Exports\Fracture_20240404_180435_7_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\Fracture_20240404_180435.is_tens_Exports\Fracture_20240404_180435_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\Fracture_20240404_180435.is_tens_Exports\Fracture_20240404_180435_5_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\Fracture_20240404_180435.is_tens_Exports\Fracture_20240404_180435_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\Fracture_20240404_180435.is_tens_Exports\Fracture_20240404_180435_8_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\Fracture_20240404_180435.is_tens_Exports\Fracture_20240404_180435_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\Fracture_20240404_180435.is_tens_Exports\Fracture_20240404_180435_2_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\Fracture_20240404_180435.is_tens_Exports\Fracture_20240404_180435_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\Fracture_20240404_180435.is_tens_Exports\Fracture_20240404_180435_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\Fracture_20240404_180435.is_tens_Exports\Fracture_20240404_180435_3_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\Fracture_20240404_180435.is_tens_Exports\Fracture_20240404_180435_4_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10420\COMPRESSION_20240405_121754.is_comp_Exports\COMPRESSION_20240405_121754_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10420\COMPRESSION_20240405_121754.is_comp_Exports\COMPRESSION_20240405_121754_1_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10420\COMPRESSION_20240405_121754.is_comp_Exports\COMPRESSION_20240405_121754_2_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10420\Fracture_20240405_114504.is_tens_Exports\Fracture_20240405_114504_5_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10420\Fracture_20240405_114504.is_tens_Exports\Fracture_20240405_114504_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10420\Fracture_20240405_114504.is_tens_Exports\Fracture_20240405_114504_4_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10420\Fracture_20240405_114504.is_tens_Exports\Fracture_20240405_114504_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10420\Fracture_20240405_114504.is_tens_Exports\Fracture_20240405_114504_1_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10420\Fracture_20240405_114504.is_tens_Exports\Fracture_20240405_114504_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10420\Fracture_20240405_114504.is_tens_Exports\Fracture_20240405_114504_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10420\Fracture_20240405_114504.is_tens_Exports\Fracture_20240405_114504_3_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10420\Fracture_20240405_114504.is_tens_Exports\Fracture_20240405_114504_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10420\Fracture_20240405_114504.is_tens_Exports\Fracture_20240405_114504_7_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10420\Fracture_20240405_114504.is_tens_Exports\Fracture_20240405_114504_8_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10420\Fracture_20240405_114504.is_tens_Exports\Fracture_20240405_114504_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10420\Fracture_20240405_114504.is_tens_Exports\Fracture_20240405_114504_2_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10420\Fracture_20240405_114504.is_tens_Exports\Fracture_20240405_114504_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10420\Fracture_20240405_114504.is_tens_Exports\Fracture_20240405_114504_6_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10420\Fracture_20240405_114504.is_tens_Exports\Fracture_20240405_114504_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10434\COMPRESSION_20240405_152822.is_comp_Exports\COMPRESSION_20240405_152822_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10434\COMPRESSION_20240405_152822.is_comp_Exports\COMPRESSION_20240405_152822_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10434\COMPRESSION_20240405_152822.is_comp_Exports\COMPRESSION_20240405_152822_1_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10434\COMPRESSION_20240405_152822.is_comp_Exports\COMPRESSION_20240405_152822_2_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10434\TENSION_20240405_150639.is_tens_Exports\TENSION_20240405_150639_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10434\Fracture_20240405_154123.is_tens_Exports\Fracture_20240405_154123_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10434\Fracture_20240405_154123.is_tens_Exports\Fracture_20240405_154123_1_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10434\Fracture_20240405_154123.is_tens_Exports\Fracture_20240405_154123_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10434\Fracture_20240405_154123.is_tens_Exports\Fracture_20240405_154123_2_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10434\Fracture_20240405_154123.is_tens_Exports\Fracture_20240405_154123_3_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10434\Fracture_20240405_154123.is_tens_Exports\Fracture_20240405_154123_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10434\Fracture_20240405_154123.is_tens_Exports\Fracture_20240405_154123_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10434\Fracture_20240405_154123.is_tens_Exports\Fracture_20240405_154123_7_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10434\Fracture_20240405_154123.is_tens_Exports\Fracture_20240405_154123_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10434\Fracture_20240405_154123.is_tens_Exports\Fracture_20240405_154123_6_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10434\Fracture_20240405_154123.is_tens_Exports\Fracture_20240405_154123_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10434\Fracture_20240405_154123.is_tens_Exports\Fracture_20240405_154123_8_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10434\Fracture_20240405_154123.is_tens_Exports\Fracture_20240405_154123_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10434\Fracture_20240405_154123.is_tens_Exports\Fracture_20240405_154123_4_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10434\Fracture_20240405_154123.is_tens_Exports\Fracture_20240405_154123_5_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10434\Fracture_20240405_154123.is_tens_Exports\Fracture_20240405_154123_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10418\compression\COMPRESSION_20240415_164723_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10418\compression\COMPRESSION_20240415_164723_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10418\tension\TENSION_20240415_163324_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10418\tension\TENSION_20240415_163324_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10418\fracture\Fracture_20240415_160544_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10418\fracture\Fracture_20240415_160544_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10418\fracture\Fracture_20240415_160544_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10418\fracture\Fracture_20240415_160544_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10418\fracture\Fracture_20240415_160544_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10418\fracture\Fracture_20240415_160544_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10418\fracture\Fracture_20240415_160544_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10418\fracture\Fracture_20240415_160544_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10428\compression\COMPRESSION_20240415_185638_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10428\compression\COMPRESSION_20240415_185638_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10428\tension\TENSION_20240415_195322_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10428\tension\TENSION_20240415_195322_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10428\fracture\Fracture_20240415_192460_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10428\fracture\Fracture_20240415_192460_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10428\fracture\Fracture_20240415_192460_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10428\fracture\Fracture_20240415_192460_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10428\fracture\Fracture_20240415_192460_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10428\fracture\Fracture_20240415_192460_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10428\fracture\Fracture_20240415_192460_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10428\fracture\Fracture_20240415_192460_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10432\compression\COMPRESSION_20240415_83136_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10432\compression\COMPRESSION_20240415_83136_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10432\tension\TENSION_20240415_90842_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10432\fracture\Fracture_20240415_91957_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10432\fracture\Fracture_20240415_91957_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10432\fracture\Fracture_20240415_91957_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10432\fracture\Fracture_20240415_91957_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10432\fracture\Fracture_20240415_91957_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10432\fracture\Fracture_20240415_91957_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10432\fracture\Fracture_20240415_91957_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10432\fracture\Fracture_20240415_91957_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10415\compression\COMPRESSION_20240416_84813_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10415\compression\COMPRESSION_20240416_84813_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10415\tension\TENSION_20240416_81513_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10415\tension\TENSION_20240416_81513_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10415\fracture\Fracture_20240416_90122_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10415\fracture\Fracture_20240416_90122_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10415\fracture\Fracture_20240416_90122_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10415\fracture\Fracture_20240416_90122_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10415\fracture\Fracture_20240416_90122_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10415\fracture\Fracture_20240416_90122_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10415\fracture\Fracture_20240416_90122_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10415\fracture\Fracture_20240416_90122_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10417\compression\COMPRESSION_20240416_120439_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10417\compression\COMPRESSION_20240416_120439_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10417\tension\TENSION_20240416_121310_3.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10417\tension\TENSION_20240416_121310_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10417\fracture\Fracture_20240416_114211_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10417\fracture\Fracture_20240416_114211_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10417\fracture\Fracture_20240404_114124_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10417\fracture\Fracture_20240416_114211_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10417\fracture\Fracture_20240416_114211_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10417\fracture\Fracture_20240416_114211_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10417\fracture\Fracture_20240416_114211_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10417\fracture\Fracture_20240416_114211_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10422\compression\COMPRESSION_20240416_172030_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10422\compression\COMPRESSION_20240416_172030_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10422\tension\TENSION_20240416_174844_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10422\tension\TENSION_20240416_174844_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10422\fracture\Fracture_20240416_180236_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10422\fracture\Fracture_20240416_180236_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10422\fracture\Fracture_20240416_180236_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10422\fracture\Fracture_20240416_180236_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10422\fracture\Fracture_20240416_180236_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10422\fracture\Fracture_20240416_180236_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10422\fracture\Fracture_20240416_180236_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10422\fracture\Fracture_20240416_180236_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10431\compression\COMPRESSION_20240416_145110_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10431\compression\COMPRESSION_20240416_145110_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10431\tension\TENSION_20240416_144009_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10431\tension\TENSION_20240416_144009_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10431\fracture\Fracture_20240416_150238_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10431\fracture\Fracture_20240416_150238_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10431\fracture\Fracture_20240416_150238_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10431\fracture\Fracture_20240416_150238_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10431\fracture\Fracture_20240416_150238_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10431\fracture\Fracture_20240416_150238_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10431\fracture\Fracture_20240416_150238_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10431\fracture\Fracture_20240416_150238_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_80438\compression\COMPRESSION_20241119_164057_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_80438\compression\COMPRESSION_20241119_164057_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_80438\tension\TENSION_20241119_162250_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_80438\tension\TENSION_20241119_162250_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_80438\fracture\Fracture_20241119_165759_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_80438\fracture\Fracture_20241119_165759_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_80438\fracture\Fracture_20241119_165759_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_80438\fracture\Fracture_20241119_165759_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_80438\fracture\Fracture_20241119_165759_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_80438\fracture\Fracture_20241119_165759_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_80438\fracture\Fracture_20241119_165759_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_80438\fracture\Fracture_20241119_165759_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10416\compression\COMPRESSION_20240417_84148_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10416\compression\COMPRESSION_20240417_84148_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10416\fracture\Fracture_20240417_81020_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10416\fracture\Fracture_20240417_81020_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10416\fracture\Fracture_20240417_81020_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10416\fracture\Fracture_20240417_81020_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10416\fracture\Fracture_20240417_81020_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10416\fracture\Fracture_20240417_81020_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10416\fracture\Fracture_20240417_81020_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10416\fracture\Fracture_20240417_81020_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10424\compression\COMPRESSION_20240417_171125_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10424\compression\COMPRESSION_20240417_171125_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10424\tension\TENSION_20240417_173337_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10424\tension\TENSION_20240417_173337_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10424\fracture\Fracture_20240417_175036_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10424\fracture\Fracture_20240417_175036_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10424\fracture\Fracture_20240417_175036_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10424\fracture\Fracture_20240417_175036_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10424\fracture\Fracture_20240417_175036_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10424\fracture\Fracture_20240417_175036_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10424\fracture\Fracture_20240417_175036_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10424\fracture\Fracture_20240417_175036_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10425\compression\COMPRESSION_20240417_140453_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10425\compression\COMPRESSION_20240417_140453_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10425\tension\TENSION_20240417_135228_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10425\tension\TENSION_20240417_135228_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10425\fracture\Fracture_20240417_141803_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10425\fracture\Fracture_20240417_141803_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10425\fracture\Fracture_20240417_141803_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10425\fracture\Fracture_20240417_141803_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10425\fracture\Fracture_20240417_141803_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10425\fracture\Fracture_20240417_141803_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10425\fracture\Fracture_20240417_141803_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10425\fracture\Fracture_20240417_141803_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_80460\compression\COMPRESSION_20241120_192108_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_80460\compression\COMPRESSION_20241120_192108_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_80460\tension\TENSION_20241120_193920_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_80460\tension\TENSION_20241120_193920_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_80460\fracture\Fracture_20241120_184330_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_80460\fracture\Fracture_20241120_184330_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_80460\fracture\Fracture_20241120_184330_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_80460\fracture\Fracture_20241120_184330_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_80460\fracture\Fracture_20241120_184330_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_80460\fracture\Fracture_20241120_184330_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_80460\fracture\Fracture_20241120_184330_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10419\compression\COMPRESSION_20240418_82512_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10419\compression\COMPRESSION_20240418_82512_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10419\tension\TENSION_20240418_91816_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10419\tension\TENSION_20240418_85826_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10419\fracture\Fracture_20240418_94536_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10419\fracture\Fracture_20240418_94536_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10419\fracture\Fracture_20240418_92606_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10419\fracture\Fracture_20240418_94536_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10419\fracture\Fracture_20240418_92606_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10419\fracture\Fracture_20240418_92606_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10419\fracture\Fracture_20240418_94536_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10419\fracture\Fracture_20240418_92606_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10421\compression\COMPRESSION_20240418_120928_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10421\compression\COMPRESSION_20240418_120928_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10421\tension\TENSION_20240418_115359_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10421\tension\TENSION_20240418_115359_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10421\fracture\Fracture_20240418_112559_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10421\fracture\Fracture_20240418_112559_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10421\fracture\Fracture_20240418_112559_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10421\fracture\Fracture_20240418_112559_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10421\fracture\Fracture_20240418_112559_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10421\fracture\Fracture_20240418_112559_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10421\fracture\Fracture_20240418_112559_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10421\fracture\Fracture_20240418_112559_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10423\compression\COMPRESSION_20240418_182603_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10423\compression\COMPRESSION_20240418_182603_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10423\tension\TENSION_20240418_175708_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10423\tension\TENSION_20240418_175708_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10423\fracture\Fracture_20240418_183839_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10423\fracture\Fracture_20240418_183839_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10423\fracture\Fracture_20240418_183839_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10423\fracture\Fracture_20240418_183839_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10423\fracture\Fracture_20240418_183839_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10423\fracture\Fracture_20240418_183839_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10423\fracture\Fracture_20240418_183839_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10423\fracture\Fracture_20240418_183839_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10430\compression\COMPRESSION_20240418_142637_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10430\compression\COMPRESSION_20240418_142637_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10430\tension\TENSION_20240418_150031_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10430\tension\TENSION_20240418_150031_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10430\fracture\Fracture_20240418_144330_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10430\fracture\Fracture_20240418_144330_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10430\fracture\Fracture_20240418_144330_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10430\fracture\Fracture_20240418_144330_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10430\fracture\Fracture_20240418_144330_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10430\fracture\Fracture_20240418_144330_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10430\fracture\Fracture_20240418_144330_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10430\fracture\Fracture_20240418_144330_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10420\compression\COMPRESSION_20240419_123337_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10420\compression\COMPRESSION_20240419_113912_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10420\fracture\Fracture_20240419_130559_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10420\fracture\Fracture_20240419_130855_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10420\fracture\Fracture_20240419_130034_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10420\fracture\Fracture_20240419_131135_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10420\fracture\Fracture_20240419_131022_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10420\fracture\Fracture_20240419_130423_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10420\fracture\Fracture_20240419_130222_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10434\compression\COMPRESSION_20240419_155330_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10434\compression\COMPRESSION_20240419_155330_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10434\tension\TENSION_20240419_153237_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10434\fracture\Fracture_20240419_151460_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10434\fracture\Fracture_20240419_151460_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10434\fracture\Fracture_20240419_151460_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10434\fracture\Fracture_20240419_151460_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10434\fracture\Fracture_20240419_151460_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10434\fracture\Fracture_20240419_151460_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10434\fracture\Fracture_20240419_151460_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10434\fracture\Fracture_20240419_151460_4_2.csv</t>
   </si>
 </sst>
 </file>
@@ -2777,16 +3983,16 @@
   <dimension ref="A1:J427"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.08984375" customWidth="true"/>
-    <col min="2" max="2" width="6.54296875" customWidth="true"/>
-    <col min="3" max="3" width="10.36328125" customWidth="true"/>
-    <col min="4" max="4" width="16.36328125" customWidth="true"/>
-    <col min="5" max="5" width="11.81640625" customWidth="true"/>
-    <col min="6" max="6" width="11.90625" customWidth="true"/>
-    <col min="7" max="7" width="7.90625" customWidth="true"/>
-    <col min="8" max="8" width="36.26953125" customWidth="true"/>
-    <col min="9" max="9" width="195.7265625" customWidth="true"/>
-    <col min="10" max="10" width="10.453125" customWidth="true"/>
+    <col min="1" max="1" width="14.85546875" customWidth="true"/>
+    <col min="2" max="2" width="7" customWidth="true"/>
+    <col min="3" max="3" width="11.28515625" customWidth="true"/>
+    <col min="4" max="4" width="17.28515625" customWidth="true"/>
+    <col min="5" max="5" width="12.7109375" customWidth="true"/>
+    <col min="6" max="6" width="13" customWidth="true"/>
+    <col min="7" max="7" width="8.5703125" customWidth="true"/>
+    <col min="8" max="8" width="37.42578125" customWidth="true"/>
+    <col min="9" max="9" width="175.28515625" customWidth="true"/>
+    <col min="10" max="10" width="10.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2847,7 +4053,7 @@
         <v>55</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>478</v>
+        <v>905</v>
       </c>
       <c r="J2" s="0">
         <v>11688.002</v>
@@ -2879,7 +4085,7 @@
         <v>57</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>480</v>
+        <v>906</v>
       </c>
       <c r="J3" s="0">
         <v>935.94889999999998</v>
@@ -2911,7 +4117,7 @@
         <v>58</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>481</v>
+        <v>907</v>
       </c>
       <c r="J4" s="0">
         <v>880.38310000000001</v>
@@ -2943,7 +4149,7 @@
         <v>59</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>482</v>
+        <v>908</v>
       </c>
       <c r="J5" s="0">
         <v>502.106</v>
@@ -2975,7 +4181,7 @@
         <v>60</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>483</v>
+        <v>909</v>
       </c>
       <c r="J6" s="0">
         <v>466.17020000000002</v>
@@ -3007,7 +4213,7 @@
         <v>61</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>484</v>
+        <v>910</v>
       </c>
       <c r="J7" s="0">
         <v>453.3066</v>
@@ -3039,7 +4245,7 @@
         <v>62</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>485</v>
+        <v>911</v>
       </c>
       <c r="J8" s="0">
         <v>443.37130000000002</v>
@@ -3071,7 +4277,7 @@
         <v>63</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>486</v>
+        <v>912</v>
       </c>
       <c r="J9" s="0">
         <v>438.5403</v>
@@ -3103,7 +4309,7 @@
         <v>64</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>487</v>
+        <v>913</v>
       </c>
       <c r="J10" s="0">
         <v>427.42660000000001</v>
@@ -3135,7 +4341,7 @@
         <v>66</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>489</v>
+        <v>914</v>
       </c>
       <c r="J11" s="0">
         <v>359.1311</v>
@@ -3167,7 +4373,7 @@
         <v>67</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>490</v>
+        <v>915</v>
       </c>
       <c r="J12" s="0">
         <v>15177.4365</v>
@@ -3199,7 +4405,7 @@
         <v>68</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>491</v>
+        <v>916</v>
       </c>
       <c r="J13" s="0">
         <v>10441.9121</v>
@@ -3231,7 +4437,7 @@
         <v>69</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>492</v>
+        <v>917</v>
       </c>
       <c r="J14" s="0">
         <v>1168.5962</v>
@@ -3263,7 +4469,7 @@
         <v>70</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>493</v>
+        <v>918</v>
       </c>
       <c r="J15" s="0">
         <v>1026.5851</v>
@@ -3295,7 +4501,7 @@
         <v>71</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>494</v>
+        <v>919</v>
       </c>
       <c r="J16" s="0">
         <v>551.72749999999996</v>
@@ -3327,7 +4533,7 @@
         <v>72</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>495</v>
+        <v>920</v>
       </c>
       <c r="J17" s="0">
         <v>484.46609999999998</v>
@@ -3359,7 +4565,7 @@
         <v>73</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>496</v>
+        <v>921</v>
       </c>
       <c r="J18" s="0">
         <v>462.44240000000002</v>
@@ -3391,7 +4597,7 @@
         <v>74</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>497</v>
+        <v>922</v>
       </c>
       <c r="J19" s="0">
         <v>438.6388</v>
@@ -3423,7 +4629,7 @@
         <v>75</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>498</v>
+        <v>923</v>
       </c>
       <c r="J20" s="0">
         <v>433.1481</v>
@@ -3455,7 +4661,7 @@
         <v>76</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>499</v>
+        <v>924</v>
       </c>
       <c r="J21" s="0">
         <v>417.18799999999999</v>
@@ -3487,7 +4693,7 @@
         <v>77</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>500</v>
+        <v>925</v>
       </c>
       <c r="J22" s="0">
         <v>403.36680000000001</v>
@@ -3519,7 +4725,7 @@
         <v>78</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>501</v>
+        <v>926</v>
       </c>
       <c r="J23" s="0">
         <v>344.44220000000001</v>
@@ -3551,7 +4757,7 @@
         <v>79</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>502</v>
+        <v>927</v>
       </c>
       <c r="J24" s="0">
         <v>13941.7637</v>
@@ -3583,7 +4789,7 @@
         <v>80</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>503</v>
+        <v>928</v>
       </c>
       <c r="J25" s="0">
         <v>10106.319299999999</v>
@@ -3615,7 +4821,7 @@
         <v>83</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>506</v>
+        <v>929</v>
       </c>
       <c r="J26" s="0">
         <v>538.54449999999997</v>
@@ -3647,7 +4853,7 @@
         <v>84</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>507</v>
+        <v>930</v>
       </c>
       <c r="J27" s="0">
         <v>528.50789999999995</v>
@@ -3679,7 +4885,7 @@
         <v>85</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>508</v>
+        <v>931</v>
       </c>
       <c r="J28" s="0">
         <v>515.40830000000005</v>
@@ -3711,7 +4917,7 @@
         <v>86</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>509</v>
+        <v>932</v>
       </c>
       <c r="J29" s="0">
         <v>505.25689999999997</v>
@@ -3743,7 +4949,7 @@
         <v>87</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>510</v>
+        <v>933</v>
       </c>
       <c r="J30" s="0">
         <v>428.78109999999998</v>
@@ -3775,7 +4981,7 @@
         <v>88</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>511</v>
+        <v>934</v>
       </c>
       <c r="J31" s="0">
         <v>373.29050000000001</v>
@@ -3807,7 +5013,7 @@
         <v>89</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>512</v>
+        <v>935</v>
       </c>
       <c r="J32" s="0">
         <v>357.77280000000002</v>
@@ -3839,7 +5045,7 @@
         <v>90</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>513</v>
+        <v>936</v>
       </c>
       <c r="J33" s="0">
         <v>326.51060000000001</v>
@@ -3871,7 +5077,7 @@
         <v>91</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>514</v>
+        <v>937</v>
       </c>
       <c r="J34" s="0">
         <v>12781.4072</v>
@@ -3903,7 +5109,7 @@
         <v>93</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>516</v>
+        <v>938</v>
       </c>
       <c r="J35" s="0">
         <v>1452.7743</v>
@@ -3935,7 +5141,7 @@
         <v>94</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>517</v>
+        <v>939</v>
       </c>
       <c r="J36" s="0">
         <v>1450.1411000000001</v>
@@ -3967,7 +5173,7 @@
         <v>95</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>518</v>
+        <v>940</v>
       </c>
       <c r="J37" s="0">
         <v>473.58769999999998</v>
@@ -3999,7 +5205,7 @@
         <v>96</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>519</v>
+        <v>941</v>
       </c>
       <c r="J38" s="0">
         <v>468.9753</v>
@@ -4031,7 +5237,7 @@
         <v>97</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>520</v>
+        <v>942</v>
       </c>
       <c r="J39" s="0">
         <v>453.3648</v>
@@ -4063,7 +5269,7 @@
         <v>98</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>521</v>
+        <v>943</v>
       </c>
       <c r="J40" s="0">
         <v>435.75220000000002</v>
@@ -4095,7 +5301,7 @@
         <v>99</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>522</v>
+        <v>944</v>
       </c>
       <c r="J41" s="0">
         <v>434.1336</v>
@@ -4127,7 +5333,7 @@
         <v>100</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>523</v>
+        <v>945</v>
       </c>
       <c r="J42" s="0">
         <v>429.1137</v>
@@ -4159,7 +5365,7 @@
         <v>101</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>524</v>
+        <v>946</v>
       </c>
       <c r="J43" s="0">
         <v>392.56209999999999</v>
@@ -4191,7 +5397,7 @@
         <v>102</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>525</v>
+        <v>947</v>
       </c>
       <c r="J44" s="0">
         <v>366.25650000000002</v>
@@ -4223,7 +5429,7 @@
         <v>103</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>526</v>
+        <v>948</v>
       </c>
       <c r="J45" s="0">
         <v>11646.511699999999</v>
@@ -4255,7 +5461,7 @@
         <v>104</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>527</v>
+        <v>949</v>
       </c>
       <c r="J46" s="0">
         <v>7558.6841000000004</v>
@@ -4287,7 +5493,7 @@
         <v>105</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>528</v>
+        <v>950</v>
       </c>
       <c r="J47" s="0">
         <v>1293.2311</v>
@@ -4319,7 +5525,7 @@
         <v>106</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>529</v>
+        <v>951</v>
       </c>
       <c r="J48" s="0">
         <v>1168.5597</v>
@@ -4351,7 +5557,7 @@
         <v>107</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>530</v>
+        <v>952</v>
       </c>
       <c r="J49" s="0">
         <v>531.21609999999998</v>
@@ -4383,7 +5589,7 @@
         <v>108</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>531</v>
+        <v>953</v>
       </c>
       <c r="J50" s="0">
         <v>470.07299999999998</v>
@@ -4415,7 +5621,7 @@
         <v>109</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>532</v>
+        <v>954</v>
       </c>
       <c r="J51" s="0">
         <v>439.15929999999997</v>
@@ -4447,7 +5653,7 @@
         <v>110</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>533</v>
+        <v>955</v>
       </c>
       <c r="J52" s="0">
         <v>424.38709999999998</v>
@@ -4479,7 +5685,7 @@
         <v>111</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>534</v>
+        <v>956</v>
       </c>
       <c r="J53" s="0">
         <v>419.4384</v>
@@ -4511,7 +5717,7 @@
         <v>112</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>535</v>
+        <v>957</v>
       </c>
       <c r="J54" s="0">
         <v>413.99000000000001</v>
@@ -4543,7 +5749,7 @@
         <v>113</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>536</v>
+        <v>958</v>
       </c>
       <c r="J55" s="0">
         <v>408.73599999999999</v>
@@ -4575,7 +5781,7 @@
         <v>114</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>537</v>
+        <v>959</v>
       </c>
       <c r="J56" s="0">
         <v>408.7253</v>
@@ -4607,7 +5813,7 @@
         <v>115</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>538</v>
+        <v>960</v>
       </c>
       <c r="J57" s="0">
         <v>11876.8555</v>
@@ -4639,7 +5845,7 @@
         <v>116</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>539</v>
+        <v>961</v>
       </c>
       <c r="J58" s="0">
         <v>10286.9082</v>
@@ -4671,7 +5877,7 @@
         <v>117</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>540</v>
+        <v>962</v>
       </c>
       <c r="J59" s="0">
         <v>1060.3289</v>
@@ -4703,7 +5909,7 @@
         <v>118</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>541</v>
+        <v>963</v>
       </c>
       <c r="J60" s="0">
         <v>1004.1268</v>
@@ -4735,7 +5941,7 @@
         <v>119</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>542</v>
+        <v>964</v>
       </c>
       <c r="J61" s="0">
         <v>497.2799</v>
@@ -4767,7 +5973,7 @@
         <v>120</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>543</v>
+        <v>965</v>
       </c>
       <c r="J62" s="0">
         <v>485.87290000000002</v>
@@ -4799,7 +6005,7 @@
         <v>121</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>544</v>
+        <v>966</v>
       </c>
       <c r="J63" s="0">
         <v>429.8492</v>
@@ -4831,7 +6037,7 @@
         <v>122</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>545</v>
+        <v>967</v>
       </c>
       <c r="J64" s="0">
         <v>425.51229999999998</v>
@@ -4863,7 +6069,7 @@
         <v>123</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>546</v>
+        <v>968</v>
       </c>
       <c r="J65" s="0">
         <v>396.25139999999999</v>
@@ -4895,7 +6101,7 @@
         <v>124</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>547</v>
+        <v>969</v>
       </c>
       <c r="J66" s="0">
         <v>392.3723</v>
@@ -4927,7 +6133,7 @@
         <v>125</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>548</v>
+        <v>970</v>
       </c>
       <c r="J67" s="0">
         <v>351.54930000000002</v>
@@ -4959,7 +6165,7 @@
         <v>126</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>549</v>
+        <v>971</v>
       </c>
       <c r="J68" s="0">
         <v>348.02690000000001</v>
@@ -4991,7 +6197,7 @@
         <v>127</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>550</v>
+        <v>972</v>
       </c>
       <c r="J69" s="0">
         <v>12171.997100000001</v>
@@ -5023,7 +6229,7 @@
         <v>128</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>551</v>
+        <v>973</v>
       </c>
       <c r="J70" s="0">
         <v>6862.1084000000001</v>
@@ -5055,7 +6261,7 @@
         <v>129</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>552</v>
+        <v>974</v>
       </c>
       <c r="J71" s="0">
         <v>1099.6836000000001</v>
@@ -5087,7 +6293,7 @@
         <v>130</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>553</v>
+        <v>975</v>
       </c>
       <c r="J72" s="0">
         <v>752.58019999999999</v>
@@ -5119,7 +6325,7 @@
         <v>131</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>554</v>
+        <v>976</v>
       </c>
       <c r="J73" s="0">
         <v>487.68040000000002</v>
@@ -5151,7 +6357,7 @@
         <v>132</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>555</v>
+        <v>977</v>
       </c>
       <c r="J74" s="0">
         <v>463.46300000000002</v>
@@ -5183,7 +6389,7 @@
         <v>133</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>556</v>
+        <v>978</v>
       </c>
       <c r="J75" s="0">
         <v>442.20010000000002</v>
@@ -5215,7 +6421,7 @@
         <v>134</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>557</v>
+        <v>979</v>
       </c>
       <c r="J76" s="0">
         <v>426.24950000000001</v>
@@ -5247,7 +6453,7 @@
         <v>135</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>558</v>
+        <v>980</v>
       </c>
       <c r="J77" s="0">
         <v>392.93150000000003</v>
@@ -5279,7 +6485,7 @@
         <v>136</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>559</v>
+        <v>981</v>
       </c>
       <c r="J78" s="0">
         <v>377.69189999999998</v>
@@ -5311,7 +6517,7 @@
         <v>137</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>560</v>
+        <v>982</v>
       </c>
       <c r="J79" s="0">
         <v>372.46730000000002</v>
@@ -5343,7 +6549,7 @@
         <v>138</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>561</v>
+        <v>983</v>
       </c>
       <c r="J80" s="0">
         <v>367.9117</v>
@@ -5375,7 +6581,7 @@
         <v>139</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>562</v>
+        <v>984</v>
       </c>
       <c r="J81" s="0">
         <v>9907.2489999999998</v>
@@ -5407,7 +6613,7 @@
         <v>140</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>563</v>
+        <v>985</v>
       </c>
       <c r="J82" s="0">
         <v>9652.7158</v>
@@ -5439,7 +6645,7 @@
         <v>141</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>564</v>
+        <v>986</v>
       </c>
       <c r="J83" s="0">
         <v>1441.7384999999999</v>
@@ -5471,7 +6677,7 @@
         <v>142</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>565</v>
+        <v>987</v>
       </c>
       <c r="J84" s="0">
         <v>1225.0391</v>
@@ -5503,7 +6709,7 @@
         <v>143</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>566</v>
+        <v>988</v>
       </c>
       <c r="J85" s="0">
         <v>535.24869999999999</v>
@@ -5535,7 +6741,7 @@
         <v>144</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>567</v>
+        <v>989</v>
       </c>
       <c r="J86" s="0">
         <v>505.87869999999998</v>
@@ -5567,7 +6773,7 @@
         <v>145</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>568</v>
+        <v>990</v>
       </c>
       <c r="J87" s="0">
         <v>499.1123</v>
@@ -5599,7 +6805,7 @@
         <v>146</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>569</v>
+        <v>991</v>
       </c>
       <c r="J88" s="0">
         <v>454.46269999999998</v>
@@ -5631,7 +6837,7 @@
         <v>147</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>570</v>
+        <v>992</v>
       </c>
       <c r="J89" s="0">
         <v>452.58749999999998</v>
@@ -5663,7 +6869,7 @@
         <v>148</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>571</v>
+        <v>993</v>
       </c>
       <c r="J90" s="0">
         <v>434.6585</v>
@@ -5695,7 +6901,7 @@
         <v>149</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>572</v>
+        <v>994</v>
       </c>
       <c r="J91" s="0">
         <v>401.7577</v>
@@ -5727,7 +6933,7 @@
         <v>150</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>573</v>
+        <v>995</v>
       </c>
       <c r="J92" s="0">
         <v>395.96719999999999</v>
@@ -5759,7 +6965,7 @@
         <v>151</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>574</v>
+        <v>996</v>
       </c>
       <c r="J93" s="0">
         <v>13039.6055</v>
@@ -5791,7 +6997,7 @@
         <v>152</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>575</v>
+        <v>997</v>
       </c>
       <c r="J94" s="0">
         <v>6975.5502999999999</v>
@@ -5823,7 +7029,7 @@
         <v>153</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>576</v>
+        <v>998</v>
       </c>
       <c r="J95" s="0">
         <v>1471.2853</v>
@@ -5855,7 +7061,7 @@
         <v>154</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>577</v>
+        <v>999</v>
       </c>
       <c r="J96" s="0">
         <v>1120.2394999999999</v>
@@ -5887,7 +7093,7 @@
         <v>155</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>578</v>
+        <v>1000</v>
       </c>
       <c r="J97" s="0">
         <v>525.06529999999998</v>
@@ -5919,7 +7125,7 @@
         <v>156</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>579</v>
+        <v>1001</v>
       </c>
       <c r="J98" s="0">
         <v>511.11419999999998</v>
@@ -5951,7 +7157,7 @@
         <v>157</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>580</v>
+        <v>1002</v>
       </c>
       <c r="J99" s="0">
         <v>488.54860000000002</v>
@@ -5983,7 +7189,7 @@
         <v>158</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>581</v>
+        <v>1003</v>
       </c>
       <c r="J100" s="0">
         <v>456.88260000000002</v>
@@ -6015,7 +7221,7 @@
         <v>159</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>582</v>
+        <v>1004</v>
       </c>
       <c r="J101" s="0">
         <v>454.80709999999999</v>
@@ -6047,7 +7253,7 @@
         <v>160</v>
       </c>
       <c r="I102" s="0" t="s">
-        <v>583</v>
+        <v>1005</v>
       </c>
       <c r="J102" s="0">
         <v>440.73829999999998</v>
@@ -6079,7 +7285,7 @@
         <v>161</v>
       </c>
       <c r="I103" s="0" t="s">
-        <v>584</v>
+        <v>1006</v>
       </c>
       <c r="J103" s="0">
         <v>390.3793</v>
@@ -6111,7 +7317,7 @@
         <v>162</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>585</v>
+        <v>1007</v>
       </c>
       <c r="J104" s="0">
         <v>366.7876</v>
@@ -6143,7 +7349,7 @@
         <v>163</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>586</v>
+        <v>1008</v>
       </c>
       <c r="J105" s="0">
         <v>13740.0527</v>
@@ -6175,7 +7381,7 @@
         <v>164</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>587</v>
+        <v>1009</v>
       </c>
       <c r="J106" s="0">
         <v>9744.2099999999991</v>
@@ -6207,7 +7413,7 @@
         <v>167</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>590</v>
+        <v>1010</v>
       </c>
       <c r="J107" s="0">
         <v>543.12710000000004</v>
@@ -6239,7 +7445,7 @@
         <v>168</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>591</v>
+        <v>1011</v>
       </c>
       <c r="J108" s="0">
         <v>530.70270000000005</v>
@@ -6271,7 +7477,7 @@
         <v>169</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>592</v>
+        <v>1012</v>
       </c>
       <c r="J109" s="0">
         <v>482.14240000000001</v>
@@ -6303,7 +7509,7 @@
         <v>170</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>593</v>
+        <v>1013</v>
       </c>
       <c r="J110" s="0">
         <v>462.08449999999999</v>
@@ -6335,7 +7541,7 @@
         <v>171</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>594</v>
+        <v>1014</v>
       </c>
       <c r="J111" s="0">
         <v>457.30529999999999</v>
@@ -6367,7 +7573,7 @@
         <v>172</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>595</v>
+        <v>1015</v>
       </c>
       <c r="J112" s="0">
         <v>450.53769999999997</v>
@@ -6399,7 +7605,7 @@
         <v>173</v>
       </c>
       <c r="I113" s="0" t="s">
-        <v>596</v>
+        <v>1016</v>
       </c>
       <c r="J113" s="0">
         <v>416.66809999999998</v>
@@ -6431,7 +7637,7 @@
         <v>174</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>597</v>
+        <v>1017</v>
       </c>
       <c r="J114" s="0">
         <v>381.01350000000002</v>
@@ -6463,7 +7669,7 @@
         <v>179</v>
       </c>
       <c r="I115" s="0" t="s">
-        <v>602</v>
+        <v>1018</v>
       </c>
       <c r="J115" s="0">
         <v>606.53700000000003</v>
@@ -6495,7 +7701,7 @@
         <v>180</v>
       </c>
       <c r="I116" s="0" t="s">
-        <v>603</v>
+        <v>1019</v>
       </c>
       <c r="J116" s="0">
         <v>479.4468</v>
@@ -6527,7 +7733,7 @@
         <v>181</v>
       </c>
       <c r="I117" s="0" t="s">
-        <v>604</v>
+        <v>1020</v>
       </c>
       <c r="J117" s="0">
         <v>479.09190000000001</v>
@@ -6559,7 +7765,7 @@
         <v>182</v>
       </c>
       <c r="I118" s="0" t="s">
-        <v>605</v>
+        <v>1021</v>
       </c>
       <c r="J118" s="0">
         <v>441.61619999999999</v>
@@ -6591,7 +7797,7 @@
         <v>183</v>
       </c>
       <c r="I119" s="0" t="s">
-        <v>606</v>
+        <v>1022</v>
       </c>
       <c r="J119" s="0">
         <v>417.55779999999999</v>
@@ -6623,7 +7829,7 @@
         <v>184</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>607</v>
+        <v>1023</v>
       </c>
       <c r="J120" s="0">
         <v>380.84750000000003</v>
@@ -6655,7 +7861,7 @@
         <v>185</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>608</v>
+        <v>1024</v>
       </c>
       <c r="J121" s="0">
         <v>380.4452</v>
@@ -6687,7 +7893,7 @@
         <v>186</v>
       </c>
       <c r="I122" s="0" t="s">
-        <v>609</v>
+        <v>1025</v>
       </c>
       <c r="J122" s="0">
         <v>338.78429999999997</v>
@@ -6719,7 +7925,7 @@
         <v>187</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>610</v>
+        <v>1026</v>
       </c>
       <c r="J123" s="0">
         <v>11531.805700000001</v>
@@ -6751,7 +7957,7 @@
         <v>188</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>611</v>
+        <v>1027</v>
       </c>
       <c r="J124" s="0">
         <v>6375.0625</v>
@@ -6783,7 +7989,7 @@
         <v>105</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>612</v>
+        <v>1028</v>
       </c>
       <c r="J125" s="0">
         <v>1293.2311</v>
@@ -6815,7 +8021,7 @@
         <v>106</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>613</v>
+        <v>1029</v>
       </c>
       <c r="J126" s="0">
         <v>1168.5597</v>
@@ -6847,7 +8053,7 @@
         <v>144</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>614</v>
+        <v>1030</v>
       </c>
       <c r="J127" s="0">
         <v>505.87869999999998</v>
@@ -6879,7 +8085,7 @@
         <v>189</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>615</v>
+        <v>1031</v>
       </c>
       <c r="J128" s="0">
         <v>480.84039999999999</v>
@@ -6911,7 +8117,7 @@
         <v>190</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>616</v>
+        <v>1032</v>
       </c>
       <c r="J129" s="0">
         <v>474.62130000000002</v>
@@ -6943,7 +8149,7 @@
         <v>191</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>617</v>
+        <v>1033</v>
       </c>
       <c r="J130" s="0">
         <v>462.91030000000001</v>
@@ -6975,7 +8181,7 @@
         <v>192</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>618</v>
+        <v>1034</v>
       </c>
       <c r="J131" s="0">
         <v>435.94409999999999</v>
@@ -7007,7 +8213,7 @@
         <v>193</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>619</v>
+        <v>1035</v>
       </c>
       <c r="J132" s="0">
         <v>419.98750000000001</v>
@@ -7039,7 +8245,7 @@
         <v>194</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>620</v>
+        <v>1036</v>
       </c>
       <c r="J133" s="0">
         <v>401.06349999999998</v>
@@ -7071,7 +8277,7 @@
         <v>195</v>
       </c>
       <c r="I134" s="0" t="s">
-        <v>621</v>
+        <v>1037</v>
       </c>
       <c r="J134" s="0">
         <v>400.24349999999998</v>
@@ -7103,7 +8309,7 @@
         <v>196</v>
       </c>
       <c r="I135" s="0" t="s">
-        <v>622</v>
+        <v>1038</v>
       </c>
       <c r="J135" s="0">
         <v>10941.195299999999</v>
@@ -7135,7 +8341,7 @@
         <v>197</v>
       </c>
       <c r="I136" s="0" t="s">
-        <v>623</v>
+        <v>1039</v>
       </c>
       <c r="J136" s="0">
         <v>7539.1181999999999</v>
@@ -7167,7 +8373,7 @@
         <v>198</v>
       </c>
       <c r="I137" s="0" t="s">
-        <v>624</v>
+        <v>1040</v>
       </c>
       <c r="J137" s="0">
         <v>1460.5899999999999</v>
@@ -7199,7 +8405,7 @@
         <v>199</v>
       </c>
       <c r="I138" s="0" t="s">
-        <v>625</v>
+        <v>1041</v>
       </c>
       <c r="J138" s="0">
         <v>1390.1700000000001</v>
@@ -7231,7 +8437,7 @@
         <v>200</v>
       </c>
       <c r="I139" s="0" t="s">
-        <v>626</v>
+        <v>1042</v>
       </c>
       <c r="J139" s="0">
         <v>1191.2892999999999</v>
@@ -7263,7 +8469,7 @@
         <v>201</v>
       </c>
       <c r="I140" s="0" t="s">
-        <v>627</v>
+        <v>1043</v>
       </c>
       <c r="J140" s="0">
         <v>905.0009</v>
@@ -7295,7 +8501,7 @@
         <v>202</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>628</v>
+        <v>1044</v>
       </c>
       <c r="J141" s="0">
         <v>509.07279999999997</v>
@@ -7327,7 +8533,7 @@
         <v>203</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>629</v>
+        <v>1045</v>
       </c>
       <c r="J142" s="0">
         <v>509.06999999999999</v>
@@ -7359,7 +8565,7 @@
         <v>204</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>630</v>
+        <v>1046</v>
       </c>
       <c r="J143" s="0">
         <v>467.17430000000002</v>
@@ -7391,7 +8597,7 @@
         <v>205</v>
       </c>
       <c r="I144" s="0" t="s">
-        <v>631</v>
+        <v>1047</v>
       </c>
       <c r="J144" s="0">
         <v>467.17000000000002</v>
@@ -7423,7 +8629,7 @@
         <v>206</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>632</v>
+        <v>1048</v>
       </c>
       <c r="J145" s="0">
         <v>461.41000000000003</v>
@@ -7455,7 +8661,7 @@
         <v>207</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>633</v>
+        <v>1049</v>
       </c>
       <c r="J146" s="0">
         <v>461.40780000000001</v>
@@ -7487,7 +8693,7 @@
         <v>208</v>
       </c>
       <c r="I147" s="0" t="s">
-        <v>634</v>
+        <v>1050</v>
       </c>
       <c r="J147" s="0">
         <v>426.55000000000001</v>
@@ -7519,7 +8725,7 @@
         <v>209</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>635</v>
+        <v>1051</v>
       </c>
       <c r="J148" s="0">
         <v>426.54820000000001</v>
@@ -7551,7 +8757,7 @@
         <v>210</v>
       </c>
       <c r="I149" s="0" t="s">
-        <v>636</v>
+        <v>1052</v>
       </c>
       <c r="J149" s="0">
         <v>390.12</v>
@@ -7583,7 +8789,7 @@
         <v>211</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>637</v>
+        <v>1053</v>
       </c>
       <c r="J150" s="0">
         <v>390.1198</v>
@@ -7615,7 +8821,7 @@
         <v>212</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>638</v>
+        <v>1054</v>
       </c>
       <c r="J151" s="0">
         <v>386.36000000000001</v>
@@ -7647,7 +8853,7 @@
         <v>213</v>
       </c>
       <c r="I152" s="0" t="s">
-        <v>639</v>
+        <v>1055</v>
       </c>
       <c r="J152" s="0">
         <v>386.35520000000002</v>
@@ -7679,7 +8885,7 @@
         <v>214</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>640</v>
+        <v>1056</v>
       </c>
       <c r="J153" s="0">
         <v>359.35480000000001</v>
@@ -7711,7 +8917,7 @@
         <v>215</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>641</v>
+        <v>1057</v>
       </c>
       <c r="J154" s="0">
         <v>359.35000000000002</v>
@@ -7743,7 +8949,7 @@
         <v>216</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>642</v>
+        <v>1058</v>
       </c>
       <c r="J155" s="0">
         <v>4.8700000000000001</v>
@@ -7775,7 +8981,7 @@
         <v>218</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>644</v>
+        <v>1059</v>
       </c>
       <c r="J156" s="0">
         <v>12758.521500000001</v>
@@ -7807,7 +9013,7 @@
         <v>220</v>
       </c>
       <c r="I157" s="0" t="s">
-        <v>646</v>
+        <v>1060</v>
       </c>
       <c r="J157" s="0">
         <v>1518.05</v>
@@ -7839,7 +9045,7 @@
         <v>221</v>
       </c>
       <c r="I158" s="0" t="s">
-        <v>647</v>
+        <v>1061</v>
       </c>
       <c r="J158" s="0">
         <v>1483.55</v>
@@ -7871,7 +9077,7 @@
         <v>224</v>
       </c>
       <c r="I159" s="0" t="s">
-        <v>650</v>
+        <v>1062</v>
       </c>
       <c r="J159" s="0">
         <v>508.62</v>
@@ -7903,7 +9109,7 @@
         <v>225</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>651</v>
+        <v>1063</v>
       </c>
       <c r="J160" s="0">
         <v>508.61829999999998</v>
@@ -7935,7 +9141,7 @@
         <v>226</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>652</v>
+        <v>1064</v>
       </c>
       <c r="J161" s="0">
         <v>468.33999999999998</v>
@@ -7967,7 +9173,7 @@
         <v>227</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>653</v>
+        <v>1065</v>
       </c>
       <c r="J162" s="0">
         <v>468.33859999999999</v>
@@ -7999,7 +9205,7 @@
         <v>228</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>654</v>
+        <v>1066</v>
       </c>
       <c r="J163" s="0">
         <v>441.58999999999998</v>
@@ -8031,7 +9237,7 @@
         <v>229</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>655</v>
+        <v>1067</v>
       </c>
       <c r="J164" s="0">
         <v>441.58780000000002</v>
@@ -8063,7 +9269,7 @@
         <v>230</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>656</v>
+        <v>1068</v>
       </c>
       <c r="J165" s="0">
         <v>417.62110000000001</v>
@@ -8095,7 +9301,7 @@
         <v>231</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>657</v>
+        <v>1069</v>
       </c>
       <c r="J166" s="0">
         <v>417.62</v>
@@ -8127,7 +9333,7 @@
         <v>232</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>658</v>
+        <v>1070</v>
       </c>
       <c r="J167" s="0">
         <v>407.61059999999998</v>
@@ -8159,7 +9365,7 @@
         <v>233</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>659</v>
+        <v>1071</v>
       </c>
       <c r="J168" s="0">
         <v>407.61000000000001</v>
@@ -8191,7 +9397,7 @@
         <v>234</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>660</v>
+        <v>1072</v>
       </c>
       <c r="J169" s="0">
         <v>392.51999999999998</v>
@@ -8223,7 +9429,7 @@
         <v>235</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>661</v>
+        <v>1073</v>
       </c>
       <c r="J170" s="0">
         <v>392.51850000000002</v>
@@ -8255,7 +9461,7 @@
         <v>236</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>662</v>
+        <v>1074</v>
       </c>
       <c r="J171" s="0">
         <v>382.75999999999999</v>
@@ -8287,7 +9493,7 @@
         <v>237</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>663</v>
+        <v>1075</v>
       </c>
       <c r="J172" s="0">
         <v>382.75760000000002</v>
@@ -8319,7 +9525,7 @@
         <v>238</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>664</v>
+        <v>1076</v>
       </c>
       <c r="J173" s="0">
         <v>323.20999999999998</v>
@@ -8351,7 +9557,7 @@
         <v>239</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>665</v>
+        <v>1077</v>
       </c>
       <c r="J174" s="0">
         <v>323.20670000000001</v>
@@ -8383,7 +9589,7 @@
         <v>240</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>666</v>
+        <v>1078</v>
       </c>
       <c r="J175" s="0">
         <v>10995.9912</v>
@@ -8415,7 +9621,7 @@
         <v>241</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>667</v>
+        <v>1079</v>
       </c>
       <c r="J176" s="0">
         <v>7215.2777999999999</v>
@@ -8447,7 +9653,7 @@
         <v>242</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>668</v>
+        <v>1080</v>
       </c>
       <c r="J177" s="0">
         <v>1710.03</v>
@@ -8479,7 +9685,7 @@
         <v>243</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>669</v>
+        <v>1081</v>
       </c>
       <c r="J178" s="0">
         <v>1001.1900000000001</v>
@@ -8511,7 +9717,7 @@
         <v>244</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>670</v>
+        <v>1082</v>
       </c>
       <c r="J179" s="0">
         <v>1188.2415000000001</v>
@@ -8543,7 +9749,7 @@
         <v>246</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>672</v>
+        <v>1083</v>
       </c>
       <c r="J180" s="0">
         <v>426.52229999999997</v>
@@ -8575,7 +9781,7 @@
         <v>247</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>673</v>
+        <v>1084</v>
       </c>
       <c r="J181" s="0">
         <v>426.51999999999998</v>
@@ -8607,7 +9813,7 @@
         <v>248</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>674</v>
+        <v>1085</v>
       </c>
       <c r="J182" s="0">
         <v>390.1635</v>
@@ -8639,7 +9845,7 @@
         <v>249</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>675</v>
+        <v>1086</v>
       </c>
       <c r="J183" s="0">
         <v>390.16000000000003</v>
@@ -8671,7 +9877,7 @@
         <v>250</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>676</v>
+        <v>1087</v>
       </c>
       <c r="J184" s="0">
         <v>385.91000000000003</v>
@@ -8703,7 +9909,7 @@
         <v>251</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>677</v>
+        <v>1088</v>
       </c>
       <c r="J185" s="0">
         <v>385.90809999999999</v>
@@ -8735,7 +9941,7 @@
         <v>252</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>678</v>
+        <v>1089</v>
       </c>
       <c r="J186" s="0">
         <v>269.38150000000002</v>
@@ -8767,7 +9973,7 @@
         <v>253</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>679</v>
+        <v>1090</v>
       </c>
       <c r="J187" s="0">
         <v>269.38</v>
@@ -8799,7 +10005,7 @@
         <v>254</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>680</v>
+        <v>1091</v>
       </c>
       <c r="J188" s="0">
         <v>248.60079999999999</v>
@@ -8831,7 +10037,7 @@
         <v>255</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>681</v>
+        <v>1092</v>
       </c>
       <c r="J189" s="0">
         <v>248.6</v>
@@ -8863,7 +10069,7 @@
         <v>256</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>682</v>
+        <v>1093</v>
       </c>
       <c r="J190" s="0">
         <v>224.50450000000001</v>
@@ -8895,7 +10101,7 @@
         <v>257</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>683</v>
+        <v>1094</v>
       </c>
       <c r="J191" s="0">
         <v>224.5</v>
@@ -8927,7 +10133,7 @@
         <v>258</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>684</v>
+        <v>1095</v>
       </c>
       <c r="J192" s="0">
         <v>192.28460000000001</v>
@@ -8959,7 +10165,7 @@
         <v>259</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>685</v>
+        <v>1096</v>
       </c>
       <c r="J193" s="0">
         <v>192.28</v>
@@ -8991,7 +10197,7 @@
         <v>260</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>686</v>
+        <v>1097</v>
       </c>
       <c r="J194" s="0">
         <v>152.80000000000001</v>
@@ -9023,7 +10229,7 @@
         <v>261</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>687</v>
+        <v>1098</v>
       </c>
       <c r="J195" s="0">
         <v>152.7972</v>
@@ -9055,7 +10261,7 @@
         <v>262</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>688</v>
+        <v>1099</v>
       </c>
       <c r="J196" s="0">
         <v>11254.794900000001</v>
@@ -9087,7 +10293,7 @@
         <v>263</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>689</v>
+        <v>1100</v>
       </c>
       <c r="J197" s="0">
         <v>8245.5498000000007</v>
@@ -9119,7 +10325,7 @@
         <v>264</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>690</v>
+        <v>1101</v>
       </c>
       <c r="J198" s="0">
         <v>1104.5668000000001</v>
@@ -9151,7 +10357,7 @@
         <v>265</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>691</v>
+        <v>1102</v>
       </c>
       <c r="J199" s="0">
         <v>667.55740000000003</v>
@@ -9183,7 +10389,7 @@
         <v>266</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>692</v>
+        <v>1103</v>
       </c>
       <c r="J200" s="0">
         <v>476.60090000000002</v>
@@ -9215,7 +10421,7 @@
         <v>267</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>693</v>
+        <v>1104</v>
       </c>
       <c r="J201" s="0">
         <v>449.04090000000002</v>
@@ -9247,7 +10453,7 @@
         <v>268</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>694</v>
+        <v>1105</v>
       </c>
       <c r="J202" s="0">
         <v>442.10520000000002</v>
@@ -9279,7 +10485,7 @@
         <v>269</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>695</v>
+        <v>1106</v>
       </c>
       <c r="J203" s="0">
         <v>409.70580000000001</v>
@@ -9311,7 +10517,7 @@
         <v>270</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>696</v>
+        <v>1107</v>
       </c>
       <c r="J204" s="0">
         <v>397.46850000000001</v>
@@ -9343,7 +10549,7 @@
         <v>271</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>697</v>
+        <v>1108</v>
       </c>
       <c r="J205" s="0">
         <v>383.6352</v>
@@ -9375,7 +10581,7 @@
         <v>272</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>698</v>
+        <v>1109</v>
       </c>
       <c r="J206" s="0">
         <v>381.00670000000002</v>
@@ -9407,7 +10613,7 @@
         <v>273</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>699</v>
+        <v>1110</v>
       </c>
       <c r="J207" s="0">
         <v>353.37259999999998</v>
@@ -9439,7 +10645,7 @@
         <v>274</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>700</v>
+        <v>1111</v>
       </c>
       <c r="J208" s="0">
         <v>14310.114299999999</v>
@@ -9471,7 +10677,7 @@
         <v>275</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>701</v>
+        <v>1112</v>
       </c>
       <c r="J209" s="0">
         <v>8465.1962999999996</v>
@@ -9503,7 +10709,7 @@
         <v>276</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>702</v>
+        <v>1113</v>
       </c>
       <c r="J210" s="0">
         <v>1220.287</v>
@@ -9535,7 +10741,7 @@
         <v>277</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>703</v>
+        <v>1114</v>
       </c>
       <c r="J211" s="0">
         <v>599.00360000000001</v>
@@ -9567,7 +10773,7 @@
         <v>278</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>704</v>
+        <v>1115</v>
       </c>
       <c r="J212" s="0">
         <v>555.67830000000004</v>
@@ -9599,7 +10805,7 @@
         <v>279</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>705</v>
+        <v>1116</v>
       </c>
       <c r="J213" s="0">
         <v>491.62889999999999</v>
@@ -9631,7 +10837,7 @@
         <v>280</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>706</v>
+        <v>1117</v>
       </c>
       <c r="J214" s="0">
         <v>487.06729999999999</v>
@@ -9663,7 +10869,7 @@
         <v>281</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>707</v>
+        <v>1118</v>
       </c>
       <c r="J215" s="0">
         <v>443.50709999999998</v>
@@ -9695,7 +10901,7 @@
         <v>282</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>708</v>
+        <v>1119</v>
       </c>
       <c r="J216" s="0">
         <v>437.17829999999998</v>
@@ -9727,7 +10933,7 @@
         <v>283</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>709</v>
+        <v>1120</v>
       </c>
       <c r="J217" s="0">
         <v>422.71879999999999</v>
@@ -9759,7 +10965,7 @@
         <v>284</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>710</v>
+        <v>1121</v>
       </c>
       <c r="J218" s="0">
         <v>405.00119999999998</v>
@@ -9791,7 +10997,7 @@
         <v>285</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>711</v>
+        <v>1122</v>
       </c>
       <c r="J219" s="0">
         <v>378.08580000000001</v>
@@ -9823,7 +11029,7 @@
         <v>286</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>712</v>
+        <v>1123</v>
       </c>
       <c r="J220" s="0">
         <v>10927.456099999999</v>
@@ -9855,7 +11061,7 @@
         <v>287</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>713</v>
+        <v>1124</v>
       </c>
       <c r="J221" s="0">
         <v>7092.1475</v>
@@ -9887,7 +11093,7 @@
         <v>288</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>714</v>
+        <v>1125</v>
       </c>
       <c r="J222" s="0">
         <v>1251.4889000000001</v>
@@ -9919,7 +11125,7 @@
         <v>290</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>716</v>
+        <v>1126</v>
       </c>
       <c r="J223" s="0">
         <v>573.87549999999999</v>
@@ -9951,7 +11157,7 @@
         <v>291</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>717</v>
+        <v>1127</v>
       </c>
       <c r="J224" s="0">
         <v>432.66559999999998</v>
@@ -9983,7 +11189,7 @@
         <v>292</v>
       </c>
       <c r="I225" s="0" t="s">
-        <v>718</v>
+        <v>1128</v>
       </c>
       <c r="J225" s="0">
         <v>429.50220000000002</v>
@@ -10015,7 +11221,7 @@
         <v>293</v>
       </c>
       <c r="I226" s="0" t="s">
-        <v>719</v>
+        <v>1129</v>
       </c>
       <c r="J226" s="0">
         <v>425.55560000000003</v>
@@ -10047,7 +11253,7 @@
         <v>294</v>
       </c>
       <c r="I227" s="0" t="s">
-        <v>720</v>
+        <v>1130</v>
       </c>
       <c r="J227" s="0">
         <v>412.95150000000001</v>
@@ -10079,7 +11285,7 @@
         <v>295</v>
       </c>
       <c r="I228" s="0" t="s">
-        <v>721</v>
+        <v>1131</v>
       </c>
       <c r="J228" s="0">
         <v>403.95030000000003</v>
@@ -10111,7 +11317,7 @@
         <v>296</v>
       </c>
       <c r="I229" s="0" t="s">
-        <v>722</v>
+        <v>1132</v>
       </c>
       <c r="J229" s="0">
         <v>366.0301</v>
@@ -10143,7 +11349,7 @@
         <v>297</v>
       </c>
       <c r="I230" s="0" t="s">
-        <v>723</v>
+        <v>1133</v>
       </c>
       <c r="J230" s="0">
         <v>322.23540000000003</v>
@@ -10175,7 +11381,7 @@
         <v>298</v>
       </c>
       <c r="I231" s="0" t="s">
-        <v>724</v>
+        <v>1134</v>
       </c>
       <c r="J231" s="0">
         <v>14707.393599999999</v>
@@ -10207,7 +11413,7 @@
         <v>299</v>
       </c>
       <c r="I232" s="0" t="s">
-        <v>725</v>
+        <v>1135</v>
       </c>
       <c r="J232" s="0">
         <v>6104.8818000000001</v>
@@ -10239,7 +11445,7 @@
         <v>300</v>
       </c>
       <c r="I233" s="0" t="s">
-        <v>726</v>
+        <v>1136</v>
       </c>
       <c r="J233" s="0">
         <v>882.45939999999996</v>
@@ -10271,7 +11477,7 @@
         <v>301</v>
       </c>
       <c r="I234" s="0" t="s">
-        <v>727</v>
+        <v>1137</v>
       </c>
       <c r="J234" s="0">
         <v>761.87369999999999</v>
@@ -10303,7 +11509,7 @@
         <v>302</v>
       </c>
       <c r="I235" s="0" t="s">
-        <v>728</v>
+        <v>1138</v>
       </c>
       <c r="J235" s="0">
         <v>521.54589999999996</v>
@@ -10335,7 +11541,7 @@
         <v>303</v>
       </c>
       <c r="I236" s="0" t="s">
-        <v>729</v>
+        <v>1139</v>
       </c>
       <c r="J236" s="0">
         <v>500.20800000000003</v>
@@ -10367,7 +11573,7 @@
         <v>304</v>
       </c>
       <c r="I237" s="0" t="s">
-        <v>730</v>
+        <v>1140</v>
       </c>
       <c r="J237" s="0">
         <v>462.5016</v>
@@ -10399,7 +11605,7 @@
         <v>305</v>
       </c>
       <c r="I238" s="0" t="s">
-        <v>731</v>
+        <v>1141</v>
       </c>
       <c r="J238" s="0">
         <v>460.94619999999998</v>
@@ -10431,7 +11637,7 @@
         <v>306</v>
       </c>
       <c r="I239" s="0" t="s">
-        <v>732</v>
+        <v>1142</v>
       </c>
       <c r="J239" s="0">
         <v>455.41989999999999</v>
@@ -10463,7 +11669,7 @@
         <v>307</v>
       </c>
       <c r="I240" s="0" t="s">
-        <v>733</v>
+        <v>1143</v>
       </c>
       <c r="J240" s="0">
         <v>429.3236</v>
@@ -10495,7 +11701,7 @@
         <v>308</v>
       </c>
       <c r="I241" s="0" t="s">
-        <v>734</v>
+        <v>1144</v>
       </c>
       <c r="J241" s="0">
         <v>399.94749999999999</v>
@@ -10527,7 +11733,7 @@
         <v>309</v>
       </c>
       <c r="I242" s="0" t="s">
-        <v>735</v>
+        <v>1145</v>
       </c>
       <c r="J242" s="0">
         <v>232.58420000000001</v>
@@ -10559,7 +11765,7 @@
         <v>310</v>
       </c>
       <c r="I243" s="0" t="s">
-        <v>736</v>
+        <v>1146</v>
       </c>
       <c r="J243" s="0">
         <v>11847.5967</v>
@@ -10591,7 +11797,7 @@
         <v>311</v>
       </c>
       <c r="I244" s="0" t="s">
-        <v>737</v>
+        <v>1147</v>
       </c>
       <c r="J244" s="0">
         <v>6282.4102000000003</v>
@@ -10623,7 +11829,7 @@
         <v>312</v>
       </c>
       <c r="I245" s="0" t="s">
-        <v>738</v>
+        <v>1148</v>
       </c>
       <c r="J245" s="0">
         <v>1301.1243999999999</v>
@@ -10655,7 +11861,7 @@
         <v>313</v>
       </c>
       <c r="I246" s="0" t="s">
-        <v>739</v>
+        <v>1149</v>
       </c>
       <c r="J246" s="0">
         <v>939.31240000000003</v>
@@ -10687,7 +11893,7 @@
         <v>314</v>
       </c>
       <c r="I247" s="0" t="s">
-        <v>740</v>
+        <v>1150</v>
       </c>
       <c r="J247" s="0">
         <v>482.02300000000002</v>
@@ -10719,7 +11925,7 @@
         <v>315</v>
       </c>
       <c r="I248" s="0" t="s">
-        <v>741</v>
+        <v>1151</v>
       </c>
       <c r="J248" s="0">
         <v>466.72879999999998</v>
@@ -10751,7 +11957,7 @@
         <v>192</v>
       </c>
       <c r="I249" s="0" t="s">
-        <v>742</v>
+        <v>1152</v>
       </c>
       <c r="J249" s="0">
         <v>435.94409999999999</v>
@@ -10783,7 +11989,7 @@
         <v>316</v>
       </c>
       <c r="I250" s="0" t="s">
-        <v>743</v>
+        <v>1153</v>
       </c>
       <c r="J250" s="0">
         <v>400.39690000000002</v>
@@ -10815,7 +12021,7 @@
         <v>317</v>
       </c>
       <c r="I251" s="0" t="s">
-        <v>744</v>
+        <v>1154</v>
       </c>
       <c r="J251" s="0">
         <v>400.39350000000002</v>
@@ -10847,7 +12053,7 @@
         <v>318</v>
       </c>
       <c r="I252" s="0" t="s">
-        <v>745</v>
+        <v>1155</v>
       </c>
       <c r="J252" s="0">
         <v>385.38260000000002</v>
@@ -10879,7 +12085,7 @@
         <v>319</v>
       </c>
       <c r="I253" s="0" t="s">
-        <v>746</v>
+        <v>1156</v>
       </c>
       <c r="J253" s="0">
         <v>347.70269999999999</v>
@@ -10911,7 +12117,7 @@
         <v>320</v>
       </c>
       <c r="I254" s="0" t="s">
-        <v>747</v>
+        <v>1157</v>
       </c>
       <c r="J254" s="0">
         <v>329.09859999999998</v>
@@ -10943,7 +12149,7 @@
         <v>321</v>
       </c>
       <c r="I255" s="0" t="s">
-        <v>748</v>
+        <v>1158</v>
       </c>
       <c r="J255" s="0">
         <v>12556.6572</v>
@@ -10975,7 +12181,7 @@
         <v>322</v>
       </c>
       <c r="I256" s="0" t="s">
-        <v>749</v>
+        <v>1159</v>
       </c>
       <c r="J256" s="0">
         <v>6296.4022999999998</v>
@@ -11007,7 +12213,7 @@
         <v>323</v>
       </c>
       <c r="I257" s="0" t="s">
-        <v>750</v>
+        <v>1160</v>
       </c>
       <c r="J257" s="0">
         <v>968.71990000000005</v>
@@ -11039,7 +12245,7 @@
         <v>324</v>
       </c>
       <c r="I258" s="0" t="s">
-        <v>751</v>
+        <v>1161</v>
       </c>
       <c r="J258" s="0">
         <v>883.06809999999996</v>
@@ -11071,7 +12277,7 @@
         <v>325</v>
       </c>
       <c r="I259" s="0" t="s">
-        <v>752</v>
+        <v>1162</v>
       </c>
       <c r="J259" s="0">
         <v>478.95100000000002</v>
@@ -11103,7 +12309,7 @@
         <v>326</v>
       </c>
       <c r="I260" s="0" t="s">
-        <v>753</v>
+        <v>1163</v>
       </c>
       <c r="J260" s="0">
         <v>465.39179999999999</v>
@@ -11135,7 +12341,7 @@
         <v>327</v>
       </c>
       <c r="I261" s="0" t="s">
-        <v>754</v>
+        <v>1164</v>
       </c>
       <c r="J261" s="0">
         <v>463.80270000000002</v>
@@ -11167,7 +12373,7 @@
         <v>328</v>
       </c>
       <c r="I262" s="0" t="s">
-        <v>755</v>
+        <v>1165</v>
       </c>
       <c r="J262" s="0">
         <v>462.91269999999997</v>
@@ -11199,7 +12405,7 @@
         <v>329</v>
       </c>
       <c r="I263" s="0" t="s">
-        <v>756</v>
+        <v>1166</v>
       </c>
       <c r="J263" s="0">
         <v>445.06830000000002</v>
@@ -11231,7 +12437,7 @@
         <v>330</v>
       </c>
       <c r="I264" s="0" t="s">
-        <v>757</v>
+        <v>1167</v>
       </c>
       <c r="J264" s="0">
         <v>423.10739999999999</v>
@@ -11263,7 +12469,7 @@
         <v>331</v>
       </c>
       <c r="I265" s="0" t="s">
-        <v>758</v>
+        <v>1168</v>
       </c>
       <c r="J265" s="0">
         <v>402.7998</v>
@@ -11295,7 +12501,7 @@
         <v>332</v>
       </c>
       <c r="I266" s="0" t="s">
-        <v>759</v>
+        <v>1169</v>
       </c>
       <c r="J266" s="0">
         <v>372.56169999999997</v>
@@ -11327,7 +12533,7 @@
         <v>333</v>
       </c>
       <c r="I267" s="0" t="s">
-        <v>760</v>
+        <v>1170</v>
       </c>
       <c r="J267" s="0">
         <v>10030.694299999999</v>
@@ -11359,7 +12565,7 @@
         <v>334</v>
       </c>
       <c r="I268" s="0" t="s">
-        <v>761</v>
+        <v>1171</v>
       </c>
       <c r="J268" s="0">
         <v>6168.2295000000004</v>
@@ -11391,7 +12597,7 @@
         <v>335</v>
       </c>
       <c r="I269" s="0" t="s">
-        <v>762</v>
+        <v>1172</v>
       </c>
       <c r="J269" s="0">
         <v>961.54250000000002</v>
@@ -11423,7 +12629,7 @@
         <v>336</v>
       </c>
       <c r="I270" s="0" t="s">
-        <v>763</v>
+        <v>1173</v>
       </c>
       <c r="J270" s="0">
         <v>564.7491</v>
@@ -11455,7 +12661,7 @@
         <v>337</v>
       </c>
       <c r="I271" s="0" t="s">
-        <v>764</v>
+        <v>1174</v>
       </c>
       <c r="J271" s="0">
         <v>502.06450000000001</v>
@@ -11487,7 +12693,7 @@
         <v>338</v>
       </c>
       <c r="I272" s="0" t="s">
-        <v>765</v>
+        <v>1175</v>
       </c>
       <c r="J272" s="0">
         <v>498.90269999999998</v>
@@ -11519,7 +12725,7 @@
         <v>339</v>
       </c>
       <c r="I273" s="0" t="s">
-        <v>766</v>
+        <v>1176</v>
       </c>
       <c r="J273" s="0">
         <v>399.30579999999998</v>
@@ -11551,7 +12757,7 @@
         <v>340</v>
       </c>
       <c r="I274" s="0" t="s">
-        <v>767</v>
+        <v>1177</v>
       </c>
       <c r="J274" s="0">
         <v>395.6617</v>
@@ -11583,7 +12789,7 @@
         <v>341</v>
       </c>
       <c r="I275" s="0" t="s">
-        <v>768</v>
+        <v>1178</v>
       </c>
       <c r="J275" s="0">
         <v>374.79230000000001</v>
@@ -11615,7 +12821,7 @@
         <v>342</v>
       </c>
       <c r="I276" s="0" t="s">
-        <v>769</v>
+        <v>1179</v>
       </c>
       <c r="J276" s="0">
         <v>317.00749999999999</v>
@@ -11647,7 +12853,7 @@
         <v>343</v>
       </c>
       <c r="I277" s="0" t="s">
-        <v>770</v>
+        <v>1180</v>
       </c>
       <c r="J277" s="0">
         <v>312.89389999999997</v>
@@ -11679,7 +12885,7 @@
         <v>344</v>
       </c>
       <c r="I278" s="0" t="s">
-        <v>771</v>
+        <v>1181</v>
       </c>
       <c r="J278" s="0">
         <v>262.27510000000001</v>
@@ -11711,7 +12917,7 @@
         <v>345</v>
       </c>
       <c r="I279" s="0" t="s">
-        <v>772</v>
+        <v>1182</v>
       </c>
       <c r="J279" s="0">
         <v>10326.7256</v>
@@ -11743,7 +12949,7 @@
         <v>346</v>
       </c>
       <c r="I280" s="0" t="s">
-        <v>773</v>
+        <v>1183</v>
       </c>
       <c r="J280" s="0">
         <v>9974.2188000000006</v>
@@ -11775,7 +12981,7 @@
         <v>347</v>
       </c>
       <c r="I281" s="0" t="s">
-        <v>774</v>
+        <v>1184</v>
       </c>
       <c r="J281" s="0">
         <v>1148.0337</v>
@@ -11807,7 +13013,7 @@
         <v>348</v>
       </c>
       <c r="I282" s="0" t="s">
-        <v>775</v>
+        <v>1185</v>
       </c>
       <c r="J282" s="0">
         <v>914.7056</v>
@@ -11839,7 +13045,7 @@
         <v>349</v>
       </c>
       <c r="I283" s="0" t="s">
-        <v>776</v>
+        <v>1186</v>
       </c>
       <c r="J283" s="0">
         <v>483.39670000000001</v>
@@ -11871,7 +13077,7 @@
         <v>350</v>
       </c>
       <c r="I284" s="0" t="s">
-        <v>777</v>
+        <v>1187</v>
       </c>
       <c r="J284" s="0">
         <v>480.69290000000001</v>
@@ -11903,7 +13109,7 @@
         <v>351</v>
       </c>
       <c r="I285" s="0" t="s">
-        <v>778</v>
+        <v>1188</v>
       </c>
       <c r="J285" s="0">
         <v>477.11810000000003</v>
@@ -11935,7 +13141,7 @@
         <v>352</v>
       </c>
       <c r="I286" s="0" t="s">
-        <v>779</v>
+        <v>1189</v>
       </c>
       <c r="J286" s="0">
         <v>470.54579999999999</v>
@@ -11967,7 +13173,7 @@
         <v>353</v>
       </c>
       <c r="I287" s="0" t="s">
-        <v>780</v>
+        <v>1190</v>
       </c>
       <c r="J287" s="0">
         <v>463.21350000000001</v>
@@ -11999,7 +13205,7 @@
         <v>354</v>
       </c>
       <c r="I288" s="0" t="s">
-        <v>781</v>
+        <v>1191</v>
       </c>
       <c r="J288" s="0">
         <v>458.6345</v>
@@ -12031,7 +13237,7 @@
         <v>355</v>
       </c>
       <c r="I289" s="0" t="s">
-        <v>782</v>
+        <v>1192</v>
       </c>
       <c r="J289" s="0">
         <v>399.29669999999999</v>
@@ -12063,7 +13269,7 @@
         <v>356</v>
       </c>
       <c r="I290" s="0" t="s">
-        <v>783</v>
+        <v>1193</v>
       </c>
       <c r="J290" s="0">
         <v>349.30439999999999</v>
@@ -12095,7 +13301,7 @@
         <v>357</v>
       </c>
       <c r="I291" s="0" t="s">
-        <v>784</v>
+        <v>1194</v>
       </c>
       <c r="J291" s="0">
         <v>11249.227500000001</v>
@@ -12127,7 +13333,7 @@
         <v>358</v>
       </c>
       <c r="I292" s="0" t="s">
-        <v>785</v>
+        <v>1195</v>
       </c>
       <c r="J292" s="0">
         <v>6804.9902000000002</v>
@@ -12159,7 +13365,7 @@
         <v>361</v>
       </c>
       <c r="I293" s="0" t="s">
-        <v>788</v>
+        <v>1196</v>
       </c>
       <c r="J293" s="0">
         <v>547.55139999999994</v>
@@ -12191,7 +13397,7 @@
         <v>362</v>
       </c>
       <c r="I294" s="0" t="s">
-        <v>789</v>
+        <v>1197</v>
       </c>
       <c r="J294" s="0">
         <v>544.9031</v>
@@ -12223,7 +13429,7 @@
         <v>363</v>
       </c>
       <c r="I295" s="0" t="s">
-        <v>790</v>
+        <v>1198</v>
       </c>
       <c r="J295" s="0">
         <v>538.0435</v>
@@ -12255,7 +13461,7 @@
         <v>364</v>
       </c>
       <c r="I296" s="0" t="s">
-        <v>791</v>
+        <v>1199</v>
       </c>
       <c r="J296" s="0">
         <v>529.52170000000001</v>
@@ -12287,7 +13493,7 @@
         <v>365</v>
       </c>
       <c r="I297" s="0" t="s">
-        <v>792</v>
+        <v>1200</v>
       </c>
       <c r="J297" s="0">
         <v>429.88639999999998</v>
@@ -12319,7 +13525,7 @@
         <v>366</v>
       </c>
       <c r="I298" s="0" t="s">
-        <v>793</v>
+        <v>1201</v>
       </c>
       <c r="J298" s="0">
         <v>423.78399999999999</v>
@@ -12351,7 +13557,7 @@
         <v>367</v>
       </c>
       <c r="I299" s="0" t="s">
-        <v>794</v>
+        <v>1202</v>
       </c>
       <c r="J299" s="0">
         <v>374.9067</v>
@@ -12383,7 +13589,7 @@
         <v>368</v>
       </c>
       <c r="I300" s="0" t="s">
-        <v>795</v>
+        <v>1203</v>
       </c>
       <c r="J300" s="0">
         <v>327.96339999999998</v>
@@ -12415,7 +13621,7 @@
         <v>369</v>
       </c>
       <c r="I301" s="0" t="s">
-        <v>796</v>
+        <v>1204</v>
       </c>
       <c r="J301" s="0">
         <v>14917.853499999999</v>
@@ -12447,7 +13653,7 @@
         <v>370</v>
       </c>
       <c r="I302" s="0" t="s">
-        <v>797</v>
+        <v>1205</v>
       </c>
       <c r="J302" s="0">
         <v>10013.698200000001</v>
@@ -12479,7 +13685,7 @@
         <v>371</v>
       </c>
       <c r="I303" s="0" t="s">
-        <v>798</v>
+        <v>1206</v>
       </c>
       <c r="J303" s="0">
         <v>1332.2670000000001</v>
@@ -12511,7 +13717,7 @@
         <v>372</v>
       </c>
       <c r="I304" s="0" t="s">
-        <v>799</v>
+        <v>1207</v>
       </c>
       <c r="J304" s="0">
         <v>828.53430000000003</v>
@@ -12543,7 +13749,7 @@
         <v>373</v>
       </c>
       <c r="I305" s="0" t="s">
-        <v>800</v>
+        <v>1208</v>
       </c>
       <c r="J305" s="0">
         <v>578.22249999999997</v>
@@ -12575,7 +13781,7 @@
         <v>374</v>
       </c>
       <c r="I306" s="0" t="s">
-        <v>801</v>
+        <v>1209</v>
       </c>
       <c r="J306" s="0">
         <v>519.49069999999995</v>
@@ -12607,7 +13813,7 @@
         <v>375</v>
       </c>
       <c r="I307" s="0" t="s">
-        <v>802</v>
+        <v>1210</v>
       </c>
       <c r="J307" s="0">
         <v>488.8802</v>
@@ -12639,7 +13845,7 @@
         <v>376</v>
       </c>
       <c r="I308" s="0" t="s">
-        <v>803</v>
+        <v>1211</v>
       </c>
       <c r="J308" s="0">
         <v>479.72430000000003</v>
@@ -12671,7 +13877,7 @@
         <v>377</v>
       </c>
       <c r="I309" s="0" t="s">
-        <v>804</v>
+        <v>1212</v>
       </c>
       <c r="J309" s="0">
         <v>471.13209999999998</v>
@@ -12703,7 +13909,7 @@
         <v>378</v>
       </c>
       <c r="I310" s="0" t="s">
-        <v>805</v>
+        <v>1213</v>
       </c>
       <c r="J310" s="0">
         <v>465.73070000000001</v>
@@ -12735,7 +13941,7 @@
         <v>379</v>
       </c>
       <c r="I311" s="0" t="s">
-        <v>806</v>
+        <v>1214</v>
       </c>
       <c r="J311" s="0">
         <v>414.24799999999999</v>
@@ -12767,7 +13973,7 @@
         <v>380</v>
       </c>
       <c r="I312" s="0" t="s">
-        <v>807</v>
+        <v>1215</v>
       </c>
       <c r="J312" s="0">
         <v>382.2792</v>
@@ -12799,7 +14005,7 @@
         <v>381</v>
       </c>
       <c r="I313" s="0" t="s">
-        <v>808</v>
+        <v>1216</v>
       </c>
       <c r="J313" s="0">
         <v>13171.9355</v>
@@ -12831,7 +14037,7 @@
         <v>382</v>
       </c>
       <c r="I314" s="0" t="s">
-        <v>809</v>
+        <v>1217</v>
       </c>
       <c r="J314" s="0">
         <v>7219.6553000000004</v>
@@ -12863,7 +14069,7 @@
         <v>383</v>
       </c>
       <c r="I315" s="0" t="s">
-        <v>810</v>
+        <v>1218</v>
       </c>
       <c r="J315" s="0">
         <v>858.04020000000003</v>
@@ -12895,7 +14101,7 @@
         <v>384</v>
       </c>
       <c r="I316" s="0" t="s">
-        <v>811</v>
+        <v>1219</v>
       </c>
       <c r="J316" s="0">
         <v>548.43979999999999</v>
@@ -12927,7 +14133,7 @@
         <v>385</v>
       </c>
       <c r="I317" s="0" t="s">
-        <v>812</v>
+        <v>1220</v>
       </c>
       <c r="J317" s="0">
         <v>525.69830000000002</v>
@@ -12959,7 +14165,7 @@
         <v>386</v>
       </c>
       <c r="I318" s="0" t="s">
-        <v>813</v>
+        <v>1221</v>
       </c>
       <c r="J318" s="0">
         <v>474.8716</v>
@@ -12991,7 +14197,7 @@
         <v>387</v>
       </c>
       <c r="I319" s="0" t="s">
-        <v>814</v>
+        <v>1222</v>
       </c>
       <c r="J319" s="0">
         <v>453.47840000000002</v>
@@ -13023,7 +14229,7 @@
         <v>388</v>
       </c>
       <c r="I320" s="0" t="s">
-        <v>815</v>
+        <v>1223</v>
       </c>
       <c r="J320" s="0">
         <v>439.9545</v>
@@ -13055,7 +14261,7 @@
         <v>389</v>
       </c>
       <c r="I321" s="0" t="s">
-        <v>816</v>
+        <v>1224</v>
       </c>
       <c r="J321" s="0">
         <v>432.7242</v>
@@ -13087,7 +14293,7 @@
         <v>390</v>
       </c>
       <c r="I322" s="0" t="s">
-        <v>817</v>
+        <v>1225</v>
       </c>
       <c r="J322" s="0">
         <v>427.84280000000001</v>
@@ -13119,7 +14325,7 @@
         <v>391</v>
       </c>
       <c r="I323" s="0" t="s">
-        <v>818</v>
+        <v>1226</v>
       </c>
       <c r="J323" s="0">
         <v>406.00720000000001</v>
@@ -13151,7 +14357,7 @@
         <v>392</v>
       </c>
       <c r="I324" s="0" t="s">
-        <v>819</v>
+        <v>1227</v>
       </c>
       <c r="J324" s="0">
         <v>368.30669999999998</v>
@@ -13183,7 +14389,7 @@
         <v>393</v>
       </c>
       <c r="I325" s="0" t="s">
-        <v>820</v>
+        <v>1228</v>
       </c>
       <c r="J325" s="0">
         <v>10183.9961</v>
@@ -13215,7 +14421,7 @@
         <v>394</v>
       </c>
       <c r="I326" s="0" t="s">
-        <v>821</v>
+        <v>1229</v>
       </c>
       <c r="J326" s="0">
         <v>9260.2188000000006</v>
@@ -13247,7 +14453,7 @@
         <v>395</v>
       </c>
       <c r="I327" s="0" t="s">
-        <v>822</v>
+        <v>1230</v>
       </c>
       <c r="J327" s="0">
         <v>1286.2859000000001</v>
@@ -13279,7 +14485,7 @@
         <v>396</v>
       </c>
       <c r="I328" s="0" t="s">
-        <v>823</v>
+        <v>1231</v>
       </c>
       <c r="J328" s="0">
         <v>1212.9492</v>
@@ -13311,7 +14517,7 @@
         <v>398</v>
       </c>
       <c r="I329" s="0" t="s">
-        <v>825</v>
+        <v>1232</v>
       </c>
       <c r="J329" s="0">
         <v>423.24180000000001</v>
@@ -13343,7 +14549,7 @@
         <v>399</v>
       </c>
       <c r="I330" s="0" t="s">
-        <v>826</v>
+        <v>1233</v>
       </c>
       <c r="J330" s="0">
         <v>408.47359999999998</v>
@@ -13375,7 +14581,7 @@
         <v>400</v>
       </c>
       <c r="I331" s="0" t="s">
-        <v>827</v>
+        <v>1234</v>
       </c>
       <c r="J331" s="0">
         <v>405.3897</v>
@@ -13407,7 +14613,7 @@
         <v>401</v>
       </c>
       <c r="I332" s="0" t="s">
-        <v>828</v>
+        <v>1235</v>
       </c>
       <c r="J332" s="0">
         <v>379.12220000000002</v>
@@ -13439,7 +14645,7 @@
         <v>402</v>
       </c>
       <c r="I333" s="0" t="s">
-        <v>829</v>
+        <v>1236</v>
       </c>
       <c r="J333" s="0">
         <v>371.36880000000002</v>
@@ -13471,7 +14677,7 @@
         <v>403</v>
       </c>
       <c r="I334" s="0" t="s">
-        <v>830</v>
+        <v>1237</v>
       </c>
       <c r="J334" s="0">
         <v>350.1583</v>
@@ -13503,7 +14709,7 @@
         <v>404</v>
       </c>
       <c r="I335" s="0" t="s">
-        <v>831</v>
+        <v>1238</v>
       </c>
       <c r="J335" s="0">
         <v>338.19600000000003</v>
@@ -13535,7 +14741,7 @@
         <v>405</v>
       </c>
       <c r="I336" s="0" t="s">
-        <v>832</v>
+        <v>1239</v>
       </c>
       <c r="J336" s="0">
         <v>10894.9053</v>
@@ -13567,7 +14773,7 @@
         <v>406</v>
       </c>
       <c r="I337" s="0" t="s">
-        <v>833</v>
+        <v>1240</v>
       </c>
       <c r="J337" s="0">
         <v>5662.0551999999998</v>
@@ -13599,7 +14805,7 @@
         <v>407</v>
       </c>
       <c r="I338" s="0" t="s">
-        <v>834</v>
+        <v>1241</v>
       </c>
       <c r="J338" s="0">
         <v>1945.5608</v>
@@ -13631,7 +14837,7 @@
         <v>408</v>
       </c>
       <c r="I339" s="0" t="s">
-        <v>835</v>
+        <v>1242</v>
       </c>
       <c r="J339" s="0">
         <v>1073.6666</v>
@@ -13663,7 +14869,7 @@
         <v>409</v>
       </c>
       <c r="I340" s="0" t="s">
-        <v>836</v>
+        <v>1243</v>
       </c>
       <c r="J340" s="0">
         <v>513.65530000000001</v>
@@ -13695,7 +14901,7 @@
         <v>410</v>
       </c>
       <c r="I341" s="0" t="s">
-        <v>837</v>
+        <v>1244</v>
       </c>
       <c r="J341" s="0">
         <v>457.6961</v>
@@ -13727,7 +14933,7 @@
         <v>411</v>
       </c>
       <c r="I342" s="0" t="s">
-        <v>838</v>
+        <v>1245</v>
       </c>
       <c r="J342" s="0">
         <v>456.3168</v>
@@ -13759,7 +14965,7 @@
         <v>412</v>
       </c>
       <c r="I343" s="0" t="s">
-        <v>839</v>
+        <v>1246</v>
       </c>
       <c r="J343" s="0">
         <v>454.07369999999997</v>
@@ -13791,7 +14997,7 @@
         <v>413</v>
       </c>
       <c r="I344" s="0" t="s">
-        <v>840</v>
+        <v>1247</v>
       </c>
       <c r="J344" s="0">
         <v>429.38220000000001</v>
@@ -13823,7 +15029,7 @@
         <v>414</v>
       </c>
       <c r="I345" s="0" t="s">
-        <v>841</v>
+        <v>1248</v>
       </c>
       <c r="J345" s="0">
         <v>386.53370000000001</v>
@@ -13855,7 +15061,7 @@
         <v>415</v>
       </c>
       <c r="I346" s="0" t="s">
-        <v>842</v>
+        <v>1249</v>
       </c>
       <c r="J346" s="0">
         <v>359.30450000000002</v>
@@ -13887,7 +15093,7 @@
         <v>416</v>
       </c>
       <c r="I347" s="0" t="s">
-        <v>843</v>
+        <v>1250</v>
       </c>
       <c r="J347" s="0">
         <v>330.99799999999999</v>
@@ -13919,7 +15125,7 @@
         <v>417</v>
       </c>
       <c r="I348" s="0" t="s">
-        <v>844</v>
+        <v>1251</v>
       </c>
       <c r="J348" s="0">
         <v>11140.4043</v>
@@ -13951,7 +15157,7 @@
         <v>418</v>
       </c>
       <c r="I349" s="0" t="s">
-        <v>845</v>
+        <v>1252</v>
       </c>
       <c r="J349" s="0">
         <v>7539.1777000000002</v>
@@ -13983,7 +15189,7 @@
         <v>419</v>
       </c>
       <c r="I350" s="0" t="s">
-        <v>846</v>
+        <v>1253</v>
       </c>
       <c r="J350" s="0">
         <v>1166.9911999999999</v>
@@ -14015,7 +15221,7 @@
         <v>420</v>
       </c>
       <c r="I351" s="0" t="s">
-        <v>847</v>
+        <v>1254</v>
       </c>
       <c r="J351" s="0">
         <v>968.274</v>
@@ -14047,7 +15253,7 @@
         <v>421</v>
       </c>
       <c r="I352" s="0" t="s">
-        <v>848</v>
+        <v>1255</v>
       </c>
       <c r="J352" s="0">
         <v>590.66909999999996</v>
@@ -14079,7 +15285,7 @@
         <v>422</v>
       </c>
       <c r="I353" s="0" t="s">
-        <v>849</v>
+        <v>1256</v>
       </c>
       <c r="J353" s="0">
         <v>502.17599999999999</v>
@@ -14111,7 +15317,7 @@
         <v>423</v>
       </c>
       <c r="I354" s="0" t="s">
-        <v>850</v>
+        <v>1257</v>
       </c>
       <c r="J354" s="0">
         <v>479.93529999999998</v>
@@ -14143,7 +15349,7 @@
         <v>424</v>
       </c>
       <c r="I355" s="0" t="s">
-        <v>851</v>
+        <v>1258</v>
       </c>
       <c r="J355" s="0">
         <v>469.60969999999998</v>
@@ -14175,7 +15381,7 @@
         <v>425</v>
       </c>
       <c r="I356" s="0" t="s">
-        <v>852</v>
+        <v>1259</v>
       </c>
       <c r="J356" s="0">
         <v>451.56819999999999</v>
@@ -14207,7 +15413,7 @@
         <v>426</v>
       </c>
       <c r="I357" s="0" t="s">
-        <v>853</v>
+        <v>1260</v>
       </c>
       <c r="J357" s="0">
         <v>412.2346</v>
@@ -14239,7 +15445,7 @@
         <v>427</v>
       </c>
       <c r="I358" s="0" t="s">
-        <v>854</v>
+        <v>1261</v>
       </c>
       <c r="J358" s="0">
         <v>401.46249999999998</v>
@@ -14271,7 +15477,7 @@
         <v>428</v>
       </c>
       <c r="I359" s="0" t="s">
-        <v>855</v>
+        <v>1262</v>
       </c>
       <c r="J359" s="0">
         <v>323.00450000000001</v>
@@ -14303,7 +15509,7 @@
         <v>429</v>
       </c>
       <c r="I360" s="0" t="s">
-        <v>856</v>
+        <v>1263</v>
       </c>
       <c r="J360" s="0">
         <v>11573.126</v>
@@ -14335,7 +15541,7 @@
         <v>430</v>
       </c>
       <c r="I361" s="0" t="s">
-        <v>857</v>
+        <v>1264</v>
       </c>
       <c r="J361" s="0">
         <v>6620.0068000000001</v>
@@ -14367,7 +15573,7 @@
         <v>431</v>
       </c>
       <c r="I362" s="0" t="s">
-        <v>858</v>
+        <v>1265</v>
       </c>
       <c r="J362" s="0">
         <v>751.08780000000002</v>
@@ -14399,7 +15605,7 @@
         <v>432</v>
       </c>
       <c r="I363" s="0" t="s">
-        <v>859</v>
+        <v>1266</v>
       </c>
       <c r="J363" s="0">
         <v>745.37040000000002</v>
@@ -14431,7 +15637,7 @@
         <v>433</v>
       </c>
       <c r="I364" s="0" t="s">
-        <v>860</v>
+        <v>1267</v>
       </c>
       <c r="J364" s="0">
         <v>347.99090000000001</v>
@@ -14463,7 +15669,7 @@
         <v>434</v>
       </c>
       <c r="I365" s="0" t="s">
-        <v>861</v>
+        <v>1268</v>
       </c>
       <c r="J365" s="0">
         <v>332.82709999999997</v>
@@ -14495,7 +15701,7 @@
         <v>435</v>
       </c>
       <c r="I366" s="0" t="s">
-        <v>862</v>
+        <v>1269</v>
       </c>
       <c r="J366" s="0">
         <v>300.09730000000002</v>
@@ -14527,7 +15733,7 @@
         <v>436</v>
       </c>
       <c r="I367" s="0" t="s">
-        <v>863</v>
+        <v>1270</v>
       </c>
       <c r="J367" s="0">
         <v>267.48480000000001</v>
@@ -14559,7 +15765,7 @@
         <v>437</v>
       </c>
       <c r="I368" s="0" t="s">
-        <v>864</v>
+        <v>1271</v>
       </c>
       <c r="J368" s="0">
         <v>247.57060000000001</v>
@@ -14591,7 +15797,7 @@
         <v>438</v>
       </c>
       <c r="I369" s="0" t="s">
-        <v>865</v>
+        <v>1272</v>
       </c>
       <c r="J369" s="0">
         <v>241.20079999999999</v>
@@ -14623,7 +15829,7 @@
         <v>439</v>
       </c>
       <c r="I370" s="0" t="s">
-        <v>866</v>
+        <v>1273</v>
       </c>
       <c r="J370" s="0">
         <v>224.6387</v>
@@ -14655,7 +15861,7 @@
         <v>440</v>
       </c>
       <c r="I371" s="0" t="s">
-        <v>867</v>
+        <v>1274</v>
       </c>
       <c r="J371" s="0">
         <v>196.59559999999999</v>
@@ -14687,7 +15893,7 @@
         <v>441</v>
       </c>
       <c r="I372" s="0" t="s">
-        <v>868</v>
+        <v>1275</v>
       </c>
       <c r="J372" s="0">
         <v>9005.0449000000008</v>
@@ -14719,7 +15925,7 @@
         <v>442</v>
       </c>
       <c r="I373" s="0" t="s">
-        <v>869</v>
+        <v>1276</v>
       </c>
       <c r="J373" s="0">
         <v>8991.1543000000001</v>
@@ -14751,7 +15957,7 @@
         <v>443</v>
       </c>
       <c r="I374" s="0" t="s">
-        <v>870</v>
+        <v>1277</v>
       </c>
       <c r="J374" s="0">
         <v>1060.6902</v>
@@ -14783,7 +15989,7 @@
         <v>444</v>
       </c>
       <c r="I375" s="0" t="s">
-        <v>871</v>
+        <v>1278</v>
       </c>
       <c r="J375" s="0">
         <v>873.68520000000001</v>
@@ -14815,7 +16021,7 @@
         <v>445</v>
       </c>
       <c r="I376" s="0" t="s">
-        <v>872</v>
+        <v>1279</v>
       </c>
       <c r="J376" s="0">
         <v>492.66989999999999</v>
@@ -14847,7 +16053,7 @@
         <v>446</v>
       </c>
       <c r="I377" s="0" t="s">
-        <v>873</v>
+        <v>1280</v>
       </c>
       <c r="J377" s="0">
         <v>479.0992</v>
@@ -14879,7 +16085,7 @@
         <v>447</v>
       </c>
       <c r="I378" s="0" t="s">
-        <v>874</v>
+        <v>1281</v>
       </c>
       <c r="J378" s="0">
         <v>473.75420000000003</v>
@@ -14911,7 +16117,7 @@
         <v>448</v>
       </c>
       <c r="I379" s="0" t="s">
-        <v>875</v>
+        <v>1282</v>
       </c>
       <c r="J379" s="0">
         <v>451.01459999999997</v>
@@ -14943,7 +16149,7 @@
         <v>449</v>
       </c>
       <c r="I380" s="0" t="s">
-        <v>876</v>
+        <v>1283</v>
       </c>
       <c r="J380" s="0">
         <v>445.8254</v>
@@ -14975,7 +16181,7 @@
         <v>450</v>
       </c>
       <c r="I381" s="0" t="s">
-        <v>877</v>
+        <v>1284</v>
       </c>
       <c r="J381" s="0">
         <v>416.5324</v>
@@ -15007,7 +16213,7 @@
         <v>451</v>
       </c>
       <c r="I382" s="0" t="s">
-        <v>878</v>
+        <v>1285</v>
       </c>
       <c r="J382" s="0">
         <v>410.74439999999999</v>
@@ -15039,7 +16245,7 @@
         <v>452</v>
       </c>
       <c r="I383" s="0" t="s">
-        <v>879</v>
+        <v>1286</v>
       </c>
       <c r="J383" s="0">
         <v>398.16070000000002</v>
@@ -15071,7 +16277,7 @@
         <v>453</v>
       </c>
       <c r="I384" s="0" t="s">
-        <v>880</v>
+        <v>1287</v>
       </c>
       <c r="J384" s="0">
         <v>11446.293</v>
@@ -15103,7 +16309,7 @@
         <v>454</v>
       </c>
       <c r="I385" s="0" t="s">
-        <v>881</v>
+        <v>1288</v>
       </c>
       <c r="J385" s="0">
         <v>7034.3638000000001</v>
@@ -15135,7 +16341,7 @@
         <v>457</v>
       </c>
       <c r="I386" s="0" t="s">
-        <v>884</v>
+        <v>1289</v>
       </c>
       <c r="J386" s="0">
         <v>544.20960000000002</v>
@@ -15167,7 +16373,7 @@
         <v>458</v>
       </c>
       <c r="I387" s="0" t="s">
-        <v>885</v>
+        <v>1290</v>
       </c>
       <c r="J387" s="0">
         <v>530.34780000000001</v>
@@ -15199,7 +16405,7 @@
         <v>459</v>
       </c>
       <c r="I388" s="0" t="s">
-        <v>886</v>
+        <v>1291</v>
       </c>
       <c r="J388" s="0">
         <v>496.8383</v>
@@ -15231,7 +16437,7 @@
         <v>460</v>
       </c>
       <c r="I389" s="0" t="s">
-        <v>887</v>
+        <v>1292</v>
       </c>
       <c r="J389" s="0">
         <v>456.82279999999997</v>
@@ -15263,7 +16469,7 @@
         <v>461</v>
       </c>
       <c r="I390" s="0" t="s">
-        <v>888</v>
+        <v>1293</v>
       </c>
       <c r="J390" s="0">
         <v>430.56229999999999</v>
@@ -15295,7 +16501,7 @@
         <v>462</v>
       </c>
       <c r="I391" s="0" t="s">
-        <v>889</v>
+        <v>1294</v>
       </c>
       <c r="J391" s="0">
         <v>394.98270000000002</v>
@@ -15327,7 +16533,7 @@
         <v>463</v>
       </c>
       <c r="I392" s="0" t="s">
-        <v>890</v>
+        <v>1295</v>
       </c>
       <c r="J392" s="0">
         <v>390.7165</v>
@@ -15359,7 +16565,7 @@
         <v>465</v>
       </c>
       <c r="I393" s="0" t="s">
-        <v>892</v>
+        <v>1296</v>
       </c>
       <c r="J393" s="0">
         <v>11910.3838</v>
@@ -15391,7 +16597,7 @@
         <v>466</v>
       </c>
       <c r="I394" s="0" t="s">
-        <v>893</v>
+        <v>1297</v>
       </c>
       <c r="J394" s="0">
         <v>7360.2744000000002</v>
@@ -15423,7 +16629,7 @@
         <v>467</v>
       </c>
       <c r="I395" s="0" t="s">
-        <v>894</v>
+        <v>1298</v>
       </c>
       <c r="J395" s="0">
         <v>712.87210000000005</v>
@@ -15455,7 +16661,7 @@
         <v>469</v>
       </c>
       <c r="I396" s="0" t="s">
-        <v>896</v>
+        <v>1299</v>
       </c>
       <c r="J396" s="0">
         <v>462.625</v>
@@ -15487,7 +16693,7 @@
         <v>470</v>
       </c>
       <c r="I397" s="0" t="s">
-        <v>897</v>
+        <v>1300</v>
       </c>
       <c r="J397" s="0">
         <v>430.88380000000001</v>
@@ -15519,7 +16725,7 @@
         <v>471</v>
       </c>
       <c r="I398" s="0" t="s">
-        <v>898</v>
+        <v>1301</v>
       </c>
       <c r="J398" s="0">
         <v>412.29090000000002</v>
@@ -15551,7 +16757,7 @@
         <v>472</v>
       </c>
       <c r="I399" s="0" t="s">
-        <v>899</v>
+        <v>1302</v>
       </c>
       <c r="J399" s="0">
         <v>401.78739999999999</v>
@@ -15583,7 +16789,7 @@
         <v>473</v>
       </c>
       <c r="I400" s="0" t="s">
-        <v>900</v>
+        <v>1303</v>
       </c>
       <c r="J400" s="0">
         <v>380.73540000000003</v>
@@ -15615,7 +16821,7 @@
         <v>474</v>
       </c>
       <c r="I401" s="0" t="s">
-        <v>901</v>
+        <v>1304</v>
       </c>
       <c r="J401" s="0">
         <v>309.23020000000002</v>
@@ -15647,7 +16853,7 @@
         <v>475</v>
       </c>
       <c r="I402" s="0" t="s">
-        <v>902</v>
+        <v>1305</v>
       </c>
       <c r="J402" s="0">
         <v>275.06909999999999</v>
@@ -15679,7 +16885,7 @@
         <v>476</v>
       </c>
       <c r="I403" s="0" t="s">
-        <v>903</v>
+        <v>1306</v>
       </c>
       <c r="J403" s="0">
         <v>206.4333</v>

--- a/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="93148" uniqueCount="1307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="223756" uniqueCount="1307">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="223756" uniqueCount="1307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="231012" uniqueCount="1307">
   <si>
     <t>Year</t>
   </si>
@@ -3983,16 +3983,16 @@
   <dimension ref="A1:J427"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" customWidth="true"/>
-    <col min="2" max="2" width="7" customWidth="true"/>
-    <col min="3" max="3" width="11.28515625" customWidth="true"/>
-    <col min="4" max="4" width="17.28515625" customWidth="true"/>
-    <col min="5" max="5" width="12.7109375" customWidth="true"/>
-    <col min="6" max="6" width="13" customWidth="true"/>
-    <col min="7" max="7" width="8.5703125" customWidth="true"/>
-    <col min="8" max="8" width="37.42578125" customWidth="true"/>
-    <col min="9" max="9" width="175.28515625" customWidth="true"/>
-    <col min="10" max="10" width="10.7109375" customWidth="true"/>
+    <col min="1" max="1" width="14.08984375" customWidth="true"/>
+    <col min="2" max="2" width="6.54296875" customWidth="true"/>
+    <col min="3" max="3" width="10.36328125" customWidth="true"/>
+    <col min="4" max="4" width="16.36328125" customWidth="true"/>
+    <col min="5" max="5" width="11.81640625" customWidth="true"/>
+    <col min="6" max="6" width="11.90625" customWidth="true"/>
+    <col min="7" max="7" width="7.90625" customWidth="true"/>
+    <col min="8" max="8" width="36.26953125" customWidth="true"/>
+    <col min="9" max="9" width="195.7265625" customWidth="true"/>
+    <col min="10" max="10" width="10.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4053,7 +4053,7 @@
         <v>55</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>905</v>
+        <v>478</v>
       </c>
       <c r="J2" s="0">
         <v>11688.002</v>
@@ -4085,7 +4085,7 @@
         <v>57</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>906</v>
+        <v>480</v>
       </c>
       <c r="J3" s="0">
         <v>935.94889999999998</v>
@@ -4117,7 +4117,7 @@
         <v>58</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>907</v>
+        <v>481</v>
       </c>
       <c r="J4" s="0">
         <v>880.38310000000001</v>
@@ -4149,7 +4149,7 @@
         <v>59</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>908</v>
+        <v>482</v>
       </c>
       <c r="J5" s="0">
         <v>502.106</v>
@@ -4181,7 +4181,7 @@
         <v>60</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>909</v>
+        <v>483</v>
       </c>
       <c r="J6" s="0">
         <v>466.17020000000002</v>
@@ -4213,7 +4213,7 @@
         <v>61</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>910</v>
+        <v>484</v>
       </c>
       <c r="J7" s="0">
         <v>453.3066</v>
@@ -4245,7 +4245,7 @@
         <v>62</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>911</v>
+        <v>485</v>
       </c>
       <c r="J8" s="0">
         <v>443.37130000000002</v>
@@ -4277,7 +4277,7 @@
         <v>63</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>912</v>
+        <v>486</v>
       </c>
       <c r="J9" s="0">
         <v>438.5403</v>
@@ -4309,7 +4309,7 @@
         <v>64</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>913</v>
+        <v>487</v>
       </c>
       <c r="J10" s="0">
         <v>427.42660000000001</v>
@@ -4341,7 +4341,7 @@
         <v>66</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>914</v>
+        <v>489</v>
       </c>
       <c r="J11" s="0">
         <v>359.1311</v>
@@ -4373,7 +4373,7 @@
         <v>67</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>915</v>
+        <v>490</v>
       </c>
       <c r="J12" s="0">
         <v>15177.4365</v>
@@ -4405,7 +4405,7 @@
         <v>68</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>916</v>
+        <v>491</v>
       </c>
       <c r="J13" s="0">
         <v>10441.9121</v>
@@ -4437,7 +4437,7 @@
         <v>69</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>917</v>
+        <v>492</v>
       </c>
       <c r="J14" s="0">
         <v>1168.5962</v>
@@ -4469,7 +4469,7 @@
         <v>70</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>918</v>
+        <v>493</v>
       </c>
       <c r="J15" s="0">
         <v>1026.5851</v>
@@ -4501,7 +4501,7 @@
         <v>71</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>919</v>
+        <v>494</v>
       </c>
       <c r="J16" s="0">
         <v>551.72749999999996</v>
@@ -4533,7 +4533,7 @@
         <v>72</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>920</v>
+        <v>495</v>
       </c>
       <c r="J17" s="0">
         <v>484.46609999999998</v>
@@ -4565,7 +4565,7 @@
         <v>73</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>921</v>
+        <v>496</v>
       </c>
       <c r="J18" s="0">
         <v>462.44240000000002</v>
@@ -4597,7 +4597,7 @@
         <v>74</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>922</v>
+        <v>497</v>
       </c>
       <c r="J19" s="0">
         <v>438.6388</v>
@@ -4629,7 +4629,7 @@
         <v>75</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>923</v>
+        <v>498</v>
       </c>
       <c r="J20" s="0">
         <v>433.1481</v>
@@ -4661,7 +4661,7 @@
         <v>76</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>924</v>
+        <v>499</v>
       </c>
       <c r="J21" s="0">
         <v>417.18799999999999</v>
@@ -4693,7 +4693,7 @@
         <v>77</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>925</v>
+        <v>500</v>
       </c>
       <c r="J22" s="0">
         <v>403.36680000000001</v>
@@ -4725,7 +4725,7 @@
         <v>78</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>926</v>
+        <v>501</v>
       </c>
       <c r="J23" s="0">
         <v>344.44220000000001</v>
@@ -4757,7 +4757,7 @@
         <v>79</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>927</v>
+        <v>502</v>
       </c>
       <c r="J24" s="0">
         <v>13941.7637</v>
@@ -4789,7 +4789,7 @@
         <v>80</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>928</v>
+        <v>503</v>
       </c>
       <c r="J25" s="0">
         <v>10106.319299999999</v>
@@ -4821,7 +4821,7 @@
         <v>83</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>929</v>
+        <v>506</v>
       </c>
       <c r="J26" s="0">
         <v>538.54449999999997</v>
@@ -4853,7 +4853,7 @@
         <v>84</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>930</v>
+        <v>507</v>
       </c>
       <c r="J27" s="0">
         <v>528.50789999999995</v>
@@ -4885,7 +4885,7 @@
         <v>85</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>931</v>
+        <v>508</v>
       </c>
       <c r="J28" s="0">
         <v>515.40830000000005</v>
@@ -4917,7 +4917,7 @@
         <v>86</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>932</v>
+        <v>509</v>
       </c>
       <c r="J29" s="0">
         <v>505.25689999999997</v>
@@ -4949,7 +4949,7 @@
         <v>87</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>933</v>
+        <v>510</v>
       </c>
       <c r="J30" s="0">
         <v>428.78109999999998</v>
@@ -4981,7 +4981,7 @@
         <v>88</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>934</v>
+        <v>511</v>
       </c>
       <c r="J31" s="0">
         <v>373.29050000000001</v>
@@ -5013,7 +5013,7 @@
         <v>89</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>935</v>
+        <v>512</v>
       </c>
       <c r="J32" s="0">
         <v>357.77280000000002</v>
@@ -5045,7 +5045,7 @@
         <v>90</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>936</v>
+        <v>513</v>
       </c>
       <c r="J33" s="0">
         <v>326.51060000000001</v>
@@ -5077,7 +5077,7 @@
         <v>91</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>937</v>
+        <v>514</v>
       </c>
       <c r="J34" s="0">
         <v>12781.4072</v>
@@ -5109,7 +5109,7 @@
         <v>93</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>938</v>
+        <v>516</v>
       </c>
       <c r="J35" s="0">
         <v>1452.7743</v>
@@ -5141,7 +5141,7 @@
         <v>94</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>939</v>
+        <v>517</v>
       </c>
       <c r="J36" s="0">
         <v>1450.1411000000001</v>
@@ -5173,7 +5173,7 @@
         <v>95</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>940</v>
+        <v>518</v>
       </c>
       <c r="J37" s="0">
         <v>473.58769999999998</v>
@@ -5205,7 +5205,7 @@
         <v>96</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>941</v>
+        <v>519</v>
       </c>
       <c r="J38" s="0">
         <v>468.9753</v>
@@ -5237,7 +5237,7 @@
         <v>97</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>942</v>
+        <v>520</v>
       </c>
       <c r="J39" s="0">
         <v>453.3648</v>
@@ -5269,7 +5269,7 @@
         <v>98</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>943</v>
+        <v>521</v>
       </c>
       <c r="J40" s="0">
         <v>435.75220000000002</v>
@@ -5301,7 +5301,7 @@
         <v>99</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>944</v>
+        <v>522</v>
       </c>
       <c r="J41" s="0">
         <v>434.1336</v>
@@ -5333,7 +5333,7 @@
         <v>100</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>945</v>
+        <v>523</v>
       </c>
       <c r="J42" s="0">
         <v>429.1137</v>
@@ -5365,7 +5365,7 @@
         <v>101</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>946</v>
+        <v>524</v>
       </c>
       <c r="J43" s="0">
         <v>392.56209999999999</v>
@@ -5397,7 +5397,7 @@
         <v>102</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>947</v>
+        <v>525</v>
       </c>
       <c r="J44" s="0">
         <v>366.25650000000002</v>
@@ -5429,7 +5429,7 @@
         <v>103</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>948</v>
+        <v>526</v>
       </c>
       <c r="J45" s="0">
         <v>11646.511699999999</v>
@@ -5461,7 +5461,7 @@
         <v>104</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>949</v>
+        <v>527</v>
       </c>
       <c r="J46" s="0">
         <v>7558.6841000000004</v>
@@ -5493,7 +5493,7 @@
         <v>105</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>950</v>
+        <v>528</v>
       </c>
       <c r="J47" s="0">
         <v>1293.2311</v>
@@ -5525,7 +5525,7 @@
         <v>106</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>951</v>
+        <v>529</v>
       </c>
       <c r="J48" s="0">
         <v>1168.5597</v>
@@ -5557,7 +5557,7 @@
         <v>107</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>952</v>
+        <v>530</v>
       </c>
       <c r="J49" s="0">
         <v>531.21609999999998</v>
@@ -5589,7 +5589,7 @@
         <v>108</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>953</v>
+        <v>531</v>
       </c>
       <c r="J50" s="0">
         <v>470.07299999999998</v>
@@ -5621,7 +5621,7 @@
         <v>109</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>954</v>
+        <v>532</v>
       </c>
       <c r="J51" s="0">
         <v>439.15929999999997</v>
@@ -5653,7 +5653,7 @@
         <v>110</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>955</v>
+        <v>533</v>
       </c>
       <c r="J52" s="0">
         <v>424.38709999999998</v>
@@ -5685,7 +5685,7 @@
         <v>111</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>956</v>
+        <v>534</v>
       </c>
       <c r="J53" s="0">
         <v>419.4384</v>
@@ -5717,7 +5717,7 @@
         <v>112</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>957</v>
+        <v>535</v>
       </c>
       <c r="J54" s="0">
         <v>413.99000000000001</v>
@@ -5749,7 +5749,7 @@
         <v>113</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>958</v>
+        <v>536</v>
       </c>
       <c r="J55" s="0">
         <v>408.73599999999999</v>
@@ -5781,7 +5781,7 @@
         <v>114</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>959</v>
+        <v>537</v>
       </c>
       <c r="J56" s="0">
         <v>408.7253</v>
@@ -5813,7 +5813,7 @@
         <v>115</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>960</v>
+        <v>538</v>
       </c>
       <c r="J57" s="0">
         <v>11876.8555</v>
@@ -5845,7 +5845,7 @@
         <v>116</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>961</v>
+        <v>539</v>
       </c>
       <c r="J58" s="0">
         <v>10286.9082</v>
@@ -5877,7 +5877,7 @@
         <v>117</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>962</v>
+        <v>540</v>
       </c>
       <c r="J59" s="0">
         <v>1060.3289</v>
@@ -5909,7 +5909,7 @@
         <v>118</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>963</v>
+        <v>541</v>
       </c>
       <c r="J60" s="0">
         <v>1004.1268</v>
@@ -5941,7 +5941,7 @@
         <v>119</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>964</v>
+        <v>542</v>
       </c>
       <c r="J61" s="0">
         <v>497.2799</v>
@@ -5973,7 +5973,7 @@
         <v>120</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>965</v>
+        <v>543</v>
       </c>
       <c r="J62" s="0">
         <v>485.87290000000002</v>
@@ -6005,7 +6005,7 @@
         <v>121</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>966</v>
+        <v>544</v>
       </c>
       <c r="J63" s="0">
         <v>429.8492</v>
@@ -6037,7 +6037,7 @@
         <v>122</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>967</v>
+        <v>545</v>
       </c>
       <c r="J64" s="0">
         <v>425.51229999999998</v>
@@ -6069,7 +6069,7 @@
         <v>123</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>968</v>
+        <v>546</v>
       </c>
       <c r="J65" s="0">
         <v>396.25139999999999</v>
@@ -6101,7 +6101,7 @@
         <v>124</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>969</v>
+        <v>547</v>
       </c>
       <c r="J66" s="0">
         <v>392.3723</v>
@@ -6133,7 +6133,7 @@
         <v>125</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>970</v>
+        <v>548</v>
       </c>
       <c r="J67" s="0">
         <v>351.54930000000002</v>
@@ -6165,7 +6165,7 @@
         <v>126</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>971</v>
+        <v>549</v>
       </c>
       <c r="J68" s="0">
         <v>348.02690000000001</v>
@@ -6197,7 +6197,7 @@
         <v>127</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>972</v>
+        <v>550</v>
       </c>
       <c r="J69" s="0">
         <v>12171.997100000001</v>
@@ -6229,7 +6229,7 @@
         <v>128</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>973</v>
+        <v>551</v>
       </c>
       <c r="J70" s="0">
         <v>6862.1084000000001</v>
@@ -6261,7 +6261,7 @@
         <v>129</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>974</v>
+        <v>552</v>
       </c>
       <c r="J71" s="0">
         <v>1099.6836000000001</v>
@@ -6293,7 +6293,7 @@
         <v>130</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>975</v>
+        <v>553</v>
       </c>
       <c r="J72" s="0">
         <v>752.58019999999999</v>
@@ -6325,7 +6325,7 @@
         <v>131</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>976</v>
+        <v>554</v>
       </c>
       <c r="J73" s="0">
         <v>487.68040000000002</v>
@@ -6357,7 +6357,7 @@
         <v>132</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>977</v>
+        <v>555</v>
       </c>
       <c r="J74" s="0">
         <v>463.46300000000002</v>
@@ -6389,7 +6389,7 @@
         <v>133</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>978</v>
+        <v>556</v>
       </c>
       <c r="J75" s="0">
         <v>442.20010000000002</v>
@@ -6421,7 +6421,7 @@
         <v>134</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>979</v>
+        <v>557</v>
       </c>
       <c r="J76" s="0">
         <v>426.24950000000001</v>
@@ -6453,7 +6453,7 @@
         <v>135</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>980</v>
+        <v>558</v>
       </c>
       <c r="J77" s="0">
         <v>392.93150000000003</v>
@@ -6485,7 +6485,7 @@
         <v>136</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>981</v>
+        <v>559</v>
       </c>
       <c r="J78" s="0">
         <v>377.69189999999998</v>
@@ -6517,7 +6517,7 @@
         <v>137</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>982</v>
+        <v>560</v>
       </c>
       <c r="J79" s="0">
         <v>372.46730000000002</v>
@@ -6549,7 +6549,7 @@
         <v>138</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>983</v>
+        <v>561</v>
       </c>
       <c r="J80" s="0">
         <v>367.9117</v>
@@ -6581,7 +6581,7 @@
         <v>139</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>984</v>
+        <v>562</v>
       </c>
       <c r="J81" s="0">
         <v>9907.2489999999998</v>
@@ -6613,7 +6613,7 @@
         <v>140</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>985</v>
+        <v>563</v>
       </c>
       <c r="J82" s="0">
         <v>9652.7158</v>
@@ -6645,7 +6645,7 @@
         <v>141</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>986</v>
+        <v>564</v>
       </c>
       <c r="J83" s="0">
         <v>1441.7384999999999</v>
@@ -6677,7 +6677,7 @@
         <v>142</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>987</v>
+        <v>565</v>
       </c>
       <c r="J84" s="0">
         <v>1225.0391</v>
@@ -6709,7 +6709,7 @@
         <v>143</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>988</v>
+        <v>566</v>
       </c>
       <c r="J85" s="0">
         <v>535.24869999999999</v>
@@ -6741,7 +6741,7 @@
         <v>144</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>989</v>
+        <v>567</v>
       </c>
       <c r="J86" s="0">
         <v>505.87869999999998</v>
@@ -6773,7 +6773,7 @@
         <v>145</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>990</v>
+        <v>568</v>
       </c>
       <c r="J87" s="0">
         <v>499.1123</v>
@@ -6805,7 +6805,7 @@
         <v>146</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>991</v>
+        <v>569</v>
       </c>
       <c r="J88" s="0">
         <v>454.46269999999998</v>
@@ -6837,7 +6837,7 @@
         <v>147</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>992</v>
+        <v>570</v>
       </c>
       <c r="J89" s="0">
         <v>452.58749999999998</v>
@@ -6869,7 +6869,7 @@
         <v>148</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>993</v>
+        <v>571</v>
       </c>
       <c r="J90" s="0">
         <v>434.6585</v>
@@ -6901,7 +6901,7 @@
         <v>149</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>994</v>
+        <v>572</v>
       </c>
       <c r="J91" s="0">
         <v>401.7577</v>
@@ -6933,7 +6933,7 @@
         <v>150</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>995</v>
+        <v>573</v>
       </c>
       <c r="J92" s="0">
         <v>395.96719999999999</v>
@@ -6965,7 +6965,7 @@
         <v>151</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>996</v>
+        <v>574</v>
       </c>
       <c r="J93" s="0">
         <v>13039.6055</v>
@@ -6997,7 +6997,7 @@
         <v>152</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>997</v>
+        <v>575</v>
       </c>
       <c r="J94" s="0">
         <v>6975.5502999999999</v>
@@ -7029,7 +7029,7 @@
         <v>153</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>998</v>
+        <v>576</v>
       </c>
       <c r="J95" s="0">
         <v>1471.2853</v>
@@ -7061,7 +7061,7 @@
         <v>154</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>999</v>
+        <v>577</v>
       </c>
       <c r="J96" s="0">
         <v>1120.2394999999999</v>
@@ -7093,7 +7093,7 @@
         <v>155</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>1000</v>
+        <v>578</v>
       </c>
       <c r="J97" s="0">
         <v>525.06529999999998</v>
@@ -7125,7 +7125,7 @@
         <v>156</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>1001</v>
+        <v>579</v>
       </c>
       <c r="J98" s="0">
         <v>511.11419999999998</v>
@@ -7157,7 +7157,7 @@
         <v>157</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>1002</v>
+        <v>580</v>
       </c>
       <c r="J99" s="0">
         <v>488.54860000000002</v>
@@ -7189,7 +7189,7 @@
         <v>158</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>1003</v>
+        <v>581</v>
       </c>
       <c r="J100" s="0">
         <v>456.88260000000002</v>
@@ -7221,7 +7221,7 @@
         <v>159</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>1004</v>
+        <v>582</v>
       </c>
       <c r="J101" s="0">
         <v>454.80709999999999</v>
@@ -7253,7 +7253,7 @@
         <v>160</v>
       </c>
       <c r="I102" s="0" t="s">
-        <v>1005</v>
+        <v>583</v>
       </c>
       <c r="J102" s="0">
         <v>440.73829999999998</v>
@@ -7285,7 +7285,7 @@
         <v>161</v>
       </c>
       <c r="I103" s="0" t="s">
-        <v>1006</v>
+        <v>584</v>
       </c>
       <c r="J103" s="0">
         <v>390.3793</v>
@@ -7317,7 +7317,7 @@
         <v>162</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>1007</v>
+        <v>585</v>
       </c>
       <c r="J104" s="0">
         <v>366.7876</v>
@@ -7349,7 +7349,7 @@
         <v>163</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>1008</v>
+        <v>586</v>
       </c>
       <c r="J105" s="0">
         <v>13740.0527</v>
@@ -7381,7 +7381,7 @@
         <v>164</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>1009</v>
+        <v>587</v>
       </c>
       <c r="J106" s="0">
         <v>9744.2099999999991</v>
@@ -7413,7 +7413,7 @@
         <v>167</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>1010</v>
+        <v>590</v>
       </c>
       <c r="J107" s="0">
         <v>543.12710000000004</v>
@@ -7445,7 +7445,7 @@
         <v>168</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>1011</v>
+        <v>591</v>
       </c>
       <c r="J108" s="0">
         <v>530.70270000000005</v>
@@ -7477,7 +7477,7 @@
         <v>169</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>1012</v>
+        <v>592</v>
       </c>
       <c r="J109" s="0">
         <v>482.14240000000001</v>
@@ -7509,7 +7509,7 @@
         <v>170</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>1013</v>
+        <v>593</v>
       </c>
       <c r="J110" s="0">
         <v>462.08449999999999</v>
@@ -7541,7 +7541,7 @@
         <v>171</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>1014</v>
+        <v>594</v>
       </c>
       <c r="J111" s="0">
         <v>457.30529999999999</v>
@@ -7573,7 +7573,7 @@
         <v>172</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>1015</v>
+        <v>595</v>
       </c>
       <c r="J112" s="0">
         <v>450.53769999999997</v>
@@ -7605,7 +7605,7 @@
         <v>173</v>
       </c>
       <c r="I113" s="0" t="s">
-        <v>1016</v>
+        <v>596</v>
       </c>
       <c r="J113" s="0">
         <v>416.66809999999998</v>
@@ -7637,7 +7637,7 @@
         <v>174</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>1017</v>
+        <v>597</v>
       </c>
       <c r="J114" s="0">
         <v>381.01350000000002</v>
@@ -7669,7 +7669,7 @@
         <v>179</v>
       </c>
       <c r="I115" s="0" t="s">
-        <v>1018</v>
+        <v>602</v>
       </c>
       <c r="J115" s="0">
         <v>606.53700000000003</v>
@@ -7701,7 +7701,7 @@
         <v>180</v>
       </c>
       <c r="I116" s="0" t="s">
-        <v>1019</v>
+        <v>603</v>
       </c>
       <c r="J116" s="0">
         <v>479.4468</v>
@@ -7733,7 +7733,7 @@
         <v>181</v>
       </c>
       <c r="I117" s="0" t="s">
-        <v>1020</v>
+        <v>604</v>
       </c>
       <c r="J117" s="0">
         <v>479.09190000000001</v>
@@ -7765,7 +7765,7 @@
         <v>182</v>
       </c>
       <c r="I118" s="0" t="s">
-        <v>1021</v>
+        <v>605</v>
       </c>
       <c r="J118" s="0">
         <v>441.61619999999999</v>
@@ -7797,7 +7797,7 @@
         <v>183</v>
       </c>
       <c r="I119" s="0" t="s">
-        <v>1022</v>
+        <v>606</v>
       </c>
       <c r="J119" s="0">
         <v>417.55779999999999</v>
@@ -7829,7 +7829,7 @@
         <v>184</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>1023</v>
+        <v>607</v>
       </c>
       <c r="J120" s="0">
         <v>380.84750000000003</v>
@@ -7861,7 +7861,7 @@
         <v>185</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>1024</v>
+        <v>608</v>
       </c>
       <c r="J121" s="0">
         <v>380.4452</v>
@@ -7893,7 +7893,7 @@
         <v>186</v>
       </c>
       <c r="I122" s="0" t="s">
-        <v>1025</v>
+        <v>609</v>
       </c>
       <c r="J122" s="0">
         <v>338.78429999999997</v>
@@ -7925,7 +7925,7 @@
         <v>187</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>1026</v>
+        <v>610</v>
       </c>
       <c r="J123" s="0">
         <v>11531.805700000001</v>
@@ -7957,7 +7957,7 @@
         <v>188</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>1027</v>
+        <v>611</v>
       </c>
       <c r="J124" s="0">
         <v>6375.0625</v>
@@ -7989,7 +7989,7 @@
         <v>105</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>1028</v>
+        <v>612</v>
       </c>
       <c r="J125" s="0">
         <v>1293.2311</v>
@@ -8021,7 +8021,7 @@
         <v>106</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>1029</v>
+        <v>613</v>
       </c>
       <c r="J126" s="0">
         <v>1168.5597</v>
@@ -8053,7 +8053,7 @@
         <v>144</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>1030</v>
+        <v>614</v>
       </c>
       <c r="J127" s="0">
         <v>505.87869999999998</v>
@@ -8085,7 +8085,7 @@
         <v>189</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>1031</v>
+        <v>615</v>
       </c>
       <c r="J128" s="0">
         <v>480.84039999999999</v>
@@ -8117,7 +8117,7 @@
         <v>190</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>1032</v>
+        <v>616</v>
       </c>
       <c r="J129" s="0">
         <v>474.62130000000002</v>
@@ -8149,7 +8149,7 @@
         <v>191</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>1033</v>
+        <v>617</v>
       </c>
       <c r="J130" s="0">
         <v>462.91030000000001</v>
@@ -8181,7 +8181,7 @@
         <v>192</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>1034</v>
+        <v>618</v>
       </c>
       <c r="J131" s="0">
         <v>435.94409999999999</v>
@@ -8213,7 +8213,7 @@
         <v>193</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>1035</v>
+        <v>619</v>
       </c>
       <c r="J132" s="0">
         <v>419.98750000000001</v>
@@ -8245,7 +8245,7 @@
         <v>194</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>1036</v>
+        <v>620</v>
       </c>
       <c r="J133" s="0">
         <v>401.06349999999998</v>
@@ -8277,7 +8277,7 @@
         <v>195</v>
       </c>
       <c r="I134" s="0" t="s">
-        <v>1037</v>
+        <v>621</v>
       </c>
       <c r="J134" s="0">
         <v>400.24349999999998</v>
@@ -8309,7 +8309,7 @@
         <v>196</v>
       </c>
       <c r="I135" s="0" t="s">
-        <v>1038</v>
+        <v>622</v>
       </c>
       <c r="J135" s="0">
         <v>10941.195299999999</v>
@@ -8341,7 +8341,7 @@
         <v>197</v>
       </c>
       <c r="I136" s="0" t="s">
-        <v>1039</v>
+        <v>623</v>
       </c>
       <c r="J136" s="0">
         <v>7539.1181999999999</v>
@@ -8373,7 +8373,7 @@
         <v>198</v>
       </c>
       <c r="I137" s="0" t="s">
-        <v>1040</v>
+        <v>624</v>
       </c>
       <c r="J137" s="0">
         <v>1460.5899999999999</v>
@@ -8405,7 +8405,7 @@
         <v>199</v>
       </c>
       <c r="I138" s="0" t="s">
-        <v>1041</v>
+        <v>625</v>
       </c>
       <c r="J138" s="0">
         <v>1390.1700000000001</v>
@@ -8437,7 +8437,7 @@
         <v>200</v>
       </c>
       <c r="I139" s="0" t="s">
-        <v>1042</v>
+        <v>626</v>
       </c>
       <c r="J139" s="0">
         <v>1191.2892999999999</v>
@@ -8469,7 +8469,7 @@
         <v>201</v>
       </c>
       <c r="I140" s="0" t="s">
-        <v>1043</v>
+        <v>627</v>
       </c>
       <c r="J140" s="0">
         <v>905.0009</v>
@@ -8501,7 +8501,7 @@
         <v>202</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>1044</v>
+        <v>628</v>
       </c>
       <c r="J141" s="0">
         <v>509.07279999999997</v>
@@ -8533,7 +8533,7 @@
         <v>203</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>1045</v>
+        <v>629</v>
       </c>
       <c r="J142" s="0">
         <v>509.06999999999999</v>
@@ -8565,7 +8565,7 @@
         <v>204</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>1046</v>
+        <v>630</v>
       </c>
       <c r="J143" s="0">
         <v>467.17430000000002</v>
@@ -8597,7 +8597,7 @@
         <v>205</v>
       </c>
       <c r="I144" s="0" t="s">
-        <v>1047</v>
+        <v>631</v>
       </c>
       <c r="J144" s="0">
         <v>467.17000000000002</v>
@@ -8629,7 +8629,7 @@
         <v>206</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>1048</v>
+        <v>632</v>
       </c>
       <c r="J145" s="0">
         <v>461.41000000000003</v>
@@ -8661,7 +8661,7 @@
         <v>207</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>1049</v>
+        <v>633</v>
       </c>
       <c r="J146" s="0">
         <v>461.40780000000001</v>
@@ -8693,7 +8693,7 @@
         <v>208</v>
       </c>
       <c r="I147" s="0" t="s">
-        <v>1050</v>
+        <v>634</v>
       </c>
       <c r="J147" s="0">
         <v>426.55000000000001</v>
@@ -8725,7 +8725,7 @@
         <v>209</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>1051</v>
+        <v>635</v>
       </c>
       <c r="J148" s="0">
         <v>426.54820000000001</v>
@@ -8757,7 +8757,7 @@
         <v>210</v>
       </c>
       <c r="I149" s="0" t="s">
-        <v>1052</v>
+        <v>636</v>
       </c>
       <c r="J149" s="0">
         <v>390.12</v>
@@ -8789,7 +8789,7 @@
         <v>211</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>1053</v>
+        <v>637</v>
       </c>
       <c r="J150" s="0">
         <v>390.1198</v>
@@ -8821,7 +8821,7 @@
         <v>212</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>1054</v>
+        <v>638</v>
       </c>
       <c r="J151" s="0">
         <v>386.36000000000001</v>
@@ -8853,7 +8853,7 @@
         <v>213</v>
       </c>
       <c r="I152" s="0" t="s">
-        <v>1055</v>
+        <v>639</v>
       </c>
       <c r="J152" s="0">
         <v>386.35520000000002</v>
@@ -8885,7 +8885,7 @@
         <v>214</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>1056</v>
+        <v>640</v>
       </c>
       <c r="J153" s="0">
         <v>359.35480000000001</v>
@@ -8917,7 +8917,7 @@
         <v>215</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>1057</v>
+        <v>641</v>
       </c>
       <c r="J154" s="0">
         <v>359.35000000000002</v>
@@ -8949,7 +8949,7 @@
         <v>216</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>1058</v>
+        <v>642</v>
       </c>
       <c r="J155" s="0">
         <v>4.8700000000000001</v>
@@ -8981,7 +8981,7 @@
         <v>218</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>1059</v>
+        <v>644</v>
       </c>
       <c r="J156" s="0">
         <v>12758.521500000001</v>
@@ -9013,7 +9013,7 @@
         <v>220</v>
       </c>
       <c r="I157" s="0" t="s">
-        <v>1060</v>
+        <v>646</v>
       </c>
       <c r="J157" s="0">
         <v>1518.05</v>
@@ -9045,7 +9045,7 @@
         <v>221</v>
       </c>
       <c r="I158" s="0" t="s">
-        <v>1061</v>
+        <v>647</v>
       </c>
       <c r="J158" s="0">
         <v>1483.55</v>
@@ -9077,7 +9077,7 @@
         <v>224</v>
       </c>
       <c r="I159" s="0" t="s">
-        <v>1062</v>
+        <v>650</v>
       </c>
       <c r="J159" s="0">
         <v>508.62</v>
@@ -9109,7 +9109,7 @@
         <v>225</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>1063</v>
+        <v>651</v>
       </c>
       <c r="J160" s="0">
         <v>508.61829999999998</v>
@@ -9141,7 +9141,7 @@
         <v>226</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>1064</v>
+        <v>652</v>
       </c>
       <c r="J161" s="0">
         <v>468.33999999999998</v>
@@ -9173,7 +9173,7 @@
         <v>227</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>1065</v>
+        <v>653</v>
       </c>
       <c r="J162" s="0">
         <v>468.33859999999999</v>
@@ -9205,7 +9205,7 @@
         <v>228</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>1066</v>
+        <v>654</v>
       </c>
       <c r="J163" s="0">
         <v>441.58999999999998</v>
@@ -9237,7 +9237,7 @@
         <v>229</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>1067</v>
+        <v>655</v>
       </c>
       <c r="J164" s="0">
         <v>441.58780000000002</v>
@@ -9269,7 +9269,7 @@
         <v>230</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>1068</v>
+        <v>656</v>
       </c>
       <c r="J165" s="0">
         <v>417.62110000000001</v>
@@ -9301,7 +9301,7 @@
         <v>231</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>1069</v>
+        <v>657</v>
       </c>
       <c r="J166" s="0">
         <v>417.62</v>
@@ -9333,7 +9333,7 @@
         <v>232</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>1070</v>
+        <v>658</v>
       </c>
       <c r="J167" s="0">
         <v>407.61059999999998</v>
@@ -9365,7 +9365,7 @@
         <v>233</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>1071</v>
+        <v>659</v>
       </c>
       <c r="J168" s="0">
         <v>407.61000000000001</v>
@@ -9397,7 +9397,7 @@
         <v>234</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>1072</v>
+        <v>660</v>
       </c>
       <c r="J169" s="0">
         <v>392.51999999999998</v>
@@ -9429,7 +9429,7 @@
         <v>235</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>1073</v>
+        <v>661</v>
       </c>
       <c r="J170" s="0">
         <v>392.51850000000002</v>
@@ -9461,7 +9461,7 @@
         <v>236</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>1074</v>
+        <v>662</v>
       </c>
       <c r="J171" s="0">
         <v>382.75999999999999</v>
@@ -9493,7 +9493,7 @@
         <v>237</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>1075</v>
+        <v>663</v>
       </c>
       <c r="J172" s="0">
         <v>382.75760000000002</v>
@@ -9525,7 +9525,7 @@
         <v>238</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>1076</v>
+        <v>664</v>
       </c>
       <c r="J173" s="0">
         <v>323.20999999999998</v>
@@ -9557,7 +9557,7 @@
         <v>239</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>1077</v>
+        <v>665</v>
       </c>
       <c r="J174" s="0">
         <v>323.20670000000001</v>
@@ -9589,7 +9589,7 @@
         <v>240</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>1078</v>
+        <v>666</v>
       </c>
       <c r="J175" s="0">
         <v>10995.9912</v>
@@ -9621,7 +9621,7 @@
         <v>241</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>1079</v>
+        <v>667</v>
       </c>
       <c r="J176" s="0">
         <v>7215.2777999999999</v>
@@ -9653,7 +9653,7 @@
         <v>242</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>1080</v>
+        <v>668</v>
       </c>
       <c r="J177" s="0">
         <v>1710.03</v>
@@ -9685,7 +9685,7 @@
         <v>243</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>1081</v>
+        <v>669</v>
       </c>
       <c r="J178" s="0">
         <v>1001.1900000000001</v>
@@ -9717,7 +9717,7 @@
         <v>244</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>1082</v>
+        <v>670</v>
       </c>
       <c r="J179" s="0">
         <v>1188.2415000000001</v>
@@ -9749,7 +9749,7 @@
         <v>246</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>1083</v>
+        <v>672</v>
       </c>
       <c r="J180" s="0">
         <v>426.52229999999997</v>
@@ -9781,7 +9781,7 @@
         <v>247</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>1084</v>
+        <v>673</v>
       </c>
       <c r="J181" s="0">
         <v>426.51999999999998</v>
@@ -9813,7 +9813,7 @@
         <v>248</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>1085</v>
+        <v>674</v>
       </c>
       <c r="J182" s="0">
         <v>390.1635</v>
@@ -9845,7 +9845,7 @@
         <v>249</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>1086</v>
+        <v>675</v>
       </c>
       <c r="J183" s="0">
         <v>390.16000000000003</v>
@@ -9877,7 +9877,7 @@
         <v>250</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>1087</v>
+        <v>676</v>
       </c>
       <c r="J184" s="0">
         <v>385.91000000000003</v>
@@ -9909,7 +9909,7 @@
         <v>251</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>1088</v>
+        <v>677</v>
       </c>
       <c r="J185" s="0">
         <v>385.90809999999999</v>
@@ -9941,7 +9941,7 @@
         <v>252</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>1089</v>
+        <v>678</v>
       </c>
       <c r="J186" s="0">
         <v>269.38150000000002</v>
@@ -9973,7 +9973,7 @@
         <v>253</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>1090</v>
+        <v>679</v>
       </c>
       <c r="J187" s="0">
         <v>269.38</v>
@@ -10005,7 +10005,7 @@
         <v>254</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>1091</v>
+        <v>680</v>
       </c>
       <c r="J188" s="0">
         <v>248.60079999999999</v>
@@ -10037,7 +10037,7 @@
         <v>255</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>1092</v>
+        <v>681</v>
       </c>
       <c r="J189" s="0">
         <v>248.6</v>
@@ -10069,7 +10069,7 @@
         <v>256</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>1093</v>
+        <v>682</v>
       </c>
       <c r="J190" s="0">
         <v>224.50450000000001</v>
@@ -10101,7 +10101,7 @@
         <v>257</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>1094</v>
+        <v>683</v>
       </c>
       <c r="J191" s="0">
         <v>224.5</v>
@@ -10133,7 +10133,7 @@
         <v>258</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>1095</v>
+        <v>684</v>
       </c>
       <c r="J192" s="0">
         <v>192.28460000000001</v>
@@ -10165,7 +10165,7 @@
         <v>259</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>1096</v>
+        <v>685</v>
       </c>
       <c r="J193" s="0">
         <v>192.28</v>
@@ -10197,7 +10197,7 @@
         <v>260</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>1097</v>
+        <v>686</v>
       </c>
       <c r="J194" s="0">
         <v>152.80000000000001</v>
@@ -10229,7 +10229,7 @@
         <v>261</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>1098</v>
+        <v>687</v>
       </c>
       <c r="J195" s="0">
         <v>152.7972</v>
@@ -10261,7 +10261,7 @@
         <v>262</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>1099</v>
+        <v>688</v>
       </c>
       <c r="J196" s="0">
         <v>11254.794900000001</v>
@@ -10293,7 +10293,7 @@
         <v>263</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>1100</v>
+        <v>689</v>
       </c>
       <c r="J197" s="0">
         <v>8245.5498000000007</v>
@@ -10325,7 +10325,7 @@
         <v>264</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>1101</v>
+        <v>690</v>
       </c>
       <c r="J198" s="0">
         <v>1104.5668000000001</v>
@@ -10357,7 +10357,7 @@
         <v>265</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>1102</v>
+        <v>691</v>
       </c>
       <c r="J199" s="0">
         <v>667.55740000000003</v>
@@ -10389,7 +10389,7 @@
         <v>266</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>1103</v>
+        <v>692</v>
       </c>
       <c r="J200" s="0">
         <v>476.60090000000002</v>
@@ -10421,7 +10421,7 @@
         <v>267</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>1104</v>
+        <v>693</v>
       </c>
       <c r="J201" s="0">
         <v>449.04090000000002</v>
@@ -10453,7 +10453,7 @@
         <v>268</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>1105</v>
+        <v>694</v>
       </c>
       <c r="J202" s="0">
         <v>442.10520000000002</v>
@@ -10485,7 +10485,7 @@
         <v>269</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>1106</v>
+        <v>695</v>
       </c>
       <c r="J203" s="0">
         <v>409.70580000000001</v>
@@ -10517,7 +10517,7 @@
         <v>270</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>1107</v>
+        <v>696</v>
       </c>
       <c r="J204" s="0">
         <v>397.46850000000001</v>
@@ -10549,7 +10549,7 @@
         <v>271</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>1108</v>
+        <v>697</v>
       </c>
       <c r="J205" s="0">
         <v>383.6352</v>
@@ -10581,7 +10581,7 @@
         <v>272</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>1109</v>
+        <v>698</v>
       </c>
       <c r="J206" s="0">
         <v>381.00670000000002</v>
@@ -10613,7 +10613,7 @@
         <v>273</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>1110</v>
+        <v>699</v>
       </c>
       <c r="J207" s="0">
         <v>353.37259999999998</v>
@@ -10645,7 +10645,7 @@
         <v>274</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>1111</v>
+        <v>700</v>
       </c>
       <c r="J208" s="0">
         <v>14310.114299999999</v>
@@ -10677,7 +10677,7 @@
         <v>275</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>1112</v>
+        <v>701</v>
       </c>
       <c r="J209" s="0">
         <v>8465.1962999999996</v>
@@ -10709,7 +10709,7 @@
         <v>276</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>1113</v>
+        <v>702</v>
       </c>
       <c r="J210" s="0">
         <v>1220.287</v>
@@ -10741,7 +10741,7 @@
         <v>277</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>1114</v>
+        <v>703</v>
       </c>
       <c r="J211" s="0">
         <v>599.00360000000001</v>
@@ -10773,7 +10773,7 @@
         <v>278</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>1115</v>
+        <v>704</v>
       </c>
       <c r="J212" s="0">
         <v>555.67830000000004</v>
@@ -10805,7 +10805,7 @@
         <v>279</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>1116</v>
+        <v>705</v>
       </c>
       <c r="J213" s="0">
         <v>491.62889999999999</v>
@@ -10837,7 +10837,7 @@
         <v>280</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>1117</v>
+        <v>706</v>
       </c>
       <c r="J214" s="0">
         <v>487.06729999999999</v>
@@ -10869,7 +10869,7 @@
         <v>281</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>1118</v>
+        <v>707</v>
       </c>
       <c r="J215" s="0">
         <v>443.50709999999998</v>
@@ -10901,7 +10901,7 @@
         <v>282</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>1119</v>
+        <v>708</v>
       </c>
       <c r="J216" s="0">
         <v>437.17829999999998</v>
@@ -10933,7 +10933,7 @@
         <v>283</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>1120</v>
+        <v>709</v>
       </c>
       <c r="J217" s="0">
         <v>422.71879999999999</v>
@@ -10965,7 +10965,7 @@
         <v>284</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>1121</v>
+        <v>710</v>
       </c>
       <c r="J218" s="0">
         <v>405.00119999999998</v>
@@ -10997,7 +10997,7 @@
         <v>285</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>1122</v>
+        <v>711</v>
       </c>
       <c r="J219" s="0">
         <v>378.08580000000001</v>
@@ -11029,7 +11029,7 @@
         <v>286</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>1123</v>
+        <v>712</v>
       </c>
       <c r="J220" s="0">
         <v>10927.456099999999</v>
@@ -11061,7 +11061,7 @@
         <v>287</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>1124</v>
+        <v>713</v>
       </c>
       <c r="J221" s="0">
         <v>7092.1475</v>
@@ -11093,7 +11093,7 @@
         <v>288</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>1125</v>
+        <v>714</v>
       </c>
       <c r="J222" s="0">
         <v>1251.4889000000001</v>
@@ -11125,7 +11125,7 @@
         <v>290</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>1126</v>
+        <v>716</v>
       </c>
       <c r="J223" s="0">
         <v>573.87549999999999</v>
@@ -11157,7 +11157,7 @@
         <v>291</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>1127</v>
+        <v>717</v>
       </c>
       <c r="J224" s="0">
         <v>432.66559999999998</v>
@@ -11189,7 +11189,7 @@
         <v>292</v>
       </c>
       <c r="I225" s="0" t="s">
-        <v>1128</v>
+        <v>718</v>
       </c>
       <c r="J225" s="0">
         <v>429.50220000000002</v>
@@ -11221,7 +11221,7 @@
         <v>293</v>
       </c>
       <c r="I226" s="0" t="s">
-        <v>1129</v>
+        <v>719</v>
       </c>
       <c r="J226" s="0">
         <v>425.55560000000003</v>
@@ -11253,7 +11253,7 @@
         <v>294</v>
       </c>
       <c r="I227" s="0" t="s">
-        <v>1130</v>
+        <v>720</v>
       </c>
       <c r="J227" s="0">
         <v>412.95150000000001</v>
@@ -11285,7 +11285,7 @@
         <v>295</v>
       </c>
       <c r="I228" s="0" t="s">
-        <v>1131</v>
+        <v>721</v>
       </c>
       <c r="J228" s="0">
         <v>403.95030000000003</v>
@@ -11317,7 +11317,7 @@
         <v>296</v>
       </c>
       <c r="I229" s="0" t="s">
-        <v>1132</v>
+        <v>722</v>
       </c>
       <c r="J229" s="0">
         <v>366.0301</v>
@@ -11349,7 +11349,7 @@
         <v>297</v>
       </c>
       <c r="I230" s="0" t="s">
-        <v>1133</v>
+        <v>723</v>
       </c>
       <c r="J230" s="0">
         <v>322.23540000000003</v>
@@ -11381,7 +11381,7 @@
         <v>298</v>
       </c>
       <c r="I231" s="0" t="s">
-        <v>1134</v>
+        <v>724</v>
       </c>
       <c r="J231" s="0">
         <v>14707.393599999999</v>
@@ -11413,7 +11413,7 @@
         <v>299</v>
       </c>
       <c r="I232" s="0" t="s">
-        <v>1135</v>
+        <v>725</v>
       </c>
       <c r="J232" s="0">
         <v>6104.8818000000001</v>
@@ -11445,7 +11445,7 @@
         <v>300</v>
       </c>
       <c r="I233" s="0" t="s">
-        <v>1136</v>
+        <v>726</v>
       </c>
       <c r="J233" s="0">
         <v>882.45939999999996</v>
@@ -11477,7 +11477,7 @@
         <v>301</v>
       </c>
       <c r="I234" s="0" t="s">
-        <v>1137</v>
+        <v>727</v>
       </c>
       <c r="J234" s="0">
         <v>761.87369999999999</v>
@@ -11509,7 +11509,7 @@
         <v>302</v>
       </c>
       <c r="I235" s="0" t="s">
-        <v>1138</v>
+        <v>728</v>
       </c>
       <c r="J235" s="0">
         <v>521.54589999999996</v>
@@ -11541,7 +11541,7 @@
         <v>303</v>
       </c>
       <c r="I236" s="0" t="s">
-        <v>1139</v>
+        <v>729</v>
       </c>
       <c r="J236" s="0">
         <v>500.20800000000003</v>
@@ -11573,7 +11573,7 @@
         <v>304</v>
       </c>
       <c r="I237" s="0" t="s">
-        <v>1140</v>
+        <v>730</v>
       </c>
       <c r="J237" s="0">
         <v>462.5016</v>
@@ -11605,7 +11605,7 @@
         <v>305</v>
       </c>
       <c r="I238" s="0" t="s">
-        <v>1141</v>
+        <v>731</v>
       </c>
       <c r="J238" s="0">
         <v>460.94619999999998</v>
@@ -11637,7 +11637,7 @@
         <v>306</v>
       </c>
       <c r="I239" s="0" t="s">
-        <v>1142</v>
+        <v>732</v>
       </c>
       <c r="J239" s="0">
         <v>455.41989999999999</v>
@@ -11669,7 +11669,7 @@
         <v>307</v>
       </c>
       <c r="I240" s="0" t="s">
-        <v>1143</v>
+        <v>733</v>
       </c>
       <c r="J240" s="0">
         <v>429.3236</v>
@@ -11701,7 +11701,7 @@
         <v>308</v>
       </c>
       <c r="I241" s="0" t="s">
-        <v>1144</v>
+        <v>734</v>
       </c>
       <c r="J241" s="0">
         <v>399.94749999999999</v>
@@ -11733,7 +11733,7 @@
         <v>309</v>
       </c>
       <c r="I242" s="0" t="s">
-        <v>1145</v>
+        <v>735</v>
       </c>
       <c r="J242" s="0">
         <v>232.58420000000001</v>
@@ -11765,7 +11765,7 @@
         <v>310</v>
       </c>
       <c r="I243" s="0" t="s">
-        <v>1146</v>
+        <v>736</v>
       </c>
       <c r="J243" s="0">
         <v>11847.5967</v>
@@ -11797,7 +11797,7 @@
         <v>311</v>
       </c>
       <c r="I244" s="0" t="s">
-        <v>1147</v>
+        <v>737</v>
       </c>
       <c r="J244" s="0">
         <v>6282.4102000000003</v>
@@ -11829,7 +11829,7 @@
         <v>312</v>
       </c>
       <c r="I245" s="0" t="s">
-        <v>1148</v>
+        <v>738</v>
       </c>
       <c r="J245" s="0">
         <v>1301.1243999999999</v>
@@ -11861,7 +11861,7 @@
         <v>313</v>
       </c>
       <c r="I246" s="0" t="s">
-        <v>1149</v>
+        <v>739</v>
       </c>
       <c r="J246" s="0">
         <v>939.31240000000003</v>
@@ -11893,7 +11893,7 @@
         <v>314</v>
       </c>
       <c r="I247" s="0" t="s">
-        <v>1150</v>
+        <v>740</v>
       </c>
       <c r="J247" s="0">
         <v>482.02300000000002</v>
@@ -11925,7 +11925,7 @@
         <v>315</v>
       </c>
       <c r="I248" s="0" t="s">
-        <v>1151</v>
+        <v>741</v>
       </c>
       <c r="J248" s="0">
         <v>466.72879999999998</v>
@@ -11957,7 +11957,7 @@
         <v>192</v>
       </c>
       <c r="I249" s="0" t="s">
-        <v>1152</v>
+        <v>742</v>
       </c>
       <c r="J249" s="0">
         <v>435.94409999999999</v>
@@ -11989,7 +11989,7 @@
         <v>316</v>
       </c>
       <c r="I250" s="0" t="s">
-        <v>1153</v>
+        <v>743</v>
       </c>
       <c r="J250" s="0">
         <v>400.39690000000002</v>
@@ -12021,7 +12021,7 @@
         <v>317</v>
       </c>
       <c r="I251" s="0" t="s">
-        <v>1154</v>
+        <v>744</v>
       </c>
       <c r="J251" s="0">
         <v>400.39350000000002</v>
@@ -12053,7 +12053,7 @@
         <v>318</v>
       </c>
       <c r="I252" s="0" t="s">
-        <v>1155</v>
+        <v>745</v>
       </c>
       <c r="J252" s="0">
         <v>385.38260000000002</v>
@@ -12085,7 +12085,7 @@
         <v>319</v>
       </c>
       <c r="I253" s="0" t="s">
-        <v>1156</v>
+        <v>746</v>
       </c>
       <c r="J253" s="0">
         <v>347.70269999999999</v>
@@ -12117,7 +12117,7 @@
         <v>320</v>
       </c>
       <c r="I254" s="0" t="s">
-        <v>1157</v>
+        <v>747</v>
       </c>
       <c r="J254" s="0">
         <v>329.09859999999998</v>
@@ -12149,7 +12149,7 @@
         <v>321</v>
       </c>
       <c r="I255" s="0" t="s">
-        <v>1158</v>
+        <v>748</v>
       </c>
       <c r="J255" s="0">
         <v>12556.6572</v>
@@ -12181,7 +12181,7 @@
         <v>322</v>
       </c>
       <c r="I256" s="0" t="s">
-        <v>1159</v>
+        <v>749</v>
       </c>
       <c r="J256" s="0">
         <v>6296.4022999999998</v>
@@ -12213,7 +12213,7 @@
         <v>323</v>
       </c>
       <c r="I257" s="0" t="s">
-        <v>1160</v>
+        <v>750</v>
       </c>
       <c r="J257" s="0">
         <v>968.71990000000005</v>
@@ -12245,7 +12245,7 @@
         <v>324</v>
       </c>
       <c r="I258" s="0" t="s">
-        <v>1161</v>
+        <v>751</v>
       </c>
       <c r="J258" s="0">
         <v>883.06809999999996</v>
@@ -12277,7 +12277,7 @@
         <v>325</v>
       </c>
       <c r="I259" s="0" t="s">
-        <v>1162</v>
+        <v>752</v>
       </c>
       <c r="J259" s="0">
         <v>478.95100000000002</v>
@@ -12309,7 +12309,7 @@
         <v>326</v>
       </c>
       <c r="I260" s="0" t="s">
-        <v>1163</v>
+        <v>753</v>
       </c>
       <c r="J260" s="0">
         <v>465.39179999999999</v>
@@ -12341,7 +12341,7 @@
         <v>327</v>
       </c>
       <c r="I261" s="0" t="s">
-        <v>1164</v>
+        <v>754</v>
       </c>
       <c r="J261" s="0">
         <v>463.80270000000002</v>
@@ -12373,7 +12373,7 @@
         <v>328</v>
       </c>
       <c r="I262" s="0" t="s">
-        <v>1165</v>
+        <v>755</v>
       </c>
       <c r="J262" s="0">
         <v>462.91269999999997</v>
@@ -12405,7 +12405,7 @@
         <v>329</v>
       </c>
       <c r="I263" s="0" t="s">
-        <v>1166</v>
+        <v>756</v>
       </c>
       <c r="J263" s="0">
         <v>445.06830000000002</v>
@@ -12437,7 +12437,7 @@
         <v>330</v>
       </c>
       <c r="I264" s="0" t="s">
-        <v>1167</v>
+        <v>757</v>
       </c>
       <c r="J264" s="0">
         <v>423.10739999999999</v>
@@ -12469,7 +12469,7 @@
         <v>331</v>
       </c>
       <c r="I265" s="0" t="s">
-        <v>1168</v>
+        <v>758</v>
       </c>
       <c r="J265" s="0">
         <v>402.7998</v>
@@ -12501,7 +12501,7 @@
         <v>332</v>
       </c>
       <c r="I266" s="0" t="s">
-        <v>1169</v>
+        <v>759</v>
       </c>
       <c r="J266" s="0">
         <v>372.56169999999997</v>
@@ -12533,7 +12533,7 @@
         <v>333</v>
       </c>
       <c r="I267" s="0" t="s">
-        <v>1170</v>
+        <v>760</v>
       </c>
       <c r="J267" s="0">
         <v>10030.694299999999</v>
@@ -12565,7 +12565,7 @@
         <v>334</v>
       </c>
       <c r="I268" s="0" t="s">
-        <v>1171</v>
+        <v>761</v>
       </c>
       <c r="J268" s="0">
         <v>6168.2295000000004</v>
@@ -12597,7 +12597,7 @@
         <v>335</v>
       </c>
       <c r="I269" s="0" t="s">
-        <v>1172</v>
+        <v>762</v>
       </c>
       <c r="J269" s="0">
         <v>961.54250000000002</v>
@@ -12629,7 +12629,7 @@
         <v>336</v>
       </c>
       <c r="I270" s="0" t="s">
-        <v>1173</v>
+        <v>763</v>
       </c>
       <c r="J270" s="0">
         <v>564.7491</v>
@@ -12661,7 +12661,7 @@
         <v>337</v>
       </c>
       <c r="I271" s="0" t="s">
-        <v>1174</v>
+        <v>764</v>
       </c>
       <c r="J271" s="0">
         <v>502.06450000000001</v>
@@ -12693,7 +12693,7 @@
         <v>338</v>
       </c>
       <c r="I272" s="0" t="s">
-        <v>1175</v>
+        <v>765</v>
       </c>
       <c r="J272" s="0">
         <v>498.90269999999998</v>
@@ -12725,7 +12725,7 @@
         <v>339</v>
       </c>
       <c r="I273" s="0" t="s">
-        <v>1176</v>
+        <v>766</v>
       </c>
       <c r="J273" s="0">
         <v>399.30579999999998</v>
@@ -12757,7 +12757,7 @@
         <v>340</v>
       </c>
       <c r="I274" s="0" t="s">
-        <v>1177</v>
+        <v>767</v>
       </c>
       <c r="J274" s="0">
         <v>395.6617</v>
@@ -12789,7 +12789,7 @@
         <v>341</v>
       </c>
       <c r="I275" s="0" t="s">
-        <v>1178</v>
+        <v>768</v>
       </c>
       <c r="J275" s="0">
         <v>374.79230000000001</v>
@@ -12821,7 +12821,7 @@
         <v>342</v>
       </c>
       <c r="I276" s="0" t="s">
-        <v>1179</v>
+        <v>769</v>
       </c>
       <c r="J276" s="0">
         <v>317.00749999999999</v>
@@ -12853,7 +12853,7 @@
         <v>343</v>
       </c>
       <c r="I277" s="0" t="s">
-        <v>1180</v>
+        <v>770</v>
       </c>
       <c r="J277" s="0">
         <v>312.89389999999997</v>
@@ -12885,7 +12885,7 @@
         <v>344</v>
       </c>
       <c r="I278" s="0" t="s">
-        <v>1181</v>
+        <v>771</v>
       </c>
       <c r="J278" s="0">
         <v>262.27510000000001</v>
@@ -12917,7 +12917,7 @@
         <v>345</v>
       </c>
       <c r="I279" s="0" t="s">
-        <v>1182</v>
+        <v>772</v>
       </c>
       <c r="J279" s="0">
         <v>10326.7256</v>
@@ -12949,7 +12949,7 @@
         <v>346</v>
       </c>
       <c r="I280" s="0" t="s">
-        <v>1183</v>
+        <v>773</v>
       </c>
       <c r="J280" s="0">
         <v>9974.2188000000006</v>
@@ -12981,7 +12981,7 @@
         <v>347</v>
       </c>
       <c r="I281" s="0" t="s">
-        <v>1184</v>
+        <v>774</v>
       </c>
       <c r="J281" s="0">
         <v>1148.0337</v>
@@ -13013,7 +13013,7 @@
         <v>348</v>
       </c>
       <c r="I282" s="0" t="s">
-        <v>1185</v>
+        <v>775</v>
       </c>
       <c r="J282" s="0">
         <v>914.7056</v>
@@ -13045,7 +13045,7 @@
         <v>349</v>
       </c>
       <c r="I283" s="0" t="s">
-        <v>1186</v>
+        <v>776</v>
       </c>
       <c r="J283" s="0">
         <v>483.39670000000001</v>
@@ -13077,7 +13077,7 @@
         <v>350</v>
       </c>
       <c r="I284" s="0" t="s">
-        <v>1187</v>
+        <v>777</v>
       </c>
       <c r="J284" s="0">
         <v>480.69290000000001</v>
@@ -13109,7 +13109,7 @@
         <v>351</v>
       </c>
       <c r="I285" s="0" t="s">
-        <v>1188</v>
+        <v>778</v>
       </c>
       <c r="J285" s="0">
         <v>477.11810000000003</v>
@@ -13141,7 +13141,7 @@
         <v>352</v>
       </c>
       <c r="I286" s="0" t="s">
-        <v>1189</v>
+        <v>779</v>
       </c>
       <c r="J286" s="0">
         <v>470.54579999999999</v>
@@ -13173,7 +13173,7 @@
         <v>353</v>
       </c>
       <c r="I287" s="0" t="s">
-        <v>1190</v>
+        <v>780</v>
       </c>
       <c r="J287" s="0">
         <v>463.21350000000001</v>
@@ -13205,7 +13205,7 @@
         <v>354</v>
       </c>
       <c r="I288" s="0" t="s">
-        <v>1191</v>
+        <v>781</v>
       </c>
       <c r="J288" s="0">
         <v>458.6345</v>
@@ -13237,7 +13237,7 @@
         <v>355</v>
       </c>
       <c r="I289" s="0" t="s">
-        <v>1192</v>
+        <v>782</v>
       </c>
       <c r="J289" s="0">
         <v>399.29669999999999</v>
@@ -13269,7 +13269,7 @@
         <v>356</v>
       </c>
       <c r="I290" s="0" t="s">
-        <v>1193</v>
+        <v>783</v>
       </c>
       <c r="J290" s="0">
         <v>349.30439999999999</v>
@@ -13301,7 +13301,7 @@
         <v>357</v>
       </c>
       <c r="I291" s="0" t="s">
-        <v>1194</v>
+        <v>784</v>
       </c>
       <c r="J291" s="0">
         <v>11249.227500000001</v>
@@ -13333,7 +13333,7 @@
         <v>358</v>
       </c>
       <c r="I292" s="0" t="s">
-        <v>1195</v>
+        <v>785</v>
       </c>
       <c r="J292" s="0">
         <v>6804.9902000000002</v>
@@ -13365,7 +13365,7 @@
         <v>361</v>
       </c>
       <c r="I293" s="0" t="s">
-        <v>1196</v>
+        <v>788</v>
       </c>
       <c r="J293" s="0">
         <v>547.55139999999994</v>
@@ -13397,7 +13397,7 @@
         <v>362</v>
       </c>
       <c r="I294" s="0" t="s">
-        <v>1197</v>
+        <v>789</v>
       </c>
       <c r="J294" s="0">
         <v>544.9031</v>
@@ -13429,7 +13429,7 @@
         <v>363</v>
       </c>
       <c r="I295" s="0" t="s">
-        <v>1198</v>
+        <v>790</v>
       </c>
       <c r="J295" s="0">
         <v>538.0435</v>
@@ -13461,7 +13461,7 @@
         <v>364</v>
       </c>
       <c r="I296" s="0" t="s">
-        <v>1199</v>
+        <v>791</v>
       </c>
       <c r="J296" s="0">
         <v>529.52170000000001</v>
@@ -13493,7 +13493,7 @@
         <v>365</v>
       </c>
       <c r="I297" s="0" t="s">
-        <v>1200</v>
+        <v>792</v>
       </c>
       <c r="J297" s="0">
         <v>429.88639999999998</v>
@@ -13525,7 +13525,7 @@
         <v>366</v>
       </c>
       <c r="I298" s="0" t="s">
-        <v>1201</v>
+        <v>793</v>
       </c>
       <c r="J298" s="0">
         <v>423.78399999999999</v>
@@ -13557,7 +13557,7 @@
         <v>367</v>
       </c>
       <c r="I299" s="0" t="s">
-        <v>1202</v>
+        <v>794</v>
       </c>
       <c r="J299" s="0">
         <v>374.9067</v>
@@ -13589,7 +13589,7 @@
         <v>368</v>
       </c>
       <c r="I300" s="0" t="s">
-        <v>1203</v>
+        <v>795</v>
       </c>
       <c r="J300" s="0">
         <v>327.96339999999998</v>
@@ -13621,7 +13621,7 @@
         <v>369</v>
       </c>
       <c r="I301" s="0" t="s">
-        <v>1204</v>
+        <v>796</v>
       </c>
       <c r="J301" s="0">
         <v>14917.853499999999</v>
@@ -13653,7 +13653,7 @@
         <v>370</v>
       </c>
       <c r="I302" s="0" t="s">
-        <v>1205</v>
+        <v>797</v>
       </c>
       <c r="J302" s="0">
         <v>10013.698200000001</v>
@@ -13685,7 +13685,7 @@
         <v>371</v>
       </c>
       <c r="I303" s="0" t="s">
-        <v>1206</v>
+        <v>798</v>
       </c>
       <c r="J303" s="0">
         <v>1332.2670000000001</v>
@@ -13717,7 +13717,7 @@
         <v>372</v>
       </c>
       <c r="I304" s="0" t="s">
-        <v>1207</v>
+        <v>799</v>
       </c>
       <c r="J304" s="0">
         <v>828.53430000000003</v>
@@ -13749,7 +13749,7 @@
         <v>373</v>
       </c>
       <c r="I305" s="0" t="s">
-        <v>1208</v>
+        <v>800</v>
       </c>
       <c r="J305" s="0">
         <v>578.22249999999997</v>
@@ -13781,7 +13781,7 @@
         <v>374</v>
       </c>
       <c r="I306" s="0" t="s">
-        <v>1209</v>
+        <v>801</v>
       </c>
       <c r="J306" s="0">
         <v>519.49069999999995</v>
@@ -13813,7 +13813,7 @@
         <v>375</v>
       </c>
       <c r="I307" s="0" t="s">
-        <v>1210</v>
+        <v>802</v>
       </c>
       <c r="J307" s="0">
         <v>488.8802</v>
@@ -13845,7 +13845,7 @@
         <v>376</v>
       </c>
       <c r="I308" s="0" t="s">
-        <v>1211</v>
+        <v>803</v>
       </c>
       <c r="J308" s="0">
         <v>479.72430000000003</v>
@@ -13877,7 +13877,7 @@
         <v>377</v>
       </c>
       <c r="I309" s="0" t="s">
-        <v>1212</v>
+        <v>804</v>
       </c>
       <c r="J309" s="0">
         <v>471.13209999999998</v>
@@ -13909,7 +13909,7 @@
         <v>378</v>
       </c>
       <c r="I310" s="0" t="s">
-        <v>1213</v>
+        <v>805</v>
       </c>
       <c r="J310" s="0">
         <v>465.73070000000001</v>
@@ -13941,7 +13941,7 @@
         <v>379</v>
       </c>
       <c r="I311" s="0" t="s">
-        <v>1214</v>
+        <v>806</v>
       </c>
       <c r="J311" s="0">
         <v>414.24799999999999</v>
@@ -13973,7 +13973,7 @@
         <v>380</v>
       </c>
       <c r="I312" s="0" t="s">
-        <v>1215</v>
+        <v>807</v>
       </c>
       <c r="J312" s="0">
         <v>382.2792</v>
@@ -14005,7 +14005,7 @@
         <v>381</v>
       </c>
       <c r="I313" s="0" t="s">
-        <v>1216</v>
+        <v>808</v>
       </c>
       <c r="J313" s="0">
         <v>13171.9355</v>
@@ -14037,7 +14037,7 @@
         <v>382</v>
       </c>
       <c r="I314" s="0" t="s">
-        <v>1217</v>
+        <v>809</v>
       </c>
       <c r="J314" s="0">
         <v>7219.6553000000004</v>
@@ -14069,7 +14069,7 @@
         <v>383</v>
       </c>
       <c r="I315" s="0" t="s">
-        <v>1218</v>
+        <v>810</v>
       </c>
       <c r="J315" s="0">
         <v>858.04020000000003</v>
@@ -14101,7 +14101,7 @@
         <v>384</v>
       </c>
       <c r="I316" s="0" t="s">
-        <v>1219</v>
+        <v>811</v>
       </c>
       <c r="J316" s="0">
         <v>548.43979999999999</v>
@@ -14133,7 +14133,7 @@
         <v>385</v>
       </c>
       <c r="I317" s="0" t="s">
-        <v>1220</v>
+        <v>812</v>
       </c>
       <c r="J317" s="0">
         <v>525.69830000000002</v>
@@ -14165,7 +14165,7 @@
         <v>386</v>
       </c>
       <c r="I318" s="0" t="s">
-        <v>1221</v>
+        <v>813</v>
       </c>
       <c r="J318" s="0">
         <v>474.8716</v>
@@ -14197,7 +14197,7 @@
         <v>387</v>
       </c>
       <c r="I319" s="0" t="s">
-        <v>1222</v>
+        <v>814</v>
       </c>
       <c r="J319" s="0">
         <v>453.47840000000002</v>
@@ -14229,7 +14229,7 @@
         <v>388</v>
       </c>
       <c r="I320" s="0" t="s">
-        <v>1223</v>
+        <v>815</v>
       </c>
       <c r="J320" s="0">
         <v>439.9545</v>
@@ -14261,7 +14261,7 @@
         <v>389</v>
       </c>
       <c r="I321" s="0" t="s">
-        <v>1224</v>
+        <v>816</v>
       </c>
       <c r="J321" s="0">
         <v>432.7242</v>
@@ -14293,7 +14293,7 @@
         <v>390</v>
       </c>
       <c r="I322" s="0" t="s">
-        <v>1225</v>
+        <v>817</v>
       </c>
       <c r="J322" s="0">
         <v>427.84280000000001</v>
@@ -14325,7 +14325,7 @@
         <v>391</v>
       </c>
       <c r="I323" s="0" t="s">
-        <v>1226</v>
+        <v>818</v>
       </c>
       <c r="J323" s="0">
         <v>406.00720000000001</v>
@@ -14357,7 +14357,7 @@
         <v>392</v>
       </c>
       <c r="I324" s="0" t="s">
-        <v>1227</v>
+        <v>819</v>
       </c>
       <c r="J324" s="0">
         <v>368.30669999999998</v>
@@ -14389,7 +14389,7 @@
         <v>393</v>
       </c>
       <c r="I325" s="0" t="s">
-        <v>1228</v>
+        <v>820</v>
       </c>
       <c r="J325" s="0">
         <v>10183.9961</v>
@@ -14421,7 +14421,7 @@
         <v>394</v>
       </c>
       <c r="I326" s="0" t="s">
-        <v>1229</v>
+        <v>821</v>
       </c>
       <c r="J326" s="0">
         <v>9260.2188000000006</v>
@@ -14453,7 +14453,7 @@
         <v>395</v>
       </c>
       <c r="I327" s="0" t="s">
-        <v>1230</v>
+        <v>822</v>
       </c>
       <c r="J327" s="0">
         <v>1286.2859000000001</v>
@@ -14485,7 +14485,7 @@
         <v>396</v>
       </c>
       <c r="I328" s="0" t="s">
-        <v>1231</v>
+        <v>823</v>
       </c>
       <c r="J328" s="0">
         <v>1212.9492</v>
@@ -14517,7 +14517,7 @@
         <v>398</v>
       </c>
       <c r="I329" s="0" t="s">
-        <v>1232</v>
+        <v>825</v>
       </c>
       <c r="J329" s="0">
         <v>423.24180000000001</v>
@@ -14549,7 +14549,7 @@
         <v>399</v>
       </c>
       <c r="I330" s="0" t="s">
-        <v>1233</v>
+        <v>826</v>
       </c>
       <c r="J330" s="0">
         <v>408.47359999999998</v>
@@ -14581,7 +14581,7 @@
         <v>400</v>
       </c>
       <c r="I331" s="0" t="s">
-        <v>1234</v>
+        <v>827</v>
       </c>
       <c r="J331" s="0">
         <v>405.3897</v>
@@ -14613,7 +14613,7 @@
         <v>401</v>
       </c>
       <c r="I332" s="0" t="s">
-        <v>1235</v>
+        <v>828</v>
       </c>
       <c r="J332" s="0">
         <v>379.12220000000002</v>
@@ -14645,7 +14645,7 @@
         <v>402</v>
       </c>
       <c r="I333" s="0" t="s">
-        <v>1236</v>
+        <v>829</v>
       </c>
       <c r="J333" s="0">
         <v>371.36880000000002</v>
@@ -14677,7 +14677,7 @@
         <v>403</v>
       </c>
       <c r="I334" s="0" t="s">
-        <v>1237</v>
+        <v>830</v>
       </c>
       <c r="J334" s="0">
         <v>350.1583</v>
@@ -14709,7 +14709,7 @@
         <v>404</v>
       </c>
       <c r="I335" s="0" t="s">
-        <v>1238</v>
+        <v>831</v>
       </c>
       <c r="J335" s="0">
         <v>338.19600000000003</v>
@@ -14741,7 +14741,7 @@
         <v>405</v>
       </c>
       <c r="I336" s="0" t="s">
-        <v>1239</v>
+        <v>832</v>
       </c>
       <c r="J336" s="0">
         <v>10894.9053</v>
@@ -14773,7 +14773,7 @@
         <v>406</v>
       </c>
       <c r="I337" s="0" t="s">
-        <v>1240</v>
+        <v>833</v>
       </c>
       <c r="J337" s="0">
         <v>5662.0551999999998</v>
@@ -14805,7 +14805,7 @@
         <v>407</v>
       </c>
       <c r="I338" s="0" t="s">
-        <v>1241</v>
+        <v>834</v>
       </c>
       <c r="J338" s="0">
         <v>1945.5608</v>
@@ -14837,7 +14837,7 @@
         <v>408</v>
       </c>
       <c r="I339" s="0" t="s">
-        <v>1242</v>
+        <v>835</v>
       </c>
       <c r="J339" s="0">
         <v>1073.6666</v>
@@ -14869,7 +14869,7 @@
         <v>409</v>
       </c>
       <c r="I340" s="0" t="s">
-        <v>1243</v>
+        <v>836</v>
       </c>
       <c r="J340" s="0">
         <v>513.65530000000001</v>
@@ -14901,7 +14901,7 @@
         <v>410</v>
       </c>
       <c r="I341" s="0" t="s">
-        <v>1244</v>
+        <v>837</v>
       </c>
       <c r="J341" s="0">
         <v>457.6961</v>
@@ -14933,7 +14933,7 @@
         <v>411</v>
       </c>
       <c r="I342" s="0" t="s">
-        <v>1245</v>
+        <v>838</v>
       </c>
       <c r="J342" s="0">
         <v>456.3168</v>
@@ -14965,7 +14965,7 @@
         <v>412</v>
       </c>
       <c r="I343" s="0" t="s">
-        <v>1246</v>
+        <v>839</v>
       </c>
       <c r="J343" s="0">
         <v>454.07369999999997</v>
@@ -14997,7 +14997,7 @@
         <v>413</v>
       </c>
       <c r="I344" s="0" t="s">
-        <v>1247</v>
+        <v>840</v>
       </c>
       <c r="J344" s="0">
         <v>429.38220000000001</v>
@@ -15029,7 +15029,7 @@
         <v>414</v>
       </c>
       <c r="I345" s="0" t="s">
-        <v>1248</v>
+        <v>841</v>
       </c>
       <c r="J345" s="0">
         <v>386.53370000000001</v>
@@ -15061,7 +15061,7 @@
         <v>415</v>
       </c>
       <c r="I346" s="0" t="s">
-        <v>1249</v>
+        <v>842</v>
       </c>
       <c r="J346" s="0">
         <v>359.30450000000002</v>
@@ -15093,7 +15093,7 @@
         <v>416</v>
       </c>
       <c r="I347" s="0" t="s">
-        <v>1250</v>
+        <v>843</v>
       </c>
       <c r="J347" s="0">
         <v>330.99799999999999</v>
@@ -15125,7 +15125,7 @@
         <v>417</v>
       </c>
       <c r="I348" s="0" t="s">
-        <v>1251</v>
+        <v>844</v>
       </c>
       <c r="J348" s="0">
         <v>11140.4043</v>
@@ -15157,7 +15157,7 @@
         <v>418</v>
       </c>
       <c r="I349" s="0" t="s">
-        <v>1252</v>
+        <v>845</v>
       </c>
       <c r="J349" s="0">
         <v>7539.1777000000002</v>
@@ -15189,7 +15189,7 @@
         <v>419</v>
       </c>
       <c r="I350" s="0" t="s">
-        <v>1253</v>
+        <v>846</v>
       </c>
       <c r="J350" s="0">
         <v>1166.9911999999999</v>
@@ -15221,7 +15221,7 @@
         <v>420</v>
       </c>
       <c r="I351" s="0" t="s">
-        <v>1254</v>
+        <v>847</v>
       </c>
       <c r="J351" s="0">
         <v>968.274</v>
@@ -15253,7 +15253,7 @@
         <v>421</v>
       </c>
       <c r="I352" s="0" t="s">
-        <v>1255</v>
+        <v>848</v>
       </c>
       <c r="J352" s="0">
         <v>590.66909999999996</v>
@@ -15285,7 +15285,7 @@
         <v>422</v>
       </c>
       <c r="I353" s="0" t="s">
-        <v>1256</v>
+        <v>849</v>
       </c>
       <c r="J353" s="0">
         <v>502.17599999999999</v>
@@ -15317,7 +15317,7 @@
         <v>423</v>
       </c>
       <c r="I354" s="0" t="s">
-        <v>1257</v>
+        <v>850</v>
       </c>
       <c r="J354" s="0">
         <v>479.93529999999998</v>
@@ -15349,7 +15349,7 @@
         <v>424</v>
       </c>
       <c r="I355" s="0" t="s">
-        <v>1258</v>
+        <v>851</v>
       </c>
       <c r="J355" s="0">
         <v>469.60969999999998</v>
@@ -15381,7 +15381,7 @@
         <v>425</v>
       </c>
       <c r="I356" s="0" t="s">
-        <v>1259</v>
+        <v>852</v>
       </c>
       <c r="J356" s="0">
         <v>451.56819999999999</v>
@@ -15413,7 +15413,7 @@
         <v>426</v>
       </c>
       <c r="I357" s="0" t="s">
-        <v>1260</v>
+        <v>853</v>
       </c>
       <c r="J357" s="0">
         <v>412.2346</v>
@@ -15445,7 +15445,7 @@
         <v>427</v>
       </c>
       <c r="I358" s="0" t="s">
-        <v>1261</v>
+        <v>854</v>
       </c>
       <c r="J358" s="0">
         <v>401.46249999999998</v>
@@ -15477,7 +15477,7 @@
         <v>428</v>
       </c>
       <c r="I359" s="0" t="s">
-        <v>1262</v>
+        <v>855</v>
       </c>
       <c r="J359" s="0">
         <v>323.00450000000001</v>
@@ -15509,7 +15509,7 @@
         <v>429</v>
       </c>
       <c r="I360" s="0" t="s">
-        <v>1263</v>
+        <v>856</v>
       </c>
       <c r="J360" s="0">
         <v>11573.126</v>
@@ -15541,7 +15541,7 @@
         <v>430</v>
       </c>
       <c r="I361" s="0" t="s">
-        <v>1264</v>
+        <v>857</v>
       </c>
       <c r="J361" s="0">
         <v>6620.0068000000001</v>
@@ -15573,7 +15573,7 @@
         <v>431</v>
       </c>
       <c r="I362" s="0" t="s">
-        <v>1265</v>
+        <v>858</v>
       </c>
       <c r="J362" s="0">
         <v>751.08780000000002</v>
@@ -15605,7 +15605,7 @@
         <v>432</v>
       </c>
       <c r="I363" s="0" t="s">
-        <v>1266</v>
+        <v>859</v>
       </c>
       <c r="J363" s="0">
         <v>745.37040000000002</v>
@@ -15637,7 +15637,7 @@
         <v>433</v>
       </c>
       <c r="I364" s="0" t="s">
-        <v>1267</v>
+        <v>860</v>
       </c>
       <c r="J364" s="0">
         <v>347.99090000000001</v>
@@ -15669,7 +15669,7 @@
         <v>434</v>
       </c>
       <c r="I365" s="0" t="s">
-        <v>1268</v>
+        <v>861</v>
       </c>
       <c r="J365" s="0">
         <v>332.82709999999997</v>
@@ -15701,7 +15701,7 @@
         <v>435</v>
       </c>
       <c r="I366" s="0" t="s">
-        <v>1269</v>
+        <v>862</v>
       </c>
       <c r="J366" s="0">
         <v>300.09730000000002</v>
@@ -15733,7 +15733,7 @@
         <v>436</v>
       </c>
       <c r="I367" s="0" t="s">
-        <v>1270</v>
+        <v>863</v>
       </c>
       <c r="J367" s="0">
         <v>267.48480000000001</v>
@@ -15765,7 +15765,7 @@
         <v>437</v>
       </c>
       <c r="I368" s="0" t="s">
-        <v>1271</v>
+        <v>864</v>
       </c>
       <c r="J368" s="0">
         <v>247.57060000000001</v>
@@ -15797,7 +15797,7 @@
         <v>438</v>
       </c>
       <c r="I369" s="0" t="s">
-        <v>1272</v>
+        <v>865</v>
       </c>
       <c r="J369" s="0">
         <v>241.20079999999999</v>
@@ -15829,7 +15829,7 @@
         <v>439</v>
       </c>
       <c r="I370" s="0" t="s">
-        <v>1273</v>
+        <v>866</v>
       </c>
       <c r="J370" s="0">
         <v>224.6387</v>
@@ -15861,7 +15861,7 @@
         <v>440</v>
       </c>
       <c r="I371" s="0" t="s">
-        <v>1274</v>
+        <v>867</v>
       </c>
       <c r="J371" s="0">
         <v>196.59559999999999</v>
@@ -15893,7 +15893,7 @@
         <v>441</v>
       </c>
       <c r="I372" s="0" t="s">
-        <v>1275</v>
+        <v>868</v>
       </c>
       <c r="J372" s="0">
         <v>9005.0449000000008</v>
@@ -15925,7 +15925,7 @@
         <v>442</v>
       </c>
       <c r="I373" s="0" t="s">
-        <v>1276</v>
+        <v>869</v>
       </c>
       <c r="J373" s="0">
         <v>8991.1543000000001</v>
@@ -15957,7 +15957,7 @@
         <v>443</v>
       </c>
       <c r="I374" s="0" t="s">
-        <v>1277</v>
+        <v>870</v>
       </c>
       <c r="J374" s="0">
         <v>1060.6902</v>
@@ -15989,7 +15989,7 @@
         <v>444</v>
       </c>
       <c r="I375" s="0" t="s">
-        <v>1278</v>
+        <v>871</v>
       </c>
       <c r="J375" s="0">
         <v>873.68520000000001</v>
@@ -16021,7 +16021,7 @@
         <v>445</v>
       </c>
       <c r="I376" s="0" t="s">
-        <v>1279</v>
+        <v>872</v>
       </c>
       <c r="J376" s="0">
         <v>492.66989999999999</v>
@@ -16053,7 +16053,7 @@
         <v>446</v>
       </c>
       <c r="I377" s="0" t="s">
-        <v>1280</v>
+        <v>873</v>
       </c>
       <c r="J377" s="0">
         <v>479.0992</v>
@@ -16085,7 +16085,7 @@
         <v>447</v>
       </c>
       <c r="I378" s="0" t="s">
-        <v>1281</v>
+        <v>874</v>
       </c>
       <c r="J378" s="0">
         <v>473.75420000000003</v>
@@ -16117,7 +16117,7 @@
         <v>448</v>
       </c>
       <c r="I379" s="0" t="s">
-        <v>1282</v>
+        <v>875</v>
       </c>
       <c r="J379" s="0">
         <v>451.01459999999997</v>
@@ -16149,7 +16149,7 @@
         <v>449</v>
       </c>
       <c r="I380" s="0" t="s">
-        <v>1283</v>
+        <v>876</v>
       </c>
       <c r="J380" s="0">
         <v>445.8254</v>
@@ -16181,7 +16181,7 @@
         <v>450</v>
       </c>
       <c r="I381" s="0" t="s">
-        <v>1284</v>
+        <v>877</v>
       </c>
       <c r="J381" s="0">
         <v>416.5324</v>
@@ -16213,7 +16213,7 @@
         <v>451</v>
       </c>
       <c r="I382" s="0" t="s">
-        <v>1285</v>
+        <v>878</v>
       </c>
       <c r="J382" s="0">
         <v>410.74439999999999</v>
@@ -16245,7 +16245,7 @@
         <v>452</v>
       </c>
       <c r="I383" s="0" t="s">
-        <v>1286</v>
+        <v>879</v>
       </c>
       <c r="J383" s="0">
         <v>398.16070000000002</v>
@@ -16277,7 +16277,7 @@
         <v>453</v>
       </c>
       <c r="I384" s="0" t="s">
-        <v>1287</v>
+        <v>880</v>
       </c>
       <c r="J384" s="0">
         <v>11446.293</v>
@@ -16309,7 +16309,7 @@
         <v>454</v>
       </c>
       <c r="I385" s="0" t="s">
-        <v>1288</v>
+        <v>881</v>
       </c>
       <c r="J385" s="0">
         <v>7034.3638000000001</v>
@@ -16341,7 +16341,7 @@
         <v>457</v>
       </c>
       <c r="I386" s="0" t="s">
-        <v>1289</v>
+        <v>884</v>
       </c>
       <c r="J386" s="0">
         <v>544.20960000000002</v>
@@ -16373,7 +16373,7 @@
         <v>458</v>
       </c>
       <c r="I387" s="0" t="s">
-        <v>1290</v>
+        <v>885</v>
       </c>
       <c r="J387" s="0">
         <v>530.34780000000001</v>
@@ -16405,7 +16405,7 @@
         <v>459</v>
       </c>
       <c r="I388" s="0" t="s">
-        <v>1291</v>
+        <v>886</v>
       </c>
       <c r="J388" s="0">
         <v>496.8383</v>
@@ -16437,7 +16437,7 @@
         <v>460</v>
       </c>
       <c r="I389" s="0" t="s">
-        <v>1292</v>
+        <v>887</v>
       </c>
       <c r="J389" s="0">
         <v>456.82279999999997</v>
@@ -16469,7 +16469,7 @@
         <v>461</v>
       </c>
       <c r="I390" s="0" t="s">
-        <v>1293</v>
+        <v>888</v>
       </c>
       <c r="J390" s="0">
         <v>430.56229999999999</v>
@@ -16501,7 +16501,7 @@
         <v>462</v>
       </c>
       <c r="I391" s="0" t="s">
-        <v>1294</v>
+        <v>889</v>
       </c>
       <c r="J391" s="0">
         <v>394.98270000000002</v>
@@ -16533,7 +16533,7 @@
         <v>463</v>
       </c>
       <c r="I392" s="0" t="s">
-        <v>1295</v>
+        <v>890</v>
       </c>
       <c r="J392" s="0">
         <v>390.7165</v>
@@ -16565,7 +16565,7 @@
         <v>465</v>
       </c>
       <c r="I393" s="0" t="s">
-        <v>1296</v>
+        <v>892</v>
       </c>
       <c r="J393" s="0">
         <v>11910.3838</v>
@@ -16597,7 +16597,7 @@
         <v>466</v>
       </c>
       <c r="I394" s="0" t="s">
-        <v>1297</v>
+        <v>893</v>
       </c>
       <c r="J394" s="0">
         <v>7360.2744000000002</v>
@@ -16629,7 +16629,7 @@
         <v>467</v>
       </c>
       <c r="I395" s="0" t="s">
-        <v>1298</v>
+        <v>894</v>
       </c>
       <c r="J395" s="0">
         <v>712.87210000000005</v>
@@ -16661,7 +16661,7 @@
         <v>469</v>
       </c>
       <c r="I396" s="0" t="s">
-        <v>1299</v>
+        <v>896</v>
       </c>
       <c r="J396" s="0">
         <v>462.625</v>
@@ -16693,7 +16693,7 @@
         <v>470</v>
       </c>
       <c r="I397" s="0" t="s">
-        <v>1300</v>
+        <v>897</v>
       </c>
       <c r="J397" s="0">
         <v>430.88380000000001</v>
@@ -16725,7 +16725,7 @@
         <v>471</v>
       </c>
       <c r="I398" s="0" t="s">
-        <v>1301</v>
+        <v>898</v>
       </c>
       <c r="J398" s="0">
         <v>412.29090000000002</v>
@@ -16757,7 +16757,7 @@
         <v>472</v>
       </c>
       <c r="I399" s="0" t="s">
-        <v>1302</v>
+        <v>899</v>
       </c>
       <c r="J399" s="0">
         <v>401.78739999999999</v>
@@ -16789,7 +16789,7 @@
         <v>473</v>
       </c>
       <c r="I400" s="0" t="s">
-        <v>1303</v>
+        <v>900</v>
       </c>
       <c r="J400" s="0">
         <v>380.73540000000003</v>
@@ -16821,7 +16821,7 @@
         <v>474</v>
       </c>
       <c r="I401" s="0" t="s">
-        <v>1304</v>
+        <v>901</v>
       </c>
       <c r="J401" s="0">
         <v>309.23020000000002</v>
@@ -16853,7 +16853,7 @@
         <v>475</v>
       </c>
       <c r="I402" s="0" t="s">
-        <v>1305</v>
+        <v>902</v>
       </c>
       <c r="J402" s="0">
         <v>275.06909999999999</v>
@@ -16885,7 +16885,7 @@
         <v>476</v>
       </c>
       <c r="I403" s="0" t="s">
-        <v>1306</v>
+        <v>903</v>
       </c>
       <c r="J403" s="0">
         <v>206.4333</v>

--- a/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="231012" uniqueCount="1307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="245524" uniqueCount="1307">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="245524" uniqueCount="1307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="252780" uniqueCount="1307">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="252780" uniqueCount="1307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="260036" uniqueCount="1307">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="260036" uniqueCount="1307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="292688" uniqueCount="1307">
   <si>
     <t>Year</t>
   </si>
@@ -3983,16 +3983,16 @@
   <dimension ref="A1:J427"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.08984375" customWidth="true"/>
-    <col min="2" max="2" width="6.54296875" customWidth="true"/>
-    <col min="3" max="3" width="10.36328125" customWidth="true"/>
-    <col min="4" max="4" width="16.36328125" customWidth="true"/>
-    <col min="5" max="5" width="11.81640625" customWidth="true"/>
-    <col min="6" max="6" width="11.90625" customWidth="true"/>
-    <col min="7" max="7" width="7.90625" customWidth="true"/>
-    <col min="8" max="8" width="36.26953125" customWidth="true"/>
-    <col min="9" max="9" width="195.7265625" customWidth="true"/>
-    <col min="10" max="10" width="10.453125" customWidth="true"/>
+    <col min="1" max="1" width="14.85546875" customWidth="true"/>
+    <col min="2" max="2" width="7" customWidth="true"/>
+    <col min="3" max="3" width="11.28515625" customWidth="true"/>
+    <col min="4" max="4" width="17.28515625" customWidth="true"/>
+    <col min="5" max="5" width="12.7109375" customWidth="true"/>
+    <col min="6" max="6" width="13" customWidth="true"/>
+    <col min="7" max="7" width="8.5703125" customWidth="true"/>
+    <col min="8" max="8" width="37.42578125" customWidth="true"/>
+    <col min="9" max="9" width="203.7109375" customWidth="true"/>
+    <col min="10" max="10" width="10.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="292688" uniqueCount="1307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="307200" uniqueCount="1307">
   <si>
     <t>Year</t>
   </si>
@@ -3991,7 +3991,7 @@
     <col min="6" max="6" width="13" customWidth="true"/>
     <col min="7" max="7" width="8.5703125" customWidth="true"/>
     <col min="8" max="8" width="37.42578125" customWidth="true"/>
-    <col min="9" max="9" width="203.7109375" customWidth="true"/>
+    <col min="9" max="9" width="175.28515625" customWidth="true"/>
     <col min="10" max="10" width="10.7109375" customWidth="true"/>
   </cols>
   <sheetData>
@@ -4053,7 +4053,7 @@
         <v>55</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>478</v>
+        <v>905</v>
       </c>
       <c r="J2" s="0">
         <v>11688.002</v>
@@ -4085,7 +4085,7 @@
         <v>57</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>480</v>
+        <v>906</v>
       </c>
       <c r="J3" s="0">
         <v>935.94889999999998</v>
@@ -4117,7 +4117,7 @@
         <v>58</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>481</v>
+        <v>907</v>
       </c>
       <c r="J4" s="0">
         <v>880.38310000000001</v>
@@ -4149,7 +4149,7 @@
         <v>59</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>482</v>
+        <v>908</v>
       </c>
       <c r="J5" s="0">
         <v>502.106</v>
@@ -4181,7 +4181,7 @@
         <v>60</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>483</v>
+        <v>909</v>
       </c>
       <c r="J6" s="0">
         <v>466.17020000000002</v>
@@ -4213,7 +4213,7 @@
         <v>61</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>484</v>
+        <v>910</v>
       </c>
       <c r="J7" s="0">
         <v>453.3066</v>
@@ -4245,7 +4245,7 @@
         <v>62</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>485</v>
+        <v>911</v>
       </c>
       <c r="J8" s="0">
         <v>443.37130000000002</v>
@@ -4277,7 +4277,7 @@
         <v>63</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>486</v>
+        <v>912</v>
       </c>
       <c r="J9" s="0">
         <v>438.5403</v>
@@ -4309,7 +4309,7 @@
         <v>64</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>487</v>
+        <v>913</v>
       </c>
       <c r="J10" s="0">
         <v>427.42660000000001</v>
@@ -4341,7 +4341,7 @@
         <v>66</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>489</v>
+        <v>914</v>
       </c>
       <c r="J11" s="0">
         <v>359.1311</v>
@@ -4373,7 +4373,7 @@
         <v>67</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>490</v>
+        <v>915</v>
       </c>
       <c r="J12" s="0">
         <v>15177.4365</v>
@@ -4405,7 +4405,7 @@
         <v>68</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>491</v>
+        <v>916</v>
       </c>
       <c r="J13" s="0">
         <v>10441.9121</v>
@@ -4437,7 +4437,7 @@
         <v>69</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>492</v>
+        <v>917</v>
       </c>
       <c r="J14" s="0">
         <v>1168.5962</v>
@@ -4469,7 +4469,7 @@
         <v>70</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>493</v>
+        <v>918</v>
       </c>
       <c r="J15" s="0">
         <v>1026.5851</v>
@@ -4501,7 +4501,7 @@
         <v>71</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>494</v>
+        <v>919</v>
       </c>
       <c r="J16" s="0">
         <v>551.72749999999996</v>
@@ -4533,7 +4533,7 @@
         <v>72</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>495</v>
+        <v>920</v>
       </c>
       <c r="J17" s="0">
         <v>484.46609999999998</v>
@@ -4565,7 +4565,7 @@
         <v>73</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>496</v>
+        <v>921</v>
       </c>
       <c r="J18" s="0">
         <v>462.44240000000002</v>
@@ -4597,7 +4597,7 @@
         <v>74</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>497</v>
+        <v>922</v>
       </c>
       <c r="J19" s="0">
         <v>438.6388</v>
@@ -4629,7 +4629,7 @@
         <v>75</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>498</v>
+        <v>923</v>
       </c>
       <c r="J20" s="0">
         <v>433.1481</v>
@@ -4661,7 +4661,7 @@
         <v>76</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>499</v>
+        <v>924</v>
       </c>
       <c r="J21" s="0">
         <v>417.18799999999999</v>
@@ -4693,7 +4693,7 @@
         <v>77</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>500</v>
+        <v>925</v>
       </c>
       <c r="J22" s="0">
         <v>403.36680000000001</v>
@@ -4725,7 +4725,7 @@
         <v>78</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>501</v>
+        <v>926</v>
       </c>
       <c r="J23" s="0">
         <v>344.44220000000001</v>
@@ -4757,7 +4757,7 @@
         <v>79</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>502</v>
+        <v>927</v>
       </c>
       <c r="J24" s="0">
         <v>13941.7637</v>
@@ -4789,7 +4789,7 @@
         <v>80</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>503</v>
+        <v>928</v>
       </c>
       <c r="J25" s="0">
         <v>10106.319299999999</v>
@@ -4821,7 +4821,7 @@
         <v>83</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>506</v>
+        <v>929</v>
       </c>
       <c r="J26" s="0">
         <v>538.54449999999997</v>
@@ -4853,7 +4853,7 @@
         <v>84</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>507</v>
+        <v>930</v>
       </c>
       <c r="J27" s="0">
         <v>528.50789999999995</v>
@@ -4885,7 +4885,7 @@
         <v>85</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>508</v>
+        <v>931</v>
       </c>
       <c r="J28" s="0">
         <v>515.40830000000005</v>
@@ -4917,7 +4917,7 @@
         <v>86</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>509</v>
+        <v>932</v>
       </c>
       <c r="J29" s="0">
         <v>505.25689999999997</v>
@@ -4949,7 +4949,7 @@
         <v>87</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>510</v>
+        <v>933</v>
       </c>
       <c r="J30" s="0">
         <v>428.78109999999998</v>
@@ -4981,7 +4981,7 @@
         <v>88</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>511</v>
+        <v>934</v>
       </c>
       <c r="J31" s="0">
         <v>373.29050000000001</v>
@@ -5013,7 +5013,7 @@
         <v>89</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>512</v>
+        <v>935</v>
       </c>
       <c r="J32" s="0">
         <v>357.77280000000002</v>
@@ -5045,7 +5045,7 @@
         <v>90</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>513</v>
+        <v>936</v>
       </c>
       <c r="J33" s="0">
         <v>326.51060000000001</v>
@@ -5077,7 +5077,7 @@
         <v>91</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>514</v>
+        <v>937</v>
       </c>
       <c r="J34" s="0">
         <v>12781.4072</v>
@@ -5109,7 +5109,7 @@
         <v>93</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>516</v>
+        <v>938</v>
       </c>
       <c r="J35" s="0">
         <v>1452.7743</v>
@@ -5141,7 +5141,7 @@
         <v>94</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>517</v>
+        <v>939</v>
       </c>
       <c r="J36" s="0">
         <v>1450.1411000000001</v>
@@ -5173,7 +5173,7 @@
         <v>95</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>518</v>
+        <v>940</v>
       </c>
       <c r="J37" s="0">
         <v>473.58769999999998</v>
@@ -5205,7 +5205,7 @@
         <v>96</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>519</v>
+        <v>941</v>
       </c>
       <c r="J38" s="0">
         <v>468.9753</v>
@@ -5237,7 +5237,7 @@
         <v>97</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>520</v>
+        <v>942</v>
       </c>
       <c r="J39" s="0">
         <v>453.3648</v>
@@ -5269,7 +5269,7 @@
         <v>98</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>521</v>
+        <v>943</v>
       </c>
       <c r="J40" s="0">
         <v>435.75220000000002</v>
@@ -5301,7 +5301,7 @@
         <v>99</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>522</v>
+        <v>944</v>
       </c>
       <c r="J41" s="0">
         <v>434.1336</v>
@@ -5333,7 +5333,7 @@
         <v>100</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>523</v>
+        <v>945</v>
       </c>
       <c r="J42" s="0">
         <v>429.1137</v>
@@ -5365,7 +5365,7 @@
         <v>101</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>524</v>
+        <v>946</v>
       </c>
       <c r="J43" s="0">
         <v>392.56209999999999</v>
@@ -5397,7 +5397,7 @@
         <v>102</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>525</v>
+        <v>947</v>
       </c>
       <c r="J44" s="0">
         <v>366.25650000000002</v>
@@ -5429,7 +5429,7 @@
         <v>103</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>526</v>
+        <v>948</v>
       </c>
       <c r="J45" s="0">
         <v>11646.511699999999</v>
@@ -5461,7 +5461,7 @@
         <v>104</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>527</v>
+        <v>949</v>
       </c>
       <c r="J46" s="0">
         <v>7558.6841000000004</v>
@@ -5493,7 +5493,7 @@
         <v>105</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>528</v>
+        <v>950</v>
       </c>
       <c r="J47" s="0">
         <v>1293.2311</v>
@@ -5525,7 +5525,7 @@
         <v>106</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>529</v>
+        <v>951</v>
       </c>
       <c r="J48" s="0">
         <v>1168.5597</v>
@@ -5557,7 +5557,7 @@
         <v>107</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>530</v>
+        <v>952</v>
       </c>
       <c r="J49" s="0">
         <v>531.21609999999998</v>
@@ -5589,7 +5589,7 @@
         <v>108</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>531</v>
+        <v>953</v>
       </c>
       <c r="J50" s="0">
         <v>470.07299999999998</v>
@@ -5621,7 +5621,7 @@
         <v>109</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>532</v>
+        <v>954</v>
       </c>
       <c r="J51" s="0">
         <v>439.15929999999997</v>
@@ -5653,7 +5653,7 @@
         <v>110</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>533</v>
+        <v>955</v>
       </c>
       <c r="J52" s="0">
         <v>424.38709999999998</v>
@@ -5685,7 +5685,7 @@
         <v>111</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>534</v>
+        <v>956</v>
       </c>
       <c r="J53" s="0">
         <v>419.4384</v>
@@ -5717,7 +5717,7 @@
         <v>112</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>535</v>
+        <v>957</v>
       </c>
       <c r="J54" s="0">
         <v>413.99000000000001</v>
@@ -5749,7 +5749,7 @@
         <v>113</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>536</v>
+        <v>958</v>
       </c>
       <c r="J55" s="0">
         <v>408.73599999999999</v>
@@ -5781,7 +5781,7 @@
         <v>114</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>537</v>
+        <v>959</v>
       </c>
       <c r="J56" s="0">
         <v>408.7253</v>
@@ -5813,7 +5813,7 @@
         <v>115</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>538</v>
+        <v>960</v>
       </c>
       <c r="J57" s="0">
         <v>11876.8555</v>
@@ -5845,7 +5845,7 @@
         <v>116</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>539</v>
+        <v>961</v>
       </c>
       <c r="J58" s="0">
         <v>10286.9082</v>
@@ -5877,7 +5877,7 @@
         <v>117</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>540</v>
+        <v>962</v>
       </c>
       <c r="J59" s="0">
         <v>1060.3289</v>
@@ -5909,7 +5909,7 @@
         <v>118</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>541</v>
+        <v>963</v>
       </c>
       <c r="J60" s="0">
         <v>1004.1268</v>
@@ -5941,7 +5941,7 @@
         <v>119</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>542</v>
+        <v>964</v>
       </c>
       <c r="J61" s="0">
         <v>497.2799</v>
@@ -5973,7 +5973,7 @@
         <v>120</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>543</v>
+        <v>965</v>
       </c>
       <c r="J62" s="0">
         <v>485.87290000000002</v>
@@ -6005,7 +6005,7 @@
         <v>121</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>544</v>
+        <v>966</v>
       </c>
       <c r="J63" s="0">
         <v>429.8492</v>
@@ -6037,7 +6037,7 @@
         <v>122</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>545</v>
+        <v>967</v>
       </c>
       <c r="J64" s="0">
         <v>425.51229999999998</v>
@@ -6069,7 +6069,7 @@
         <v>123</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>546</v>
+        <v>968</v>
       </c>
       <c r="J65" s="0">
         <v>396.25139999999999</v>
@@ -6101,7 +6101,7 @@
         <v>124</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>547</v>
+        <v>969</v>
       </c>
       <c r="J66" s="0">
         <v>392.3723</v>
@@ -6133,7 +6133,7 @@
         <v>125</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>548</v>
+        <v>970</v>
       </c>
       <c r="J67" s="0">
         <v>351.54930000000002</v>
@@ -6165,7 +6165,7 @@
         <v>126</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>549</v>
+        <v>971</v>
       </c>
       <c r="J68" s="0">
         <v>348.02690000000001</v>
@@ -6197,7 +6197,7 @@
         <v>127</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>550</v>
+        <v>972</v>
       </c>
       <c r="J69" s="0">
         <v>12171.997100000001</v>
@@ -6229,7 +6229,7 @@
         <v>128</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>551</v>
+        <v>973</v>
       </c>
       <c r="J70" s="0">
         <v>6862.1084000000001</v>
@@ -6261,7 +6261,7 @@
         <v>129</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>552</v>
+        <v>974</v>
       </c>
       <c r="J71" s="0">
         <v>1099.6836000000001</v>
@@ -6293,7 +6293,7 @@
         <v>130</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>553</v>
+        <v>975</v>
       </c>
       <c r="J72" s="0">
         <v>752.58019999999999</v>
@@ -6325,7 +6325,7 @@
         <v>131</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>554</v>
+        <v>976</v>
       </c>
       <c r="J73" s="0">
         <v>487.68040000000002</v>
@@ -6357,7 +6357,7 @@
         <v>132</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>555</v>
+        <v>977</v>
       </c>
       <c r="J74" s="0">
         <v>463.46300000000002</v>
@@ -6389,7 +6389,7 @@
         <v>133</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>556</v>
+        <v>978</v>
       </c>
       <c r="J75" s="0">
         <v>442.20010000000002</v>
@@ -6421,7 +6421,7 @@
         <v>134</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>557</v>
+        <v>979</v>
       </c>
       <c r="J76" s="0">
         <v>426.24950000000001</v>
@@ -6453,7 +6453,7 @@
         <v>135</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>558</v>
+        <v>980</v>
       </c>
       <c r="J77" s="0">
         <v>392.93150000000003</v>
@@ -6485,7 +6485,7 @@
         <v>136</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>559</v>
+        <v>981</v>
       </c>
       <c r="J78" s="0">
         <v>377.69189999999998</v>
@@ -6517,7 +6517,7 @@
         <v>137</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>560</v>
+        <v>982</v>
       </c>
       <c r="J79" s="0">
         <v>372.46730000000002</v>
@@ -6549,7 +6549,7 @@
         <v>138</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>561</v>
+        <v>983</v>
       </c>
       <c r="J80" s="0">
         <v>367.9117</v>
@@ -6581,7 +6581,7 @@
         <v>139</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>562</v>
+        <v>984</v>
       </c>
       <c r="J81" s="0">
         <v>9907.2489999999998</v>
@@ -6613,7 +6613,7 @@
         <v>140</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>563</v>
+        <v>985</v>
       </c>
       <c r="J82" s="0">
         <v>9652.7158</v>
@@ -6645,7 +6645,7 @@
         <v>141</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>564</v>
+        <v>986</v>
       </c>
       <c r="J83" s="0">
         <v>1441.7384999999999</v>
@@ -6677,7 +6677,7 @@
         <v>142</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>565</v>
+        <v>987</v>
       </c>
       <c r="J84" s="0">
         <v>1225.0391</v>
@@ -6709,7 +6709,7 @@
         <v>143</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>566</v>
+        <v>988</v>
       </c>
       <c r="J85" s="0">
         <v>535.24869999999999</v>
@@ -6741,7 +6741,7 @@
         <v>144</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>567</v>
+        <v>989</v>
       </c>
       <c r="J86" s="0">
         <v>505.87869999999998</v>
@@ -6773,7 +6773,7 @@
         <v>145</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>568</v>
+        <v>990</v>
       </c>
       <c r="J87" s="0">
         <v>499.1123</v>
@@ -6805,7 +6805,7 @@
         <v>146</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>569</v>
+        <v>991</v>
       </c>
       <c r="J88" s="0">
         <v>454.46269999999998</v>
@@ -6837,7 +6837,7 @@
         <v>147</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>570</v>
+        <v>992</v>
       </c>
       <c r="J89" s="0">
         <v>452.58749999999998</v>
@@ -6869,7 +6869,7 @@
         <v>148</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>571</v>
+        <v>993</v>
       </c>
       <c r="J90" s="0">
         <v>434.6585</v>
@@ -6901,7 +6901,7 @@
         <v>149</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>572</v>
+        <v>994</v>
       </c>
       <c r="J91" s="0">
         <v>401.7577</v>
@@ -6933,7 +6933,7 @@
         <v>150</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>573</v>
+        <v>995</v>
       </c>
       <c r="J92" s="0">
         <v>395.96719999999999</v>
@@ -6965,7 +6965,7 @@
         <v>151</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>574</v>
+        <v>996</v>
       </c>
       <c r="J93" s="0">
         <v>13039.6055</v>
@@ -6997,7 +6997,7 @@
         <v>152</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>575</v>
+        <v>997</v>
       </c>
       <c r="J94" s="0">
         <v>6975.5502999999999</v>
@@ -7029,7 +7029,7 @@
         <v>153</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>576</v>
+        <v>998</v>
       </c>
       <c r="J95" s="0">
         <v>1471.2853</v>
@@ -7061,7 +7061,7 @@
         <v>154</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>577</v>
+        <v>999</v>
       </c>
       <c r="J96" s="0">
         <v>1120.2394999999999</v>
@@ -7093,7 +7093,7 @@
         <v>155</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>578</v>
+        <v>1000</v>
       </c>
       <c r="J97" s="0">
         <v>525.06529999999998</v>
@@ -7125,7 +7125,7 @@
         <v>156</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>579</v>
+        <v>1001</v>
       </c>
       <c r="J98" s="0">
         <v>511.11419999999998</v>
@@ -7157,7 +7157,7 @@
         <v>157</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>580</v>
+        <v>1002</v>
       </c>
       <c r="J99" s="0">
         <v>488.54860000000002</v>
@@ -7189,7 +7189,7 @@
         <v>158</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>581</v>
+        <v>1003</v>
       </c>
       <c r="J100" s="0">
         <v>456.88260000000002</v>
@@ -7221,7 +7221,7 @@
         <v>159</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>582</v>
+        <v>1004</v>
       </c>
       <c r="J101" s="0">
         <v>454.80709999999999</v>
@@ -7253,7 +7253,7 @@
         <v>160</v>
       </c>
       <c r="I102" s="0" t="s">
-        <v>583</v>
+        <v>1005</v>
       </c>
       <c r="J102" s="0">
         <v>440.73829999999998</v>
@@ -7285,7 +7285,7 @@
         <v>161</v>
       </c>
       <c r="I103" s="0" t="s">
-        <v>584</v>
+        <v>1006</v>
       </c>
       <c r="J103" s="0">
         <v>390.3793</v>
@@ -7317,7 +7317,7 @@
         <v>162</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>585</v>
+        <v>1007</v>
       </c>
       <c r="J104" s="0">
         <v>366.7876</v>
@@ -7349,7 +7349,7 @@
         <v>163</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>586</v>
+        <v>1008</v>
       </c>
       <c r="J105" s="0">
         <v>13740.0527</v>
@@ -7381,7 +7381,7 @@
         <v>164</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>587</v>
+        <v>1009</v>
       </c>
       <c r="J106" s="0">
         <v>9744.2099999999991</v>
@@ -7413,7 +7413,7 @@
         <v>167</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>590</v>
+        <v>1010</v>
       </c>
       <c r="J107" s="0">
         <v>543.12710000000004</v>
@@ -7445,7 +7445,7 @@
         <v>168</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>591</v>
+        <v>1011</v>
       </c>
       <c r="J108" s="0">
         <v>530.70270000000005</v>
@@ -7477,7 +7477,7 @@
         <v>169</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>592</v>
+        <v>1012</v>
       </c>
       <c r="J109" s="0">
         <v>482.14240000000001</v>
@@ -7509,7 +7509,7 @@
         <v>170</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>593</v>
+        <v>1013</v>
       </c>
       <c r="J110" s="0">
         <v>462.08449999999999</v>
@@ -7541,7 +7541,7 @@
         <v>171</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>594</v>
+        <v>1014</v>
       </c>
       <c r="J111" s="0">
         <v>457.30529999999999</v>
@@ -7573,7 +7573,7 @@
         <v>172</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>595</v>
+        <v>1015</v>
       </c>
       <c r="J112" s="0">
         <v>450.53769999999997</v>
@@ -7605,7 +7605,7 @@
         <v>173</v>
       </c>
       <c r="I113" s="0" t="s">
-        <v>596</v>
+        <v>1016</v>
       </c>
       <c r="J113" s="0">
         <v>416.66809999999998</v>
@@ -7637,7 +7637,7 @@
         <v>174</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>597</v>
+        <v>1017</v>
       </c>
       <c r="J114" s="0">
         <v>381.01350000000002</v>
@@ -7669,7 +7669,7 @@
         <v>179</v>
       </c>
       <c r="I115" s="0" t="s">
-        <v>602</v>
+        <v>1018</v>
       </c>
       <c r="J115" s="0">
         <v>606.53700000000003</v>
@@ -7701,7 +7701,7 @@
         <v>180</v>
       </c>
       <c r="I116" s="0" t="s">
-        <v>603</v>
+        <v>1019</v>
       </c>
       <c r="J116" s="0">
         <v>479.4468</v>
@@ -7733,7 +7733,7 @@
         <v>181</v>
       </c>
       <c r="I117" s="0" t="s">
-        <v>604</v>
+        <v>1020</v>
       </c>
       <c r="J117" s="0">
         <v>479.09190000000001</v>
@@ -7765,7 +7765,7 @@
         <v>182</v>
       </c>
       <c r="I118" s="0" t="s">
-        <v>605</v>
+        <v>1021</v>
       </c>
       <c r="J118" s="0">
         <v>441.61619999999999</v>
@@ -7797,7 +7797,7 @@
         <v>183</v>
       </c>
       <c r="I119" s="0" t="s">
-        <v>606</v>
+        <v>1022</v>
       </c>
       <c r="J119" s="0">
         <v>417.55779999999999</v>
@@ -7829,7 +7829,7 @@
         <v>184</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>607</v>
+        <v>1023</v>
       </c>
       <c r="J120" s="0">
         <v>380.84750000000003</v>
@@ -7861,7 +7861,7 @@
         <v>185</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>608</v>
+        <v>1024</v>
       </c>
       <c r="J121" s="0">
         <v>380.4452</v>
@@ -7893,7 +7893,7 @@
         <v>186</v>
       </c>
       <c r="I122" s="0" t="s">
-        <v>609</v>
+        <v>1025</v>
       </c>
       <c r="J122" s="0">
         <v>338.78429999999997</v>
@@ -7925,7 +7925,7 @@
         <v>187</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>610</v>
+        <v>1026</v>
       </c>
       <c r="J123" s="0">
         <v>11531.805700000001</v>
@@ -7957,7 +7957,7 @@
         <v>188</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>611</v>
+        <v>1027</v>
       </c>
       <c r="J124" s="0">
         <v>6375.0625</v>
@@ -7989,7 +7989,7 @@
         <v>105</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>612</v>
+        <v>1028</v>
       </c>
       <c r="J125" s="0">
         <v>1293.2311</v>
@@ -8021,7 +8021,7 @@
         <v>106</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>613</v>
+        <v>1029</v>
       </c>
       <c r="J126" s="0">
         <v>1168.5597</v>
@@ -8053,7 +8053,7 @@
         <v>144</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>614</v>
+        <v>1030</v>
       </c>
       <c r="J127" s="0">
         <v>505.87869999999998</v>
@@ -8085,7 +8085,7 @@
         <v>189</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>615</v>
+        <v>1031</v>
       </c>
       <c r="J128" s="0">
         <v>480.84039999999999</v>
@@ -8117,7 +8117,7 @@
         <v>190</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>616</v>
+        <v>1032</v>
       </c>
       <c r="J129" s="0">
         <v>474.62130000000002</v>
@@ -8149,7 +8149,7 @@
         <v>191</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>617</v>
+        <v>1033</v>
       </c>
       <c r="J130" s="0">
         <v>462.91030000000001</v>
@@ -8181,7 +8181,7 @@
         <v>192</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>618</v>
+        <v>1034</v>
       </c>
       <c r="J131" s="0">
         <v>435.94409999999999</v>
@@ -8213,7 +8213,7 @@
         <v>193</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>619</v>
+        <v>1035</v>
       </c>
       <c r="J132" s="0">
         <v>419.98750000000001</v>
@@ -8245,7 +8245,7 @@
         <v>194</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>620</v>
+        <v>1036</v>
       </c>
       <c r="J133" s="0">
         <v>401.06349999999998</v>
@@ -8277,7 +8277,7 @@
         <v>195</v>
       </c>
       <c r="I134" s="0" t="s">
-        <v>621</v>
+        <v>1037</v>
       </c>
       <c r="J134" s="0">
         <v>400.24349999999998</v>
@@ -8309,7 +8309,7 @@
         <v>196</v>
       </c>
       <c r="I135" s="0" t="s">
-        <v>622</v>
+        <v>1038</v>
       </c>
       <c r="J135" s="0">
         <v>10941.195299999999</v>
@@ -8341,7 +8341,7 @@
         <v>197</v>
       </c>
       <c r="I136" s="0" t="s">
-        <v>623</v>
+        <v>1039</v>
       </c>
       <c r="J136" s="0">
         <v>7539.1181999999999</v>
@@ -8373,7 +8373,7 @@
         <v>198</v>
       </c>
       <c r="I137" s="0" t="s">
-        <v>624</v>
+        <v>1040</v>
       </c>
       <c r="J137" s="0">
         <v>1460.5899999999999</v>
@@ -8405,7 +8405,7 @@
         <v>199</v>
       </c>
       <c r="I138" s="0" t="s">
-        <v>625</v>
+        <v>1041</v>
       </c>
       <c r="J138" s="0">
         <v>1390.1700000000001</v>
@@ -8437,7 +8437,7 @@
         <v>200</v>
       </c>
       <c r="I139" s="0" t="s">
-        <v>626</v>
+        <v>1042</v>
       </c>
       <c r="J139" s="0">
         <v>1191.2892999999999</v>
@@ -8469,7 +8469,7 @@
         <v>201</v>
       </c>
       <c r="I140" s="0" t="s">
-        <v>627</v>
+        <v>1043</v>
       </c>
       <c r="J140" s="0">
         <v>905.0009</v>
@@ -8501,7 +8501,7 @@
         <v>202</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>628</v>
+        <v>1044</v>
       </c>
       <c r="J141" s="0">
         <v>509.07279999999997</v>
@@ -8533,7 +8533,7 @@
         <v>203</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>629</v>
+        <v>1045</v>
       </c>
       <c r="J142" s="0">
         <v>509.06999999999999</v>
@@ -8565,7 +8565,7 @@
         <v>204</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>630</v>
+        <v>1046</v>
       </c>
       <c r="J143" s="0">
         <v>467.17430000000002</v>
@@ -8597,7 +8597,7 @@
         <v>205</v>
       </c>
       <c r="I144" s="0" t="s">
-        <v>631</v>
+        <v>1047</v>
       </c>
       <c r="J144" s="0">
         <v>467.17000000000002</v>
@@ -8629,7 +8629,7 @@
         <v>206</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>632</v>
+        <v>1048</v>
       </c>
       <c r="J145" s="0">
         <v>461.41000000000003</v>
@@ -8661,7 +8661,7 @@
         <v>207</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>633</v>
+        <v>1049</v>
       </c>
       <c r="J146" s="0">
         <v>461.40780000000001</v>
@@ -8693,7 +8693,7 @@
         <v>208</v>
       </c>
       <c r="I147" s="0" t="s">
-        <v>634</v>
+        <v>1050</v>
       </c>
       <c r="J147" s="0">
         <v>426.55000000000001</v>
@@ -8725,7 +8725,7 @@
         <v>209</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>635</v>
+        <v>1051</v>
       </c>
       <c r="J148" s="0">
         <v>426.54820000000001</v>
@@ -8757,7 +8757,7 @@
         <v>210</v>
       </c>
       <c r="I149" s="0" t="s">
-        <v>636</v>
+        <v>1052</v>
       </c>
       <c r="J149" s="0">
         <v>390.12</v>
@@ -8789,7 +8789,7 @@
         <v>211</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>637</v>
+        <v>1053</v>
       </c>
       <c r="J150" s="0">
         <v>390.1198</v>
@@ -8821,7 +8821,7 @@
         <v>212</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>638</v>
+        <v>1054</v>
       </c>
       <c r="J151" s="0">
         <v>386.36000000000001</v>
@@ -8853,7 +8853,7 @@
         <v>213</v>
       </c>
       <c r="I152" s="0" t="s">
-        <v>639</v>
+        <v>1055</v>
       </c>
       <c r="J152" s="0">
         <v>386.35520000000002</v>
@@ -8885,7 +8885,7 @@
         <v>214</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>640</v>
+        <v>1056</v>
       </c>
       <c r="J153" s="0">
         <v>359.35480000000001</v>
@@ -8917,7 +8917,7 @@
         <v>215</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>641</v>
+        <v>1057</v>
       </c>
       <c r="J154" s="0">
         <v>359.35000000000002</v>
@@ -8949,7 +8949,7 @@
         <v>216</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>642</v>
+        <v>1058</v>
       </c>
       <c r="J155" s="0">
         <v>4.8700000000000001</v>
@@ -8981,7 +8981,7 @@
         <v>218</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>644</v>
+        <v>1059</v>
       </c>
       <c r="J156" s="0">
         <v>12758.521500000001</v>
@@ -9013,7 +9013,7 @@
         <v>220</v>
       </c>
       <c r="I157" s="0" t="s">
-        <v>646</v>
+        <v>1060</v>
       </c>
       <c r="J157" s="0">
         <v>1518.05</v>
@@ -9045,7 +9045,7 @@
         <v>221</v>
       </c>
       <c r="I158" s="0" t="s">
-        <v>647</v>
+        <v>1061</v>
       </c>
       <c r="J158" s="0">
         <v>1483.55</v>
@@ -9077,7 +9077,7 @@
         <v>224</v>
       </c>
       <c r="I159" s="0" t="s">
-        <v>650</v>
+        <v>1062</v>
       </c>
       <c r="J159" s="0">
         <v>508.62</v>
@@ -9109,7 +9109,7 @@
         <v>225</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>651</v>
+        <v>1063</v>
       </c>
       <c r="J160" s="0">
         <v>508.61829999999998</v>
@@ -9141,7 +9141,7 @@
         <v>226</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>652</v>
+        <v>1064</v>
       </c>
       <c r="J161" s="0">
         <v>468.33999999999998</v>
@@ -9173,7 +9173,7 @@
         <v>227</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>653</v>
+        <v>1065</v>
       </c>
       <c r="J162" s="0">
         <v>468.33859999999999</v>
@@ -9205,7 +9205,7 @@
         <v>228</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>654</v>
+        <v>1066</v>
       </c>
       <c r="J163" s="0">
         <v>441.58999999999998</v>
@@ -9237,7 +9237,7 @@
         <v>229</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>655</v>
+        <v>1067</v>
       </c>
       <c r="J164" s="0">
         <v>441.58780000000002</v>
@@ -9269,7 +9269,7 @@
         <v>230</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>656</v>
+        <v>1068</v>
       </c>
       <c r="J165" s="0">
         <v>417.62110000000001</v>
@@ -9301,7 +9301,7 @@
         <v>231</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>657</v>
+        <v>1069</v>
       </c>
       <c r="J166" s="0">
         <v>417.62</v>
@@ -9333,7 +9333,7 @@
         <v>232</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>658</v>
+        <v>1070</v>
       </c>
       <c r="J167" s="0">
         <v>407.61059999999998</v>
@@ -9365,7 +9365,7 @@
         <v>233</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>659</v>
+        <v>1071</v>
       </c>
       <c r="J168" s="0">
         <v>407.61000000000001</v>
@@ -9397,7 +9397,7 @@
         <v>234</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>660</v>
+        <v>1072</v>
       </c>
       <c r="J169" s="0">
         <v>392.51999999999998</v>
@@ -9429,7 +9429,7 @@
         <v>235</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>661</v>
+        <v>1073</v>
       </c>
       <c r="J170" s="0">
         <v>392.51850000000002</v>
@@ -9461,7 +9461,7 @@
         <v>236</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>662</v>
+        <v>1074</v>
       </c>
       <c r="J171" s="0">
         <v>382.75999999999999</v>
@@ -9493,7 +9493,7 @@
         <v>237</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>663</v>
+        <v>1075</v>
       </c>
       <c r="J172" s="0">
         <v>382.75760000000002</v>
@@ -9525,7 +9525,7 @@
         <v>238</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>664</v>
+        <v>1076</v>
       </c>
       <c r="J173" s="0">
         <v>323.20999999999998</v>
@@ -9557,7 +9557,7 @@
         <v>239</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>665</v>
+        <v>1077</v>
       </c>
       <c r="J174" s="0">
         <v>323.20670000000001</v>
@@ -9589,7 +9589,7 @@
         <v>240</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>666</v>
+        <v>1078</v>
       </c>
       <c r="J175" s="0">
         <v>10995.9912</v>
@@ -9621,7 +9621,7 @@
         <v>241</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>667</v>
+        <v>1079</v>
       </c>
       <c r="J176" s="0">
         <v>7215.2777999999999</v>
@@ -9653,7 +9653,7 @@
         <v>242</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>668</v>
+        <v>1080</v>
       </c>
       <c r="J177" s="0">
         <v>1710.03</v>
@@ -9685,7 +9685,7 @@
         <v>243</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>669</v>
+        <v>1081</v>
       </c>
       <c r="J178" s="0">
         <v>1001.1900000000001</v>
@@ -9717,7 +9717,7 @@
         <v>244</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>670</v>
+        <v>1082</v>
       </c>
       <c r="J179" s="0">
         <v>1188.2415000000001</v>
@@ -9749,7 +9749,7 @@
         <v>246</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>672</v>
+        <v>1083</v>
       </c>
       <c r="J180" s="0">
         <v>426.52229999999997</v>
@@ -9781,7 +9781,7 @@
         <v>247</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>673</v>
+        <v>1084</v>
       </c>
       <c r="J181" s="0">
         <v>426.51999999999998</v>
@@ -9813,7 +9813,7 @@
         <v>248</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>674</v>
+        <v>1085</v>
       </c>
       <c r="J182" s="0">
         <v>390.1635</v>
@@ -9845,7 +9845,7 @@
         <v>249</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>675</v>
+        <v>1086</v>
       </c>
       <c r="J183" s="0">
         <v>390.16000000000003</v>
@@ -9877,7 +9877,7 @@
         <v>250</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>676</v>
+        <v>1087</v>
       </c>
       <c r="J184" s="0">
         <v>385.91000000000003</v>
@@ -9909,7 +9909,7 @@
         <v>251</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>677</v>
+        <v>1088</v>
       </c>
       <c r="J185" s="0">
         <v>385.90809999999999</v>
@@ -9941,7 +9941,7 @@
         <v>252</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>678</v>
+        <v>1089</v>
       </c>
       <c r="J186" s="0">
         <v>269.38150000000002</v>
@@ -9973,7 +9973,7 @@
         <v>253</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>679</v>
+        <v>1090</v>
       </c>
       <c r="J187" s="0">
         <v>269.38</v>
@@ -10005,7 +10005,7 @@
         <v>254</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>680</v>
+        <v>1091</v>
       </c>
       <c r="J188" s="0">
         <v>248.60079999999999</v>
@@ -10037,7 +10037,7 @@
         <v>255</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>681</v>
+        <v>1092</v>
       </c>
       <c r="J189" s="0">
         <v>248.6</v>
@@ -10069,7 +10069,7 @@
         <v>256</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>682</v>
+        <v>1093</v>
       </c>
       <c r="J190" s="0">
         <v>224.50450000000001</v>
@@ -10101,7 +10101,7 @@
         <v>257</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>683</v>
+        <v>1094</v>
       </c>
       <c r="J191" s="0">
         <v>224.5</v>
@@ -10133,7 +10133,7 @@
         <v>258</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>684</v>
+        <v>1095</v>
       </c>
       <c r="J192" s="0">
         <v>192.28460000000001</v>
@@ -10165,7 +10165,7 @@
         <v>259</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>685</v>
+        <v>1096</v>
       </c>
       <c r="J193" s="0">
         <v>192.28</v>
@@ -10197,7 +10197,7 @@
         <v>260</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>686</v>
+        <v>1097</v>
       </c>
       <c r="J194" s="0">
         <v>152.80000000000001</v>
@@ -10229,7 +10229,7 @@
         <v>261</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>687</v>
+        <v>1098</v>
       </c>
       <c r="J195" s="0">
         <v>152.7972</v>
@@ -10261,7 +10261,7 @@
         <v>262</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>688</v>
+        <v>1099</v>
       </c>
       <c r="J196" s="0">
         <v>11254.794900000001</v>
@@ -10293,7 +10293,7 @@
         <v>263</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>689</v>
+        <v>1100</v>
       </c>
       <c r="J197" s="0">
         <v>8245.5498000000007</v>
@@ -10325,7 +10325,7 @@
         <v>264</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>690</v>
+        <v>1101</v>
       </c>
       <c r="J198" s="0">
         <v>1104.5668000000001</v>
@@ -10357,7 +10357,7 @@
         <v>265</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>691</v>
+        <v>1102</v>
       </c>
       <c r="J199" s="0">
         <v>667.55740000000003</v>
@@ -10389,7 +10389,7 @@
         <v>266</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>692</v>
+        <v>1103</v>
       </c>
       <c r="J200" s="0">
         <v>476.60090000000002</v>
@@ -10421,7 +10421,7 @@
         <v>267</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>693</v>
+        <v>1104</v>
       </c>
       <c r="J201" s="0">
         <v>449.04090000000002</v>
@@ -10453,7 +10453,7 @@
         <v>268</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>694</v>
+        <v>1105</v>
       </c>
       <c r="J202" s="0">
         <v>442.10520000000002</v>
@@ -10485,7 +10485,7 @@
         <v>269</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>695</v>
+        <v>1106</v>
       </c>
       <c r="J203" s="0">
         <v>409.70580000000001</v>
@@ -10517,7 +10517,7 @@
         <v>270</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>696</v>
+        <v>1107</v>
       </c>
       <c r="J204" s="0">
         <v>397.46850000000001</v>
@@ -10549,7 +10549,7 @@
         <v>271</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>697</v>
+        <v>1108</v>
       </c>
       <c r="J205" s="0">
         <v>383.6352</v>
@@ -10581,7 +10581,7 @@
         <v>272</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>698</v>
+        <v>1109</v>
       </c>
       <c r="J206" s="0">
         <v>381.00670000000002</v>
@@ -10613,7 +10613,7 @@
         <v>273</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>699</v>
+        <v>1110</v>
       </c>
       <c r="J207" s="0">
         <v>353.37259999999998</v>
@@ -10645,7 +10645,7 @@
         <v>274</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>700</v>
+        <v>1111</v>
       </c>
       <c r="J208" s="0">
         <v>14310.114299999999</v>
@@ -10677,7 +10677,7 @@
         <v>275</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>701</v>
+        <v>1112</v>
       </c>
       <c r="J209" s="0">
         <v>8465.1962999999996</v>
@@ -10709,7 +10709,7 @@
         <v>276</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>702</v>
+        <v>1113</v>
       </c>
       <c r="J210" s="0">
         <v>1220.287</v>
@@ -10741,7 +10741,7 @@
         <v>277</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>703</v>
+        <v>1114</v>
       </c>
       <c r="J211" s="0">
         <v>599.00360000000001</v>
@@ -10773,7 +10773,7 @@
         <v>278</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>704</v>
+        <v>1115</v>
       </c>
       <c r="J212" s="0">
         <v>555.67830000000004</v>
@@ -10805,7 +10805,7 @@
         <v>279</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>705</v>
+        <v>1116</v>
       </c>
       <c r="J213" s="0">
         <v>491.62889999999999</v>
@@ -10837,7 +10837,7 @@
         <v>280</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>706</v>
+        <v>1117</v>
       </c>
       <c r="J214" s="0">
         <v>487.06729999999999</v>
@@ -10869,7 +10869,7 @@
         <v>281</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>707</v>
+        <v>1118</v>
       </c>
       <c r="J215" s="0">
         <v>443.50709999999998</v>
@@ -10901,7 +10901,7 @@
         <v>282</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>708</v>
+        <v>1119</v>
       </c>
       <c r="J216" s="0">
         <v>437.17829999999998</v>
@@ -10933,7 +10933,7 @@
         <v>283</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>709</v>
+        <v>1120</v>
       </c>
       <c r="J217" s="0">
         <v>422.71879999999999</v>
@@ -10965,7 +10965,7 @@
         <v>284</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>710</v>
+        <v>1121</v>
       </c>
       <c r="J218" s="0">
         <v>405.00119999999998</v>
@@ -10997,7 +10997,7 @@
         <v>285</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>711</v>
+        <v>1122</v>
       </c>
       <c r="J219" s="0">
         <v>378.08580000000001</v>
@@ -11029,7 +11029,7 @@
         <v>286</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>712</v>
+        <v>1123</v>
       </c>
       <c r="J220" s="0">
         <v>10927.456099999999</v>
@@ -11061,7 +11061,7 @@
         <v>287</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>713</v>
+        <v>1124</v>
       </c>
       <c r="J221" s="0">
         <v>7092.1475</v>
@@ -11093,7 +11093,7 @@
         <v>288</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>714</v>
+        <v>1125</v>
       </c>
       <c r="J222" s="0">
         <v>1251.4889000000001</v>
@@ -11125,7 +11125,7 @@
         <v>290</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>716</v>
+        <v>1126</v>
       </c>
       <c r="J223" s="0">
         <v>573.87549999999999</v>
@@ -11157,7 +11157,7 @@
         <v>291</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>717</v>
+        <v>1127</v>
       </c>
       <c r="J224" s="0">
         <v>432.66559999999998</v>
@@ -11189,7 +11189,7 @@
         <v>292</v>
       </c>
       <c r="I225" s="0" t="s">
-        <v>718</v>
+        <v>1128</v>
       </c>
       <c r="J225" s="0">
         <v>429.50220000000002</v>
@@ -11221,7 +11221,7 @@
         <v>293</v>
       </c>
       <c r="I226" s="0" t="s">
-        <v>719</v>
+        <v>1129</v>
       </c>
       <c r="J226" s="0">
         <v>425.55560000000003</v>
@@ -11253,7 +11253,7 @@
         <v>294</v>
       </c>
       <c r="I227" s="0" t="s">
-        <v>720</v>
+        <v>1130</v>
       </c>
       <c r="J227" s="0">
         <v>412.95150000000001</v>
@@ -11285,7 +11285,7 @@
         <v>295</v>
       </c>
       <c r="I228" s="0" t="s">
-        <v>721</v>
+        <v>1131</v>
       </c>
       <c r="J228" s="0">
         <v>403.95030000000003</v>
@@ -11317,7 +11317,7 @@
         <v>296</v>
       </c>
       <c r="I229" s="0" t="s">
-        <v>722</v>
+        <v>1132</v>
       </c>
       <c r="J229" s="0">
         <v>366.0301</v>
@@ -11349,7 +11349,7 @@
         <v>297</v>
       </c>
       <c r="I230" s="0" t="s">
-        <v>723</v>
+        <v>1133</v>
       </c>
       <c r="J230" s="0">
         <v>322.23540000000003</v>
@@ -11381,7 +11381,7 @@
         <v>298</v>
       </c>
       <c r="I231" s="0" t="s">
-        <v>724</v>
+        <v>1134</v>
       </c>
       <c r="J231" s="0">
         <v>14707.393599999999</v>
@@ -11413,7 +11413,7 @@
         <v>299</v>
       </c>
       <c r="I232" s="0" t="s">
-        <v>725</v>
+        <v>1135</v>
       </c>
       <c r="J232" s="0">
         <v>6104.8818000000001</v>
@@ -11445,7 +11445,7 @@
         <v>300</v>
       </c>
       <c r="I233" s="0" t="s">
-        <v>726</v>
+        <v>1136</v>
       </c>
       <c r="J233" s="0">
         <v>882.45939999999996</v>
@@ -11477,7 +11477,7 @@
         <v>301</v>
       </c>
       <c r="I234" s="0" t="s">
-        <v>727</v>
+        <v>1137</v>
       </c>
       <c r="J234" s="0">
         <v>761.87369999999999</v>
@@ -11509,7 +11509,7 @@
         <v>302</v>
       </c>
       <c r="I235" s="0" t="s">
-        <v>728</v>
+        <v>1138</v>
       </c>
       <c r="J235" s="0">
         <v>521.54589999999996</v>
@@ -11541,7 +11541,7 @@
         <v>303</v>
       </c>
       <c r="I236" s="0" t="s">
-        <v>729</v>
+        <v>1139</v>
       </c>
       <c r="J236" s="0">
         <v>500.20800000000003</v>
@@ -11573,7 +11573,7 @@
         <v>304</v>
       </c>
       <c r="I237" s="0" t="s">
-        <v>730</v>
+        <v>1140</v>
       </c>
       <c r="J237" s="0">
         <v>462.5016</v>
@@ -11605,7 +11605,7 @@
         <v>305</v>
       </c>
       <c r="I238" s="0" t="s">
-        <v>731</v>
+        <v>1141</v>
       </c>
       <c r="J238" s="0">
         <v>460.94619999999998</v>
@@ -11637,7 +11637,7 @@
         <v>306</v>
       </c>
       <c r="I239" s="0" t="s">
-        <v>732</v>
+        <v>1142</v>
       </c>
       <c r="J239" s="0">
         <v>455.41989999999999</v>
@@ -11669,7 +11669,7 @@
         <v>307</v>
       </c>
       <c r="I240" s="0" t="s">
-        <v>733</v>
+        <v>1143</v>
       </c>
       <c r="J240" s="0">
         <v>429.3236</v>
@@ -11701,7 +11701,7 @@
         <v>308</v>
       </c>
       <c r="I241" s="0" t="s">
-        <v>734</v>
+        <v>1144</v>
       </c>
       <c r="J241" s="0">
         <v>399.94749999999999</v>
@@ -11733,7 +11733,7 @@
         <v>309</v>
       </c>
       <c r="I242" s="0" t="s">
-        <v>735</v>
+        <v>1145</v>
       </c>
       <c r="J242" s="0">
         <v>232.58420000000001</v>
@@ -11765,7 +11765,7 @@
         <v>310</v>
       </c>
       <c r="I243" s="0" t="s">
-        <v>736</v>
+        <v>1146</v>
       </c>
       <c r="J243" s="0">
         <v>11847.5967</v>
@@ -11797,7 +11797,7 @@
         <v>311</v>
       </c>
       <c r="I244" s="0" t="s">
-        <v>737</v>
+        <v>1147</v>
       </c>
       <c r="J244" s="0">
         <v>6282.4102000000003</v>
@@ -11829,7 +11829,7 @@
         <v>312</v>
       </c>
       <c r="I245" s="0" t="s">
-        <v>738</v>
+        <v>1148</v>
       </c>
       <c r="J245" s="0">
         <v>1301.1243999999999</v>
@@ -11861,7 +11861,7 @@
         <v>313</v>
       </c>
       <c r="I246" s="0" t="s">
-        <v>739</v>
+        <v>1149</v>
       </c>
       <c r="J246" s="0">
         <v>939.31240000000003</v>
@@ -11893,7 +11893,7 @@
         <v>314</v>
       </c>
       <c r="I247" s="0" t="s">
-        <v>740</v>
+        <v>1150</v>
       </c>
       <c r="J247" s="0">
         <v>482.02300000000002</v>
@@ -11925,7 +11925,7 @@
         <v>315</v>
       </c>
       <c r="I248" s="0" t="s">
-        <v>741</v>
+        <v>1151</v>
       </c>
       <c r="J248" s="0">
         <v>466.72879999999998</v>
@@ -11957,7 +11957,7 @@
         <v>192</v>
       </c>
       <c r="I249" s="0" t="s">
-        <v>742</v>
+        <v>1152</v>
       </c>
       <c r="J249" s="0">
         <v>435.94409999999999</v>
@@ -11989,7 +11989,7 @@
         <v>316</v>
       </c>
       <c r="I250" s="0" t="s">
-        <v>743</v>
+        <v>1153</v>
       </c>
       <c r="J250" s="0">
         <v>400.39690000000002</v>
@@ -12021,7 +12021,7 @@
         <v>317</v>
       </c>
       <c r="I251" s="0" t="s">
-        <v>744</v>
+        <v>1154</v>
       </c>
       <c r="J251" s="0">
         <v>400.39350000000002</v>
@@ -12053,7 +12053,7 @@
         <v>318</v>
       </c>
       <c r="I252" s="0" t="s">
-        <v>745</v>
+        <v>1155</v>
       </c>
       <c r="J252" s="0">
         <v>385.38260000000002</v>
@@ -12085,7 +12085,7 @@
         <v>319</v>
       </c>
       <c r="I253" s="0" t="s">
-        <v>746</v>
+        <v>1156</v>
       </c>
       <c r="J253" s="0">
         <v>347.70269999999999</v>
@@ -12117,7 +12117,7 @@
         <v>320</v>
       </c>
       <c r="I254" s="0" t="s">
-        <v>747</v>
+        <v>1157</v>
       </c>
       <c r="J254" s="0">
         <v>329.09859999999998</v>
@@ -12149,7 +12149,7 @@
         <v>321</v>
       </c>
       <c r="I255" s="0" t="s">
-        <v>748</v>
+        <v>1158</v>
       </c>
       <c r="J255" s="0">
         <v>12556.6572</v>
@@ -12181,7 +12181,7 @@
         <v>322</v>
       </c>
       <c r="I256" s="0" t="s">
-        <v>749</v>
+        <v>1159</v>
       </c>
       <c r="J256" s="0">
         <v>6296.4022999999998</v>
@@ -12213,7 +12213,7 @@
         <v>323</v>
       </c>
       <c r="I257" s="0" t="s">
-        <v>750</v>
+        <v>1160</v>
       </c>
       <c r="J257" s="0">
         <v>968.71990000000005</v>
@@ -12245,7 +12245,7 @@
         <v>324</v>
       </c>
       <c r="I258" s="0" t="s">
-        <v>751</v>
+        <v>1161</v>
       </c>
       <c r="J258" s="0">
         <v>883.06809999999996</v>
@@ -12277,7 +12277,7 @@
         <v>325</v>
       </c>
       <c r="I259" s="0" t="s">
-        <v>752</v>
+        <v>1162</v>
       </c>
       <c r="J259" s="0">
         <v>478.95100000000002</v>
@@ -12309,7 +12309,7 @@
         <v>326</v>
       </c>
       <c r="I260" s="0" t="s">
-        <v>753</v>
+        <v>1163</v>
       </c>
       <c r="J260" s="0">
         <v>465.39179999999999</v>
@@ -12341,7 +12341,7 @@
         <v>327</v>
       </c>
       <c r="I261" s="0" t="s">
-        <v>754</v>
+        <v>1164</v>
       </c>
       <c r="J261" s="0">
         <v>463.80270000000002</v>
@@ -12373,7 +12373,7 @@
         <v>328</v>
       </c>
       <c r="I262" s="0" t="s">
-        <v>755</v>
+        <v>1165</v>
       </c>
       <c r="J262" s="0">
         <v>462.91269999999997</v>
@@ -12405,7 +12405,7 @@
         <v>329</v>
       </c>
       <c r="I263" s="0" t="s">
-        <v>756</v>
+        <v>1166</v>
       </c>
       <c r="J263" s="0">
         <v>445.06830000000002</v>
@@ -12437,7 +12437,7 @@
         <v>330</v>
       </c>
       <c r="I264" s="0" t="s">
-        <v>757</v>
+        <v>1167</v>
       </c>
       <c r="J264" s="0">
         <v>423.10739999999999</v>
@@ -12469,7 +12469,7 @@
         <v>331</v>
       </c>
       <c r="I265" s="0" t="s">
-        <v>758</v>
+        <v>1168</v>
       </c>
       <c r="J265" s="0">
         <v>402.7998</v>
@@ -12501,7 +12501,7 @@
         <v>332</v>
       </c>
       <c r="I266" s="0" t="s">
-        <v>759</v>
+        <v>1169</v>
       </c>
       <c r="J266" s="0">
         <v>372.56169999999997</v>
@@ -12533,7 +12533,7 @@
         <v>333</v>
       </c>
       <c r="I267" s="0" t="s">
-        <v>760</v>
+        <v>1170</v>
       </c>
       <c r="J267" s="0">
         <v>10030.694299999999</v>
@@ -12565,7 +12565,7 @@
         <v>334</v>
       </c>
       <c r="I268" s="0" t="s">
-        <v>761</v>
+        <v>1171</v>
       </c>
       <c r="J268" s="0">
         <v>6168.2295000000004</v>
@@ -12597,7 +12597,7 @@
         <v>335</v>
       </c>
       <c r="I269" s="0" t="s">
-        <v>762</v>
+        <v>1172</v>
       </c>
       <c r="J269" s="0">
         <v>961.54250000000002</v>
@@ -12629,7 +12629,7 @@
         <v>336</v>
       </c>
       <c r="I270" s="0" t="s">
-        <v>763</v>
+        <v>1173</v>
       </c>
       <c r="J270" s="0">
         <v>564.7491</v>
@@ -12661,7 +12661,7 @@
         <v>337</v>
       </c>
       <c r="I271" s="0" t="s">
-        <v>764</v>
+        <v>1174</v>
       </c>
       <c r="J271" s="0">
         <v>502.06450000000001</v>
@@ -12693,7 +12693,7 @@
         <v>338</v>
       </c>
       <c r="I272" s="0" t="s">
-        <v>765</v>
+        <v>1175</v>
       </c>
       <c r="J272" s="0">
         <v>498.90269999999998</v>
@@ -12725,7 +12725,7 @@
         <v>339</v>
       </c>
       <c r="I273" s="0" t="s">
-        <v>766</v>
+        <v>1176</v>
       </c>
       <c r="J273" s="0">
         <v>399.30579999999998</v>
@@ -12757,7 +12757,7 @@
         <v>340</v>
       </c>
       <c r="I274" s="0" t="s">
-        <v>767</v>
+        <v>1177</v>
       </c>
       <c r="J274" s="0">
         <v>395.6617</v>
@@ -12789,7 +12789,7 @@
         <v>341</v>
       </c>
       <c r="I275" s="0" t="s">
-        <v>768</v>
+        <v>1178</v>
       </c>
       <c r="J275" s="0">
         <v>374.79230000000001</v>
@@ -12821,7 +12821,7 @@
         <v>342</v>
       </c>
       <c r="I276" s="0" t="s">
-        <v>769</v>
+        <v>1179</v>
       </c>
       <c r="J276" s="0">
         <v>317.00749999999999</v>
@@ -12853,7 +12853,7 @@
         <v>343</v>
       </c>
       <c r="I277" s="0" t="s">
-        <v>770</v>
+        <v>1180</v>
       </c>
       <c r="J277" s="0">
         <v>312.89389999999997</v>
@@ -12885,7 +12885,7 @@
         <v>344</v>
       </c>
       <c r="I278" s="0" t="s">
-        <v>771</v>
+        <v>1181</v>
       </c>
       <c r="J278" s="0">
         <v>262.27510000000001</v>
@@ -12917,7 +12917,7 @@
         <v>345</v>
       </c>
       <c r="I279" s="0" t="s">
-        <v>772</v>
+        <v>1182</v>
       </c>
       <c r="J279" s="0">
         <v>10326.7256</v>
@@ -12949,7 +12949,7 @@
         <v>346</v>
       </c>
       <c r="I280" s="0" t="s">
-        <v>773</v>
+        <v>1183</v>
       </c>
       <c r="J280" s="0">
         <v>9974.2188000000006</v>
@@ -12981,7 +12981,7 @@
         <v>347</v>
       </c>
       <c r="I281" s="0" t="s">
-        <v>774</v>
+        <v>1184</v>
       </c>
       <c r="J281" s="0">
         <v>1148.0337</v>
@@ -13013,7 +13013,7 @@
         <v>348</v>
       </c>
       <c r="I282" s="0" t="s">
-        <v>775</v>
+        <v>1185</v>
       </c>
       <c r="J282" s="0">
         <v>914.7056</v>
@@ -13045,7 +13045,7 @@
         <v>349</v>
       </c>
       <c r="I283" s="0" t="s">
-        <v>776</v>
+        <v>1186</v>
       </c>
       <c r="J283" s="0">
         <v>483.39670000000001</v>
@@ -13077,7 +13077,7 @@
         <v>350</v>
       </c>
       <c r="I284" s="0" t="s">
-        <v>777</v>
+        <v>1187</v>
       </c>
       <c r="J284" s="0">
         <v>480.69290000000001</v>
@@ -13109,7 +13109,7 @@
         <v>351</v>
       </c>
       <c r="I285" s="0" t="s">
-        <v>778</v>
+        <v>1188</v>
       </c>
       <c r="J285" s="0">
         <v>477.11810000000003</v>
@@ -13141,7 +13141,7 @@
         <v>352</v>
       </c>
       <c r="I286" s="0" t="s">
-        <v>779</v>
+        <v>1189</v>
       </c>
       <c r="J286" s="0">
         <v>470.54579999999999</v>
@@ -13173,7 +13173,7 @@
         <v>353</v>
       </c>
       <c r="I287" s="0" t="s">
-        <v>780</v>
+        <v>1190</v>
       </c>
       <c r="J287" s="0">
         <v>463.21350000000001</v>
@@ -13205,7 +13205,7 @@
         <v>354</v>
       </c>
       <c r="I288" s="0" t="s">
-        <v>781</v>
+        <v>1191</v>
       </c>
       <c r="J288" s="0">
         <v>458.6345</v>
@@ -13237,7 +13237,7 @@
         <v>355</v>
       </c>
       <c r="I289" s="0" t="s">
-        <v>782</v>
+        <v>1192</v>
       </c>
       <c r="J289" s="0">
         <v>399.29669999999999</v>
@@ -13269,7 +13269,7 @@
         <v>356</v>
       </c>
       <c r="I290" s="0" t="s">
-        <v>783</v>
+        <v>1193</v>
       </c>
       <c r="J290" s="0">
         <v>349.30439999999999</v>
@@ -13301,7 +13301,7 @@
         <v>357</v>
       </c>
       <c r="I291" s="0" t="s">
-        <v>784</v>
+        <v>1194</v>
       </c>
       <c r="J291" s="0">
         <v>11249.227500000001</v>
@@ -13333,7 +13333,7 @@
         <v>358</v>
       </c>
       <c r="I292" s="0" t="s">
-        <v>785</v>
+        <v>1195</v>
       </c>
       <c r="J292" s="0">
         <v>6804.9902000000002</v>
@@ -13365,7 +13365,7 @@
         <v>361</v>
       </c>
       <c r="I293" s="0" t="s">
-        <v>788</v>
+        <v>1196</v>
       </c>
       <c r="J293" s="0">
         <v>547.55139999999994</v>
@@ -13397,7 +13397,7 @@
         <v>362</v>
       </c>
       <c r="I294" s="0" t="s">
-        <v>789</v>
+        <v>1197</v>
       </c>
       <c r="J294" s="0">
         <v>544.9031</v>
@@ -13429,7 +13429,7 @@
         <v>363</v>
       </c>
       <c r="I295" s="0" t="s">
-        <v>790</v>
+        <v>1198</v>
       </c>
       <c r="J295" s="0">
         <v>538.0435</v>
@@ -13461,7 +13461,7 @@
         <v>364</v>
       </c>
       <c r="I296" s="0" t="s">
-        <v>791</v>
+        <v>1199</v>
       </c>
       <c r="J296" s="0">
         <v>529.52170000000001</v>
@@ -13493,7 +13493,7 @@
         <v>365</v>
       </c>
       <c r="I297" s="0" t="s">
-        <v>792</v>
+        <v>1200</v>
       </c>
       <c r="J297" s="0">
         <v>429.88639999999998</v>
@@ -13525,7 +13525,7 @@
         <v>366</v>
       </c>
       <c r="I298" s="0" t="s">
-        <v>793</v>
+        <v>1201</v>
       </c>
       <c r="J298" s="0">
         <v>423.78399999999999</v>
@@ -13557,7 +13557,7 @@
         <v>367</v>
       </c>
       <c r="I299" s="0" t="s">
-        <v>794</v>
+        <v>1202</v>
       </c>
       <c r="J299" s="0">
         <v>374.9067</v>
@@ -13589,7 +13589,7 @@
         <v>368</v>
       </c>
       <c r="I300" s="0" t="s">
-        <v>795</v>
+        <v>1203</v>
       </c>
       <c r="J300" s="0">
         <v>327.96339999999998</v>
@@ -13621,7 +13621,7 @@
         <v>369</v>
       </c>
       <c r="I301" s="0" t="s">
-        <v>796</v>
+        <v>1204</v>
       </c>
       <c r="J301" s="0">
         <v>14917.853499999999</v>
@@ -13653,7 +13653,7 @@
         <v>370</v>
       </c>
       <c r="I302" s="0" t="s">
-        <v>797</v>
+        <v>1205</v>
       </c>
       <c r="J302" s="0">
         <v>10013.698200000001</v>
@@ -13685,7 +13685,7 @@
         <v>371</v>
       </c>
       <c r="I303" s="0" t="s">
-        <v>798</v>
+        <v>1206</v>
       </c>
       <c r="J303" s="0">
         <v>1332.2670000000001</v>
@@ -13717,7 +13717,7 @@
         <v>372</v>
       </c>
       <c r="I304" s="0" t="s">
-        <v>799</v>
+        <v>1207</v>
       </c>
       <c r="J304" s="0">
         <v>828.53430000000003</v>
@@ -13749,7 +13749,7 @@
         <v>373</v>
       </c>
       <c r="I305" s="0" t="s">
-        <v>800</v>
+        <v>1208</v>
       </c>
       <c r="J305" s="0">
         <v>578.22249999999997</v>
@@ -13781,7 +13781,7 @@
         <v>374</v>
       </c>
       <c r="I306" s="0" t="s">
-        <v>801</v>
+        <v>1209</v>
       </c>
       <c r="J306" s="0">
         <v>519.49069999999995</v>
@@ -13813,7 +13813,7 @@
         <v>375</v>
       </c>
       <c r="I307" s="0" t="s">
-        <v>802</v>
+        <v>1210</v>
       </c>
       <c r="J307" s="0">
         <v>488.8802</v>
@@ -13845,7 +13845,7 @@
         <v>376</v>
       </c>
       <c r="I308" s="0" t="s">
-        <v>803</v>
+        <v>1211</v>
       </c>
       <c r="J308" s="0">
         <v>479.72430000000003</v>
@@ -13877,7 +13877,7 @@
         <v>377</v>
       </c>
       <c r="I309" s="0" t="s">
-        <v>804</v>
+        <v>1212</v>
       </c>
       <c r="J309" s="0">
         <v>471.13209999999998</v>
@@ -13909,7 +13909,7 @@
         <v>378</v>
       </c>
       <c r="I310" s="0" t="s">
-        <v>805</v>
+        <v>1213</v>
       </c>
       <c r="J310" s="0">
         <v>465.73070000000001</v>
@@ -13941,7 +13941,7 @@
         <v>379</v>
       </c>
       <c r="I311" s="0" t="s">
-        <v>806</v>
+        <v>1214</v>
       </c>
       <c r="J311" s="0">
         <v>414.24799999999999</v>
@@ -13973,7 +13973,7 @@
         <v>380</v>
       </c>
       <c r="I312" s="0" t="s">
-        <v>807</v>
+        <v>1215</v>
       </c>
       <c r="J312" s="0">
         <v>382.2792</v>
@@ -14005,7 +14005,7 @@
         <v>381</v>
       </c>
       <c r="I313" s="0" t="s">
-        <v>808</v>
+        <v>1216</v>
       </c>
       <c r="J313" s="0">
         <v>13171.9355</v>
@@ -14037,7 +14037,7 @@
         <v>382</v>
       </c>
       <c r="I314" s="0" t="s">
-        <v>809</v>
+        <v>1217</v>
       </c>
       <c r="J314" s="0">
         <v>7219.6553000000004</v>
@@ -14069,7 +14069,7 @@
         <v>383</v>
       </c>
       <c r="I315" s="0" t="s">
-        <v>810</v>
+        <v>1218</v>
       </c>
       <c r="J315" s="0">
         <v>858.04020000000003</v>
@@ -14101,7 +14101,7 @@
         <v>384</v>
       </c>
       <c r="I316" s="0" t="s">
-        <v>811</v>
+        <v>1219</v>
       </c>
       <c r="J316" s="0">
         <v>548.43979999999999</v>
@@ -14133,7 +14133,7 @@
         <v>385</v>
       </c>
       <c r="I317" s="0" t="s">
-        <v>812</v>
+        <v>1220</v>
       </c>
       <c r="J317" s="0">
         <v>525.69830000000002</v>
@@ -14165,7 +14165,7 @@
         <v>386</v>
       </c>
       <c r="I318" s="0" t="s">
-        <v>813</v>
+        <v>1221</v>
       </c>
       <c r="J318" s="0">
         <v>474.8716</v>
@@ -14197,7 +14197,7 @@
         <v>387</v>
       </c>
       <c r="I319" s="0" t="s">
-        <v>814</v>
+        <v>1222</v>
       </c>
       <c r="J319" s="0">
         <v>453.47840000000002</v>
@@ -14229,7 +14229,7 @@
         <v>388</v>
       </c>
       <c r="I320" s="0" t="s">
-        <v>815</v>
+        <v>1223</v>
       </c>
       <c r="J320" s="0">
         <v>439.9545</v>
@@ -14261,7 +14261,7 @@
         <v>389</v>
       </c>
       <c r="I321" s="0" t="s">
-        <v>816</v>
+        <v>1224</v>
       </c>
       <c r="J321" s="0">
         <v>432.7242</v>
@@ -14293,7 +14293,7 @@
         <v>390</v>
       </c>
       <c r="I322" s="0" t="s">
-        <v>817</v>
+        <v>1225</v>
       </c>
       <c r="J322" s="0">
         <v>427.84280000000001</v>
@@ -14325,7 +14325,7 @@
         <v>391</v>
       </c>
       <c r="I323" s="0" t="s">
-        <v>818</v>
+        <v>1226</v>
       </c>
       <c r="J323" s="0">
         <v>406.00720000000001</v>
@@ -14357,7 +14357,7 @@
         <v>392</v>
       </c>
       <c r="I324" s="0" t="s">
-        <v>819</v>
+        <v>1227</v>
       </c>
       <c r="J324" s="0">
         <v>368.30669999999998</v>
@@ -14389,7 +14389,7 @@
         <v>393</v>
       </c>
       <c r="I325" s="0" t="s">
-        <v>820</v>
+        <v>1228</v>
       </c>
       <c r="J325" s="0">
         <v>10183.9961</v>
@@ -14421,7 +14421,7 @@
         <v>394</v>
       </c>
       <c r="I326" s="0" t="s">
-        <v>821</v>
+        <v>1229</v>
       </c>
       <c r="J326" s="0">
         <v>9260.2188000000006</v>
@@ -14453,7 +14453,7 @@
         <v>395</v>
       </c>
       <c r="I327" s="0" t="s">
-        <v>822</v>
+        <v>1230</v>
       </c>
       <c r="J327" s="0">
         <v>1286.2859000000001</v>
@@ -14485,7 +14485,7 @@
         <v>396</v>
       </c>
       <c r="I328" s="0" t="s">
-        <v>823</v>
+        <v>1231</v>
       </c>
       <c r="J328" s="0">
         <v>1212.9492</v>
@@ -14517,7 +14517,7 @@
         <v>398</v>
       </c>
       <c r="I329" s="0" t="s">
-        <v>825</v>
+        <v>1232</v>
       </c>
       <c r="J329" s="0">
         <v>423.24180000000001</v>
@@ -14549,7 +14549,7 @@
         <v>399</v>
       </c>
       <c r="I330" s="0" t="s">
-        <v>826</v>
+        <v>1233</v>
       </c>
       <c r="J330" s="0">
         <v>408.47359999999998</v>
@@ -14581,7 +14581,7 @@
         <v>400</v>
       </c>
       <c r="I331" s="0" t="s">
-        <v>827</v>
+        <v>1234</v>
       </c>
       <c r="J331" s="0">
         <v>405.3897</v>
@@ -14613,7 +14613,7 @@
         <v>401</v>
       </c>
       <c r="I332" s="0" t="s">
-        <v>828</v>
+        <v>1235</v>
       </c>
       <c r="J332" s="0">
         <v>379.12220000000002</v>
@@ -14645,7 +14645,7 @@
         <v>402</v>
       </c>
       <c r="I333" s="0" t="s">
-        <v>829</v>
+        <v>1236</v>
       </c>
       <c r="J333" s="0">
         <v>371.36880000000002</v>
@@ -14677,7 +14677,7 @@
         <v>403</v>
       </c>
       <c r="I334" s="0" t="s">
-        <v>830</v>
+        <v>1237</v>
       </c>
       <c r="J334" s="0">
         <v>350.1583</v>
@@ -14709,7 +14709,7 @@
         <v>404</v>
       </c>
       <c r="I335" s="0" t="s">
-        <v>831</v>
+        <v>1238</v>
       </c>
       <c r="J335" s="0">
         <v>338.19600000000003</v>
@@ -14741,7 +14741,7 @@
         <v>405</v>
       </c>
       <c r="I336" s="0" t="s">
-        <v>832</v>
+        <v>1239</v>
       </c>
       <c r="J336" s="0">
         <v>10894.9053</v>
@@ -14773,7 +14773,7 @@
         <v>406</v>
       </c>
       <c r="I337" s="0" t="s">
-        <v>833</v>
+        <v>1240</v>
       </c>
       <c r="J337" s="0">
         <v>5662.0551999999998</v>
@@ -14805,7 +14805,7 @@
         <v>407</v>
       </c>
       <c r="I338" s="0" t="s">
-        <v>834</v>
+        <v>1241</v>
       </c>
       <c r="J338" s="0">
         <v>1945.5608</v>
@@ -14837,7 +14837,7 @@
         <v>408</v>
       </c>
       <c r="I339" s="0" t="s">
-        <v>835</v>
+        <v>1242</v>
       </c>
       <c r="J339" s="0">
         <v>1073.6666</v>
@@ -14869,7 +14869,7 @@
         <v>409</v>
       </c>
       <c r="I340" s="0" t="s">
-        <v>836</v>
+        <v>1243</v>
       </c>
       <c r="J340" s="0">
         <v>513.65530000000001</v>
@@ -14901,7 +14901,7 @@
         <v>410</v>
       </c>
       <c r="I341" s="0" t="s">
-        <v>837</v>
+        <v>1244</v>
       </c>
       <c r="J341" s="0">
         <v>457.6961</v>
@@ -14933,7 +14933,7 @@
         <v>411</v>
       </c>
       <c r="I342" s="0" t="s">
-        <v>838</v>
+        <v>1245</v>
       </c>
       <c r="J342" s="0">
         <v>456.3168</v>
@@ -14965,7 +14965,7 @@
         <v>412</v>
       </c>
       <c r="I343" s="0" t="s">
-        <v>839</v>
+        <v>1246</v>
       </c>
       <c r="J343" s="0">
         <v>454.07369999999997</v>
@@ -14997,7 +14997,7 @@
         <v>413</v>
       </c>
       <c r="I344" s="0" t="s">
-        <v>840</v>
+        <v>1247</v>
       </c>
       <c r="J344" s="0">
         <v>429.38220000000001</v>
@@ -15029,7 +15029,7 @@
         <v>414</v>
       </c>
       <c r="I345" s="0" t="s">
-        <v>841</v>
+        <v>1248</v>
       </c>
       <c r="J345" s="0">
         <v>386.53370000000001</v>
@@ -15061,7 +15061,7 @@
         <v>415</v>
       </c>
       <c r="I346" s="0" t="s">
-        <v>842</v>
+        <v>1249</v>
       </c>
       <c r="J346" s="0">
         <v>359.30450000000002</v>
@@ -15093,7 +15093,7 @@
         <v>416</v>
       </c>
       <c r="I347" s="0" t="s">
-        <v>843</v>
+        <v>1250</v>
       </c>
       <c r="J347" s="0">
         <v>330.99799999999999</v>
@@ -15125,7 +15125,7 @@
         <v>417</v>
       </c>
       <c r="I348" s="0" t="s">
-        <v>844</v>
+        <v>1251</v>
       </c>
       <c r="J348" s="0">
         <v>11140.4043</v>
@@ -15157,7 +15157,7 @@
         <v>418</v>
       </c>
       <c r="I349" s="0" t="s">
-        <v>845</v>
+        <v>1252</v>
       </c>
       <c r="J349" s="0">
         <v>7539.1777000000002</v>
@@ -15189,7 +15189,7 @@
         <v>419</v>
       </c>
       <c r="I350" s="0" t="s">
-        <v>846</v>
+        <v>1253</v>
       </c>
       <c r="J350" s="0">
         <v>1166.9911999999999</v>
@@ -15221,7 +15221,7 @@
         <v>420</v>
       </c>
       <c r="I351" s="0" t="s">
-        <v>847</v>
+        <v>1254</v>
       </c>
       <c r="J351" s="0">
         <v>968.274</v>
@@ -15253,7 +15253,7 @@
         <v>421</v>
       </c>
       <c r="I352" s="0" t="s">
-        <v>848</v>
+        <v>1255</v>
       </c>
       <c r="J352" s="0">
         <v>590.66909999999996</v>
@@ -15285,7 +15285,7 @@
         <v>422</v>
       </c>
       <c r="I353" s="0" t="s">
-        <v>849</v>
+        <v>1256</v>
       </c>
       <c r="J353" s="0">
         <v>502.17599999999999</v>
@@ -15317,7 +15317,7 @@
         <v>423</v>
       </c>
       <c r="I354" s="0" t="s">
-        <v>850</v>
+        <v>1257</v>
       </c>
       <c r="J354" s="0">
         <v>479.93529999999998</v>
@@ -15349,7 +15349,7 @@
         <v>424</v>
       </c>
       <c r="I355" s="0" t="s">
-        <v>851</v>
+        <v>1258</v>
       </c>
       <c r="J355" s="0">
         <v>469.60969999999998</v>
@@ -15381,7 +15381,7 @@
         <v>425</v>
       </c>
       <c r="I356" s="0" t="s">
-        <v>852</v>
+        <v>1259</v>
       </c>
       <c r="J356" s="0">
         <v>451.56819999999999</v>
@@ -15413,7 +15413,7 @@
         <v>426</v>
       </c>
       <c r="I357" s="0" t="s">
-        <v>853</v>
+        <v>1260</v>
       </c>
       <c r="J357" s="0">
         <v>412.2346</v>
@@ -15445,7 +15445,7 @@
         <v>427</v>
       </c>
       <c r="I358" s="0" t="s">
-        <v>854</v>
+        <v>1261</v>
       </c>
       <c r="J358" s="0">
         <v>401.46249999999998</v>
@@ -15477,7 +15477,7 @@
         <v>428</v>
       </c>
       <c r="I359" s="0" t="s">
-        <v>855</v>
+        <v>1262</v>
       </c>
       <c r="J359" s="0">
         <v>323.00450000000001</v>
@@ -15509,7 +15509,7 @@
         <v>429</v>
       </c>
       <c r="I360" s="0" t="s">
-        <v>856</v>
+        <v>1263</v>
       </c>
       <c r="J360" s="0">
         <v>11573.126</v>
@@ -15541,7 +15541,7 @@
         <v>430</v>
       </c>
       <c r="I361" s="0" t="s">
-        <v>857</v>
+        <v>1264</v>
       </c>
       <c r="J361" s="0">
         <v>6620.0068000000001</v>
@@ -15573,7 +15573,7 @@
         <v>431</v>
       </c>
       <c r="I362" s="0" t="s">
-        <v>858</v>
+        <v>1265</v>
       </c>
       <c r="J362" s="0">
         <v>751.08780000000002</v>
@@ -15605,7 +15605,7 @@
         <v>432</v>
       </c>
       <c r="I363" s="0" t="s">
-        <v>859</v>
+        <v>1266</v>
       </c>
       <c r="J363" s="0">
         <v>745.37040000000002</v>
@@ -15637,7 +15637,7 @@
         <v>433</v>
       </c>
       <c r="I364" s="0" t="s">
-        <v>860</v>
+        <v>1267</v>
       </c>
       <c r="J364" s="0">
         <v>347.99090000000001</v>
@@ -15669,7 +15669,7 @@
         <v>434</v>
       </c>
       <c r="I365" s="0" t="s">
-        <v>861</v>
+        <v>1268</v>
       </c>
       <c r="J365" s="0">
         <v>332.82709999999997</v>
@@ -15701,7 +15701,7 @@
         <v>435</v>
       </c>
       <c r="I366" s="0" t="s">
-        <v>862</v>
+        <v>1269</v>
       </c>
       <c r="J366" s="0">
         <v>300.09730000000002</v>
@@ -15733,7 +15733,7 @@
         <v>436</v>
       </c>
       <c r="I367" s="0" t="s">
-        <v>863</v>
+        <v>1270</v>
       </c>
       <c r="J367" s="0">
         <v>267.48480000000001</v>
@@ -15765,7 +15765,7 @@
         <v>437</v>
       </c>
       <c r="I368" s="0" t="s">
-        <v>864</v>
+        <v>1271</v>
       </c>
       <c r="J368" s="0">
         <v>247.57060000000001</v>
@@ -15797,7 +15797,7 @@
         <v>438</v>
       </c>
       <c r="I369" s="0" t="s">
-        <v>865</v>
+        <v>1272</v>
       </c>
       <c r="J369" s="0">
         <v>241.20079999999999</v>
@@ -15829,7 +15829,7 @@
         <v>439</v>
       </c>
       <c r="I370" s="0" t="s">
-        <v>866</v>
+        <v>1273</v>
       </c>
       <c r="J370" s="0">
         <v>224.6387</v>
@@ -15861,7 +15861,7 @@
         <v>440</v>
       </c>
       <c r="I371" s="0" t="s">
-        <v>867</v>
+        <v>1274</v>
       </c>
       <c r="J371" s="0">
         <v>196.59559999999999</v>
@@ -15893,7 +15893,7 @@
         <v>441</v>
       </c>
       <c r="I372" s="0" t="s">
-        <v>868</v>
+        <v>1275</v>
       </c>
       <c r="J372" s="0">
         <v>9005.0449000000008</v>
@@ -15925,7 +15925,7 @@
         <v>442</v>
       </c>
       <c r="I373" s="0" t="s">
-        <v>869</v>
+        <v>1276</v>
       </c>
       <c r="J373" s="0">
         <v>8991.1543000000001</v>
@@ -15957,7 +15957,7 @@
         <v>443</v>
       </c>
       <c r="I374" s="0" t="s">
-        <v>870</v>
+        <v>1277</v>
       </c>
       <c r="J374" s="0">
         <v>1060.6902</v>
@@ -15989,7 +15989,7 @@
         <v>444</v>
       </c>
       <c r="I375" s="0" t="s">
-        <v>871</v>
+        <v>1278</v>
       </c>
       <c r="J375" s="0">
         <v>873.68520000000001</v>
@@ -16021,7 +16021,7 @@
         <v>445</v>
       </c>
       <c r="I376" s="0" t="s">
-        <v>872</v>
+        <v>1279</v>
       </c>
       <c r="J376" s="0">
         <v>492.66989999999999</v>
@@ -16053,7 +16053,7 @@
         <v>446</v>
       </c>
       <c r="I377" s="0" t="s">
-        <v>873</v>
+        <v>1280</v>
       </c>
       <c r="J377" s="0">
         <v>479.0992</v>
@@ -16085,7 +16085,7 @@
         <v>447</v>
       </c>
       <c r="I378" s="0" t="s">
-        <v>874</v>
+        <v>1281</v>
       </c>
       <c r="J378" s="0">
         <v>473.75420000000003</v>
@@ -16117,7 +16117,7 @@
         <v>448</v>
       </c>
       <c r="I379" s="0" t="s">
-        <v>875</v>
+        <v>1282</v>
       </c>
       <c r="J379" s="0">
         <v>451.01459999999997</v>
@@ -16149,7 +16149,7 @@
         <v>449</v>
       </c>
       <c r="I380" s="0" t="s">
-        <v>876</v>
+        <v>1283</v>
       </c>
       <c r="J380" s="0">
         <v>445.8254</v>
@@ -16181,7 +16181,7 @@
         <v>450</v>
       </c>
       <c r="I381" s="0" t="s">
-        <v>877</v>
+        <v>1284</v>
       </c>
       <c r="J381" s="0">
         <v>416.5324</v>
@@ -16213,7 +16213,7 @@
         <v>451</v>
       </c>
       <c r="I382" s="0" t="s">
-        <v>878</v>
+        <v>1285</v>
       </c>
       <c r="J382" s="0">
         <v>410.74439999999999</v>
@@ -16245,7 +16245,7 @@
         <v>452</v>
       </c>
       <c r="I383" s="0" t="s">
-        <v>879</v>
+        <v>1286</v>
       </c>
       <c r="J383" s="0">
         <v>398.16070000000002</v>
@@ -16277,7 +16277,7 @@
         <v>453</v>
       </c>
       <c r="I384" s="0" t="s">
-        <v>880</v>
+        <v>1287</v>
       </c>
       <c r="J384" s="0">
         <v>11446.293</v>
@@ -16309,7 +16309,7 @@
         <v>454</v>
       </c>
       <c r="I385" s="0" t="s">
-        <v>881</v>
+        <v>1288</v>
       </c>
       <c r="J385" s="0">
         <v>7034.3638000000001</v>
@@ -16341,7 +16341,7 @@
         <v>457</v>
       </c>
       <c r="I386" s="0" t="s">
-        <v>884</v>
+        <v>1289</v>
       </c>
       <c r="J386" s="0">
         <v>544.20960000000002</v>
@@ -16373,7 +16373,7 @@
         <v>458</v>
       </c>
       <c r="I387" s="0" t="s">
-        <v>885</v>
+        <v>1290</v>
       </c>
       <c r="J387" s="0">
         <v>530.34780000000001</v>
@@ -16405,7 +16405,7 @@
         <v>459</v>
       </c>
       <c r="I388" s="0" t="s">
-        <v>886</v>
+        <v>1291</v>
       </c>
       <c r="J388" s="0">
         <v>496.8383</v>
@@ -16437,7 +16437,7 @@
         <v>460</v>
       </c>
       <c r="I389" s="0" t="s">
-        <v>887</v>
+        <v>1292</v>
       </c>
       <c r="J389" s="0">
         <v>456.82279999999997</v>
@@ -16469,7 +16469,7 @@
         <v>461</v>
       </c>
       <c r="I390" s="0" t="s">
-        <v>888</v>
+        <v>1293</v>
       </c>
       <c r="J390" s="0">
         <v>430.56229999999999</v>
@@ -16501,7 +16501,7 @@
         <v>462</v>
       </c>
       <c r="I391" s="0" t="s">
-        <v>889</v>
+        <v>1294</v>
       </c>
       <c r="J391" s="0">
         <v>394.98270000000002</v>
@@ -16533,7 +16533,7 @@
         <v>463</v>
       </c>
       <c r="I392" s="0" t="s">
-        <v>890</v>
+        <v>1295</v>
       </c>
       <c r="J392" s="0">
         <v>390.7165</v>
@@ -16565,7 +16565,7 @@
         <v>465</v>
       </c>
       <c r="I393" s="0" t="s">
-        <v>892</v>
+        <v>1296</v>
       </c>
       <c r="J393" s="0">
         <v>11910.3838</v>
@@ -16597,7 +16597,7 @@
         <v>466</v>
       </c>
       <c r="I394" s="0" t="s">
-        <v>893</v>
+        <v>1297</v>
       </c>
       <c r="J394" s="0">
         <v>7360.2744000000002</v>
@@ -16629,7 +16629,7 @@
         <v>467</v>
       </c>
       <c r="I395" s="0" t="s">
-        <v>894</v>
+        <v>1298</v>
       </c>
       <c r="J395" s="0">
         <v>712.87210000000005</v>
@@ -16661,7 +16661,7 @@
         <v>469</v>
       </c>
       <c r="I396" s="0" t="s">
-        <v>896</v>
+        <v>1299</v>
       </c>
       <c r="J396" s="0">
         <v>462.625</v>
@@ -16693,7 +16693,7 @@
         <v>470</v>
       </c>
       <c r="I397" s="0" t="s">
-        <v>897</v>
+        <v>1300</v>
       </c>
       <c r="J397" s="0">
         <v>430.88380000000001</v>
@@ -16725,7 +16725,7 @@
         <v>471</v>
       </c>
       <c r="I398" s="0" t="s">
-        <v>898</v>
+        <v>1301</v>
       </c>
       <c r="J398" s="0">
         <v>412.29090000000002</v>
@@ -16757,7 +16757,7 @@
         <v>472</v>
       </c>
       <c r="I399" s="0" t="s">
-        <v>899</v>
+        <v>1302</v>
       </c>
       <c r="J399" s="0">
         <v>401.78739999999999</v>
@@ -16789,7 +16789,7 @@
         <v>473</v>
       </c>
       <c r="I400" s="0" t="s">
-        <v>900</v>
+        <v>1303</v>
       </c>
       <c r="J400" s="0">
         <v>380.73540000000003</v>
@@ -16821,7 +16821,7 @@
         <v>474</v>
       </c>
       <c r="I401" s="0" t="s">
-        <v>901</v>
+        <v>1304</v>
       </c>
       <c r="J401" s="0">
         <v>309.23020000000002</v>
@@ -16853,7 +16853,7 @@
         <v>475</v>
       </c>
       <c r="I402" s="0" t="s">
-        <v>902</v>
+        <v>1305</v>
       </c>
       <c r="J402" s="0">
         <v>275.06909999999999</v>
@@ -16885,7 +16885,7 @@
         <v>476</v>
       </c>
       <c r="I403" s="0" t="s">
-        <v>903</v>
+        <v>1306</v>
       </c>
       <c r="J403" s="0">
         <v>206.4333</v>
